--- a/output/full_scan/batch_seq4_2026-06-22.xlsx
+++ b/output/full_scan/batch_seq4_2026-06-22.xlsx
@@ -792,21 +792,21 @@
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
-        <v>3481</v>
+        <v>3707</v>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>群創</t>
+          <t>漢磊</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
         <v/>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1140.196687668196</v>
+        <v>1130.443434956657</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>66</v>
+        <v>91.5</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
@@ -817,49 +817,49 @@
         <v>0</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>72.26168150955721</v>
+        <v>64.42071255993068</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>37.45602884507969</v>
+        <v>30.76493603777575</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>1.746106408141673</v>
+        <v>1.477174189972248</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>0.7748167574596554</v>
+        <v>0.4573230841525006</v>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
-        <v>3707</v>
+        <v>3481</v>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>漢磊</t>
+          <t>群創</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
         <v/>
       </c>
       <c r="D8" s="2" t="n">
-        <v>1130.443434956657</v>
+        <v>1130.196687668196</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>91.5</v>
+        <v>66</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
@@ -870,29 +870,29 @@
         <v>0</v>
       </c>
       <c r="H8" s="2" t="n">
-        <v>64.42071255993068</v>
+        <v>72.26168150955721</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>30.76493603777575</v>
+        <v>37.45602884507969</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>1.477174189972248</v>
+        <v>1.746106408141673</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>0.4573230841525006</v>
+        <v>0.7748167574596554</v>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, invest_trust_buy_2d, breakout_volume_confirm, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1015,7 +1015,7 @@
         <v/>
       </c>
       <c r="D11" s="2" t="n">
-        <v>1071.839158962671</v>
+        <v>1081.839158962671</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>73.40000000000001</v>
@@ -1121,7 +1121,7 @@
         <v/>
       </c>
       <c r="D13" s="2" t="n">
-        <v>1039.859686656685</v>
+        <v>1049.859686656685</v>
       </c>
       <c r="E13" s="2" t="n">
         <v>66.3</v>
@@ -1174,7 +1174,7 @@
         <v/>
       </c>
       <c r="D14" s="2" t="n">
-        <v>1020.213270207834</v>
+        <v>1010.213270207834</v>
       </c>
       <c r="E14" s="2" t="n">
         <v>42.7</v>
@@ -1216,21 +1216,21 @@
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">
-        <v>3438</v>
+        <v>3714</v>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>類比科</t>
+          <t>富采</t>
         </is>
       </c>
       <c r="C15" s="2" t="n">
         <v/>
       </c>
       <c r="D15" s="2" t="n">
-        <v>1002.807051304218</v>
+        <v>1005.880039920602</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>78.5</v>
+        <v>72.90000000000001</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
@@ -1241,16 +1241,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="2" t="n">
-        <v>64.44530268871236</v>
+        <v>57.65390115394436</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>34.15414062267372</v>
+        <v>16.63122874135879</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.816094749211985</v>
+        <v>1.199380797299028</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>0</v>
@@ -1259,31 +1259,31 @@
         <v>-1</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>-0.1115767941520395</v>
+        <v>0.0720473341523869</v>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="n">
-        <v>3714</v>
+        <v>3438</v>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>富采</t>
+          <t>類比科</t>
         </is>
       </c>
       <c r="C16" s="2" t="n">
         <v/>
       </c>
       <c r="D16" s="2" t="n">
-        <v>995.8800399206024</v>
+        <v>1002.807051304218</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>72.90000000000001</v>
+        <v>78.5</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
@@ -1294,16 +1294,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="2" t="n">
-        <v>57.65390115394436</v>
+        <v>64.44530268871236</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>16.63122874135879</v>
+        <v>34.15414062267372</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.199380797299028</v>
+        <v>1.816094749211985</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L16" s="2" t="n">
         <v>0</v>
@@ -1312,11 +1312,11 @@
         <v>-1</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>0.0720473341523869</v>
+        <v>-0.1115767941520395</v>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, foreign_buy_3d, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
         <v/>
       </c>
       <c r="D22" s="2" t="n">
-        <v>944.1102164069476</v>
+        <v>924.1102164069476</v>
       </c>
       <c r="E22" s="2" t="n">
         <v>557</v>
@@ -1757,7 +1757,7 @@
         <v/>
       </c>
       <c r="D25" s="2" t="n">
-        <v>892.9615164259927</v>
+        <v>902.9615164259928</v>
       </c>
       <c r="E25" s="2" t="n">
         <v>25.95</v>
@@ -1905,21 +1905,21 @@
     </row>
     <row r="28">
       <c r="A28" s="2" t="n">
-        <v>3550</v>
+        <v>3680</v>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>聯穎</t>
+          <t>家登</t>
         </is>
       </c>
       <c r="C28" s="2" t="n">
         <v/>
       </c>
       <c r="D28" s="2" t="n">
-        <v>881.6359117223723</v>
+        <v>880.3919400611363</v>
       </c>
       <c r="E28" s="2" t="n">
-        <v>35.9</v>
+        <v>547</v>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
@@ -1930,13 +1930,13 @@
         <v>0</v>
       </c>
       <c r="H28" s="2" t="n">
-        <v>78.63291082448265</v>
+        <v>56.04960404766393</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>45.71219348478207</v>
+        <v>13.15869168788597</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>2.487102058066101</v>
+        <v>1.258995562055865</v>
       </c>
       <c r="K28" s="2" t="n">
         <v>0</v>
@@ -1948,31 +1948,31 @@
         <v>-1</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>1.246118268079345</v>
+        <v>0.8723614778829152</v>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n">
-        <v>3680</v>
+        <v>3624</v>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>家登</t>
+          <t>光頡</t>
         </is>
       </c>
       <c r="C29" s="2" t="n">
         <v/>
       </c>
       <c r="D29" s="2" t="n">
-        <v>880.3919400611363</v>
+        <v>875.888469222643</v>
       </c>
       <c r="E29" s="2" t="n">
-        <v>547</v>
+        <v>176.5</v>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
@@ -1983,49 +1983,49 @@
         <v>0</v>
       </c>
       <c r="H29" s="2" t="n">
-        <v>56.04960404766393</v>
+        <v>85.20631500498348</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>13.15869168788597</v>
+        <v>34.42488886193586</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>1.258995562055865</v>
+        <v>0.991309185296215</v>
       </c>
       <c r="K29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M29" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>0.8723614778829152</v>
+        <v>4.91164437194525</v>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
-        <v>3624</v>
+        <v>3141</v>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>光頡</t>
+          <t>晶宏</t>
         </is>
       </c>
       <c r="C30" s="2" t="n">
         <v/>
       </c>
       <c r="D30" s="2" t="n">
-        <v>875.888469222643</v>
+        <v>873.5068525213269</v>
       </c>
       <c r="E30" s="2" t="n">
-        <v>176.5</v>
+        <v>78.40000000000001</v>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
@@ -2036,49 +2036,49 @@
         <v>0</v>
       </c>
       <c r="H30" s="2" t="n">
-        <v>85.20631500498348</v>
+        <v>66.18020168353873</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>34.42488886193586</v>
+        <v>32.43403481191611</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>0.991309185296215</v>
+        <v>0.8014751722437315</v>
       </c>
       <c r="K30" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L30" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M30" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N30" s="2" t="n">
-        <v>4.91164437194525</v>
+        <v>-0.7937921305451434</v>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n">
-        <v>3141</v>
+        <v>3406</v>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>晶宏</t>
+          <t>玉晶光</t>
         </is>
       </c>
       <c r="C31" s="2" t="n">
         <v/>
       </c>
       <c r="D31" s="2" t="n">
-        <v>873.5068525213269</v>
+        <v>872.2891076671208</v>
       </c>
       <c r="E31" s="2" t="n">
-        <v>78.40000000000001</v>
+        <v>774</v>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
@@ -2089,16 +2089,16 @@
         <v>0</v>
       </c>
       <c r="H31" s="2" t="n">
-        <v>66.18020168353873</v>
+        <v>69.52995858008583</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>32.43403481191611</v>
+        <v>46.50786972908282</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>0.8014751722437315</v>
+        <v>1.328910766712084</v>
       </c>
       <c r="K31" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L31" s="2" t="n">
         <v>0</v>
@@ -2107,31 +2107,31 @@
         <v>-1</v>
       </c>
       <c r="N31" s="2" t="n">
-        <v>-0.7937921305451434</v>
+        <v>7.844677195767453</v>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n">
-        <v>3675</v>
+        <v>3550</v>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>德微</t>
+          <t>聯穎</t>
         </is>
       </c>
       <c r="C32" s="2" t="n">
         <v/>
       </c>
       <c r="D32" s="2" t="n">
-        <v>867.2964267864029</v>
+        <v>871.6359117223723</v>
       </c>
       <c r="E32" s="2" t="n">
-        <v>405</v>
+        <v>35.9</v>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
@@ -2142,13 +2142,13 @@
         <v>0</v>
       </c>
       <c r="H32" s="2" t="n">
-        <v>68.19634419053942</v>
+        <v>78.63291082448265</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>31.17821984438537</v>
+        <v>45.71219348478207</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>0.2968310550875776</v>
+        <v>2.487102058066101</v>
       </c>
       <c r="K32" s="2" t="n">
         <v>0</v>
@@ -2160,31 +2160,31 @@
         <v>-1</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>-0.1425584684760679</v>
+        <v>1.246118268079345</v>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="n">
-        <v>3527</v>
+        <v>3675</v>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>聚積</t>
+          <t>德微</t>
         </is>
       </c>
       <c r="C33" s="2" t="n">
         <v/>
       </c>
       <c r="D33" s="2" t="n">
-        <v>863.4766944911818</v>
+        <v>867.2964267864029</v>
       </c>
       <c r="E33" s="2" t="n">
-        <v>70.2</v>
+        <v>405</v>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
@@ -2195,16 +2195,16 @@
         <v>0</v>
       </c>
       <c r="H33" s="2" t="n">
-        <v>67.27928118127737</v>
+        <v>68.19634419053942</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>32.45451266622661</v>
+        <v>31.17821984438537</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>1.602511263887109</v>
+        <v>0.2968310550875776</v>
       </c>
       <c r="K33" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L33" s="2" t="n">
         <v>0</v>
@@ -2213,31 +2213,31 @@
         <v>-1</v>
       </c>
       <c r="N33" s="2" t="n">
-        <v>1.302181466542013</v>
+        <v>-0.1425584684760679</v>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, dealer_buy_3d, cci_momentum, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n">
-        <v>3131</v>
+        <v>3311</v>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>弘塑</t>
+          <t>閎暉</t>
         </is>
       </c>
       <c r="C34" s="2" t="n">
         <v/>
       </c>
       <c r="D34" s="2" t="n">
-        <v>861.4059292823422</v>
+        <v>865.0399591686909</v>
       </c>
       <c r="E34" s="2" t="n">
-        <v>3585</v>
+        <v>40.25</v>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
@@ -2248,49 +2248,49 @@
         <v>0</v>
       </c>
       <c r="H34" s="2" t="n">
-        <v>63.31918418701444</v>
+        <v>61.84534186720546</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>18.82090013214684</v>
+        <v>31.30046885245265</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>1.325108987708389</v>
+        <v>0.9699737906504888</v>
       </c>
       <c r="K34" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L34" s="2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M34" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>31.28883214927182</v>
+        <v>-0.0225263760473348</v>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="n">
-        <v>3265</v>
+        <v>3527</v>
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>台星科</t>
+          <t>聚積</t>
         </is>
       </c>
       <c r="C35" s="2" t="n">
         <v/>
       </c>
       <c r="D35" s="2" t="n">
-        <v>857.9307725578986</v>
+        <v>863.4766944911818</v>
       </c>
       <c r="E35" s="2" t="n">
-        <v>193.5</v>
+        <v>70.2</v>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
@@ -2301,13 +2301,13 @@
         <v>0</v>
       </c>
       <c r="H35" s="2" t="n">
-        <v>60.27477866480992</v>
+        <v>67.27928118127737</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>16.65809824073256</v>
+        <v>32.45451266622661</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>1.233678428956675</v>
+        <v>1.602511263887109</v>
       </c>
       <c r="K35" s="2" t="n">
         <v>2</v>
@@ -2319,31 +2319,31 @@
         <v>-1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>0.4630977843997376</v>
+        <v>1.302181466542013</v>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n">
-        <v>3406</v>
+        <v>3131</v>
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>玉晶光</t>
+          <t>弘塑</t>
         </is>
       </c>
       <c r="C36" s="2" t="n">
         <v/>
       </c>
       <c r="D36" s="2" t="n">
-        <v>857.2891076671208</v>
+        <v>861.4059292823422</v>
       </c>
       <c r="E36" s="2" t="n">
-        <v>774</v>
+        <v>3585</v>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
@@ -2354,49 +2354,49 @@
         <v>0</v>
       </c>
       <c r="H36" s="2" t="n">
-        <v>69.52995858008583</v>
+        <v>63.31918418701444</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>46.50786972908282</v>
+        <v>18.82090013214684</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>1.328910766712084</v>
+        <v>1.325108987708389</v>
       </c>
       <c r="K36" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M36" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>7.844677195767453</v>
+        <v>31.28883214927182</v>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n">
-        <v>3311</v>
+        <v>3265</v>
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>閎暉</t>
+          <t>台星科</t>
         </is>
       </c>
       <c r="C37" s="2" t="n">
         <v/>
       </c>
       <c r="D37" s="2" t="n">
-        <v>855.0399591686909</v>
+        <v>857.9307725578986</v>
       </c>
       <c r="E37" s="2" t="n">
-        <v>40.25</v>
+        <v>193.5</v>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
@@ -2407,16 +2407,16 @@
         <v>0</v>
       </c>
       <c r="H37" s="2" t="n">
-        <v>61.84534186720546</v>
+        <v>60.27477866480992</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>31.30046885245265</v>
+        <v>16.65809824073256</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>0.9699737906504888</v>
+        <v>1.233678428956675</v>
       </c>
       <c r="K37" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L37" s="2" t="n">
         <v>0</v>
@@ -2425,11 +2425,11 @@
         <v>-1</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>-0.0225263760473348</v>
+        <v>0.4630977843997376</v>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, breakout_20d, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, cci_momentum, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -2806,21 +2806,21 @@
     </row>
     <row r="45">
       <c r="A45" s="2" t="n">
-        <v>3303</v>
+        <v>3592</v>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>岱稜</t>
+          <t>瑞鼎</t>
         </is>
       </c>
       <c r="C45" s="2" t="n">
         <v/>
       </c>
       <c r="D45" s="2" t="n">
-        <v>807.8357311824307</v>
+        <v>808.0638924730956</v>
       </c>
       <c r="E45" s="2" t="n">
-        <v>60.2</v>
+        <v>285</v>
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
@@ -2831,49 +2831,49 @@
         <v>0</v>
       </c>
       <c r="H45" s="2" t="n">
-        <v>68.57541127075211</v>
+        <v>60.75288678003712</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>34.004015715644</v>
+        <v>17.15383392431712</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.083573118243061</v>
+        <v>1.886675863216412</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M45" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N45" s="2" t="n">
-        <v>0.951981236432685</v>
+        <v>-0.1096970016281604</v>
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n">
-        <v>3455</v>
+        <v>3303</v>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>由田</t>
+          <t>岱稜</t>
         </is>
       </c>
       <c r="C46" s="2" t="n">
         <v/>
       </c>
       <c r="D46" s="2" t="n">
-        <v>805.4848372694787</v>
+        <v>807.8357311824307</v>
       </c>
       <c r="E46" s="2" t="n">
-        <v>266</v>
+        <v>60.2</v>
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
@@ -2884,16 +2884,16 @@
         <v>0</v>
       </c>
       <c r="H46" s="2" t="n">
-        <v>60.33006093555528</v>
+        <v>68.57541127075211</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>21.49855963408047</v>
+        <v>34.004015715644</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>1.789253493273612</v>
+        <v>1.083573118243061</v>
       </c>
       <c r="K46" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L46" s="2" t="n">
         <v>0</v>
@@ -2902,31 +2902,31 @@
         <v>-1</v>
       </c>
       <c r="N46" s="2" t="n">
-        <v>2.627966093965738</v>
+        <v>0.951981236432685</v>
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n">
-        <v>3484</v>
+        <v>3455</v>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>崧騰</t>
+          <t>由田</t>
         </is>
       </c>
       <c r="C47" s="2" t="n">
         <v/>
       </c>
       <c r="D47" s="2" t="n">
-        <v>805.1083271412338</v>
+        <v>805.4848372694787</v>
       </c>
       <c r="E47" s="2" t="n">
-        <v>52.9</v>
+        <v>266</v>
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
@@ -2937,16 +2937,16 @@
         <v>0</v>
       </c>
       <c r="H47" s="2" t="n">
-        <v>71.68317818250299</v>
+        <v>60.33006093555528</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>24.77508467262347</v>
+        <v>21.49855963408047</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>6.829940482745084</v>
+        <v>1.789253493273612</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L47" s="2" t="n">
         <v>0</v>
@@ -2955,31 +2955,31 @@
         <v>-1</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>1.042099753375455</v>
+        <v>2.627966093965738</v>
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n">
-        <v>3592</v>
+        <v>3484</v>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>瑞鼎</t>
+          <t>崧騰</t>
         </is>
       </c>
       <c r="C48" s="2" t="n">
         <v/>
       </c>
       <c r="D48" s="2" t="n">
-        <v>798.0638924730956</v>
+        <v>805.1083271412338</v>
       </c>
       <c r="E48" s="2" t="n">
-        <v>285</v>
+        <v>52.9</v>
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
@@ -2990,49 +2990,49 @@
         <v>0</v>
       </c>
       <c r="H48" s="2" t="n">
-        <v>60.75288678003712</v>
+        <v>71.68317818250299</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>17.15383392431712</v>
+        <v>24.77508467262347</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>1.886675863216412</v>
+        <v>6.829940482745084</v>
       </c>
       <c r="K48" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L48" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M48" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N48" s="2" t="n">
-        <v>-0.1096970016281604</v>
+        <v>1.042099753375455</v>
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n">
-        <v>3583</v>
+        <v>3630</v>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>辛耘</t>
+          <t>新鉅科</t>
         </is>
       </c>
       <c r="C49" s="2" t="n">
         <v/>
       </c>
       <c r="D49" s="2" t="n">
-        <v>785.5654076392259</v>
+        <v>781.2195563711762</v>
       </c>
       <c r="E49" s="2" t="n">
-        <v>889</v>
+        <v>33.65</v>
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
@@ -3043,16 +3043,16 @@
         <v>0</v>
       </c>
       <c r="H49" s="2" t="n">
-        <v>58.40190834356723</v>
+        <v>64.97140442488922</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>20.8756195180744</v>
+        <v>27.55255147073269</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>1.058456039761434</v>
+        <v>0.9219556371176162</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L49" s="2" t="n">
         <v>0</v>
@@ -3061,31 +3061,31 @@
         <v>-1</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>-0.37879956872783</v>
+        <v>0.6846685329886983</v>
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n">
-        <v>3630</v>
+        <v>3520</v>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>新鉅科</t>
+          <t>華盈</t>
         </is>
       </c>
       <c r="C50" s="2" t="n">
         <v/>
       </c>
       <c r="D50" s="2" t="n">
-        <v>781.2195563711762</v>
+        <v>778.3842363980134</v>
       </c>
       <c r="E50" s="2" t="n">
-        <v>33.65</v>
+        <v>16.8</v>
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
@@ -3096,16 +3096,16 @@
         <v>0</v>
       </c>
       <c r="H50" s="2" t="n">
-        <v>64.97140442488922</v>
+        <v>55.45464572885061</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>27.55255147073269</v>
+        <v>35.74806932414902</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>0.9219556371176162</v>
+        <v>0.4598568740232251</v>
       </c>
       <c r="K50" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L50" s="2" t="n">
         <v>0</v>
@@ -3114,31 +3114,31 @@
         <v>-1</v>
       </c>
       <c r="N50" s="2" t="n">
-        <v>0.6846685329886983</v>
+        <v>-0.011889840657288</v>
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n">
-        <v>3520</v>
+        <v>3465</v>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>華盈</t>
+          <t>進泰電子</t>
         </is>
       </c>
       <c r="C51" s="2" t="n">
         <v/>
       </c>
       <c r="D51" s="2" t="n">
-        <v>778.3842363980134</v>
+        <v>778.3015312809114</v>
       </c>
       <c r="E51" s="2" t="n">
-        <v>16.8</v>
+        <v>39.9</v>
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
@@ -3149,16 +3149,16 @@
         <v>0</v>
       </c>
       <c r="H51" s="2" t="n">
-        <v>55.45464572885061</v>
+        <v>73.62428770506888</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>35.74806932414902</v>
+        <v>36.99902776569249</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>0.4598568740232251</v>
+        <v>1.469229784296306</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L51" s="2" t="n">
         <v>0</v>
@@ -3167,31 +3167,31 @@
         <v>-1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>-0.011889840657288</v>
+        <v>0.898974376034532</v>
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n">
-        <v>3465</v>
+        <v>3583</v>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>進泰電子</t>
+          <t>辛耘</t>
         </is>
       </c>
       <c r="C52" s="2" t="n">
         <v/>
       </c>
       <c r="D52" s="2" t="n">
-        <v>778.3015312809114</v>
+        <v>775.5654076392259</v>
       </c>
       <c r="E52" s="2" t="n">
-        <v>39.9</v>
+        <v>889</v>
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
@@ -3202,13 +3202,13 @@
         <v>0</v>
       </c>
       <c r="H52" s="2" t="n">
-        <v>73.62428770506888</v>
+        <v>58.40190834356723</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>36.99902776569249</v>
+        <v>20.8756195180744</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>1.469229784296306</v>
+        <v>1.058456039761434</v>
       </c>
       <c r="K52" s="2" t="n">
         <v>0</v>
@@ -3220,11 +3220,11 @@
         <v>-1</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>0.898974376034532</v>
+        <v>-0.37879956872783</v>
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, breakout_20d, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -3442,21 +3442,21 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="n">
-        <v>3231</v>
+        <v>3706</v>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>緯創</t>
+          <t>神達</t>
         </is>
       </c>
       <c r="C57" s="2" t="n">
         <v/>
       </c>
       <c r="D57" s="2" t="n">
-        <v>736.8536157430791</v>
+        <v>739.8286150262622</v>
       </c>
       <c r="E57" s="2" t="n">
-        <v>162.5</v>
+        <v>87.40000000000001</v>
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
@@ -3467,25 +3467,25 @@
         <v>0</v>
       </c>
       <c r="H57" s="2" t="n">
-        <v>54.30936120980893</v>
+        <v>50.7911930199166</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>17.56622256745875</v>
+        <v>13.74389208776697</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>0.5934922803590745</v>
+        <v>0.6239148051126658</v>
       </c>
       <c r="K57" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="M57" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>-1.356785101922135</v>
+        <v>-0.6179857828160394</v>
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
@@ -3495,21 +3495,21 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="n">
-        <v>3227</v>
+        <v>3231</v>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>原相</t>
+          <t>緯創</t>
         </is>
       </c>
       <c r="C58" s="2" t="n">
         <v/>
       </c>
       <c r="D58" s="2" t="n">
-        <v>733.0584380214254</v>
+        <v>736.8536157430791</v>
       </c>
       <c r="E58" s="2" t="n">
-        <v>230</v>
+        <v>162.5</v>
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
@@ -3520,49 +3520,49 @@
         <v>0</v>
       </c>
       <c r="H58" s="2" t="n">
-        <v>58.54697432451807</v>
+        <v>54.30936120980893</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>22.29506266061848</v>
+        <v>17.56622256745875</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>1.886212681405242</v>
+        <v>0.5934922803590745</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="M58" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>-0.1753356500670888</v>
+        <v>-1.356785101922135</v>
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="n">
-        <v>3362</v>
+        <v>3227</v>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>先進光</t>
+          <t>原相</t>
         </is>
       </c>
       <c r="C59" s="2" t="n">
         <v/>
       </c>
       <c r="D59" s="2" t="n">
-        <v>731.4920376993841</v>
+        <v>733.0584380214254</v>
       </c>
       <c r="E59" s="2" t="n">
-        <v>205</v>
+        <v>230</v>
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
@@ -3573,49 +3573,49 @@
         <v>0</v>
       </c>
       <c r="H59" s="2" t="n">
-        <v>77.50972727252383</v>
+        <v>58.54697432451807</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>44.41944908006825</v>
+        <v>22.29506266061848</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>0.9492037699384104</v>
+        <v>1.886212681405242</v>
       </c>
       <c r="K59" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L59" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L59" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M59" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N59" s="2" t="n">
-        <v>6.509331853913302</v>
+        <v>-0.1753356500670888</v>
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n">
-        <v>3706</v>
+        <v>3362</v>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>神達</t>
+          <t>先進光</t>
         </is>
       </c>
       <c r="C60" s="2" t="n">
         <v/>
       </c>
       <c r="D60" s="2" t="n">
-        <v>724.8286150262622</v>
+        <v>731.4920376993841</v>
       </c>
       <c r="E60" s="2" t="n">
-        <v>87.40000000000001</v>
+        <v>205</v>
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
@@ -3626,29 +3626,29 @@
         <v>0</v>
       </c>
       <c r="H60" s="2" t="n">
-        <v>50.7911930199166</v>
+        <v>77.50972727252383</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>13.74389208776697</v>
+        <v>44.41944908006825</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>0.6239148051126658</v>
+        <v>0.9492037699384104</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>-0.6179857828160394</v>
+        <v>6.509331853913302</v>
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, invest_trust_buy_2d, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -4237,21 +4237,21 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>3673</v>
+        <v>3305</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>昇貿</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>671.5517330220783</v>
+        <v>667.8598628222554</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>88.5</v>
+        <v>147</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>61.34263205151396</v>
+        <v>53.88197701809596</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>30.24548074961963</v>
+        <v>23.2288852919096</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.9672721619824138</v>
+        <v>0.5004286825871733</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,11 +4280,11 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.6974675990064316</v>
+        <v>-1.993182394565167</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -4502,21 +4502,21 @@
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>3305</v>
+        <v>3673</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>昇貿</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>657.8598628222554</v>
+        <v>656.5517330220783</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>147</v>
+        <v>88.5</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,16 +4527,16 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>53.88197701809596</v>
+        <v>61.34263205151396</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>23.2288852919096</v>
+        <v>30.24548074961963</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.5004286825871733</v>
+        <v>0.9672721619824138</v>
       </c>
       <c r="K77" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L77" s="2" t="n">
         <v>0</v>
@@ -4545,11 +4545,11 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-1.993182394565167</v>
+        <v>-0.6974675990064316</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -5032,21 +5032,21 @@
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>3687</v>
+        <v>3704</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>歐買尬</t>
+          <t>合勤控</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>613.2246935901871</v>
+        <v>614.005842275344</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>78</v>
+        <v>48.5</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>59.34037107286859</v>
+        <v>61.77234382079236</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>30.49130489005564</v>
+        <v>34.8180965192699</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>0.8035665119112906</v>
+        <v>0.5307917408635052</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>-0.0101622144645068</v>
+        <v>-0.2056783609273251</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>3529</v>
+        <v>3687</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>歐買尬</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>613.0972710456424</v>
+        <v>613.2246935901871</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>3180</v>
+        <v>78</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,49 +5110,49 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>43.77208415301688</v>
+        <v>59.34037107286859</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>22.59457454145671</v>
+        <v>30.49130489005564</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.6829393924406626</v>
+        <v>0.8035665119112906</v>
       </c>
       <c r="K88" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L88" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M88" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>1.70024473622307</v>
+        <v>-0.0101622144645068</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, invest_trust_buy_2d</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>3704</v>
+        <v>3529</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>合勤控</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>604.005842275344</v>
+        <v>613.0972710456424</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>48.5</v>
+        <v>3180</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,29 +5163,29 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>61.77234382079236</v>
+        <v>43.77208415301688</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>34.8180965192699</v>
+        <v>22.59457454145671</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.5307917408635052</v>
+        <v>0.6829393924406626</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L89" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M89" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.2056783609273251</v>
+        <v>1.70024473622307</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
@@ -5403,21 +5403,21 @@
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>3535</v>
+        <v>3716</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>晶彩科</t>
+          <t>中化控股</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>575.3075720515491</v>
+        <v>574.2150384201967</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>128.5</v>
+        <v>34.65</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,13 +5428,13 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>49.93924454687225</v>
+        <v>51.75048837762611</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>21.48660861444925</v>
+        <v>26.50182621681756</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.9566685319898171</v>
+        <v>0.6333354945597074</v>
       </c>
       <c r="K94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>0.0999533328780184</v>
+        <v>-0.0911583282182207</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>3716</v>
+        <v>3535</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>中化控股</t>
+          <t>晶彩科</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>574.2150384201967</v>
+        <v>565.3075720515491</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>34.65</v>
+        <v>128.5</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,13 +5481,13 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>51.75048837762611</v>
+        <v>49.93924454687225</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>26.50182621681756</v>
+        <v>21.48660861444925</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.6333354945597074</v>
+        <v>0.9566685319898171</v>
       </c>
       <c r="K95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.0911583282182207</v>
+        <v>0.0999533328780184</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>3576</v>
+        <v>3485</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>聯合再生</t>
+          <t>敘豐</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>570.082146079221</v>
+        <v>560.9676459472147</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>18.05</v>
+        <v>319.5</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,16 +5534,16 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>49.00828305495014</v>
+        <v>50.93952067125235</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>22.66382837381164</v>
+        <v>15.08510164229576</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.5326935002116774</v>
+        <v>0.699872054699514</v>
       </c>
       <c r="K96" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.007192002870832</v>
+        <v>-3.854686863258451</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>3485</v>
+        <v>3628</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>敘豐</t>
+          <t>盈正</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>560.9676459472147</v>
+        <v>556.4868513390937</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>319.5</v>
+        <v>75.7</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.93952067125235</v>
+        <v>62.16723127340285</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>15.08510164229576</v>
+        <v>20.73866168268252</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.699872054699514</v>
+        <v>0.8536886664345359</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-3.854686863258451</v>
+        <v>0.2170926462761062</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>3628</v>
+        <v>3576</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>盈正</t>
+          <t>聯合再生</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>556.4868513390937</v>
+        <v>555.082146079221</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>75.7</v>
+        <v>18.05</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,16 +5640,16 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>62.16723127340285</v>
+        <v>49.00828305495014</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20.73866168268252</v>
+        <v>22.66382837381164</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8536886664345359</v>
+        <v>0.5326935002116774</v>
       </c>
       <c r="K98" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L98" s="2" t="n">
         <v>0</v>
@@ -5658,11 +5658,11 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.2170926462761062</v>
+        <v>0.007192002870832</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
@@ -6357,21 +6357,21 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>3339</v>
+        <v>3694</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>泰谷</t>
+          <t>海華</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>518.821804164223</v>
+        <v>519.9125470989625</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>48.2</v>
+        <v>62</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>50.47543529039581</v>
+        <v>46.31765257631338</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>13.24783713183411</v>
+        <v>22.5457907993813</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.8344587325729846</v>
+        <v>1.00217363805531</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.4837216901270664</v>
+        <v>-0.6414765886739584</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>3533</v>
+        <v>3339</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>泰谷</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>514.1720697366537</v>
+        <v>518.821804164223</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>2315</v>
+        <v>48.2</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,16 +6435,16 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>45.56583292183997</v>
+        <v>50.47543529039581</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>20.47655979658528</v>
+        <v>13.24783713183411</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>0.6167123724564944</v>
+        <v>0.8344587325729846</v>
       </c>
       <c r="K113" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L113" s="2" t="n">
         <v>0</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-10.00377851411068</v>
+        <v>0.4837216901270664</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>3287</v>
+        <v>3533</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>廣寰科</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>512.8739784481096</v>
+        <v>514.1720697366537</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>33.75</v>
+        <v>2315</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>49.82585191159364</v>
+        <v>45.56583292183997</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>22.1302407108494</v>
+        <v>20.47655979658528</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.2045152005819464</v>
+        <v>0.6167123724564944</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>-0.4486717116322813</v>
+        <v>-10.00377851411068</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>3694</v>
+        <v>3287</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>海華</t>
+          <t>廣寰科</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>509.9125470989625</v>
+        <v>512.8739784481096</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>62</v>
+        <v>33.75</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>46.31765257631338</v>
+        <v>49.82585191159364</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>22.5457907993813</v>
+        <v>22.1302407108494</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>1.00217363805531</v>
+        <v>0.2045152005819464</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,11 +6559,11 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-0.6414765886739584</v>
+        <v>-0.4486717116322813</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -6834,21 +6834,21 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>3596</v>
+        <v>3135</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>凌航</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>497.6751988455001</v>
+        <v>493.9945230066066</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,49 +6859,49 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>52.60205051409029</v>
+        <v>51.78713153720336</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>20.83811708821046</v>
+        <v>23.05842628506039</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>1.049319449664037</v>
+        <v>0.734647657873297</v>
       </c>
       <c r="K121" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L121" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M121" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-0.1078203106482407</v>
+        <v>-5.390761217192599</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>3135</v>
+        <v>3596</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>凌航</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>478.9945230066066</v>
+        <v>487.6751988455001</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>207</v>
+        <v>188</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,29 +6912,29 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>51.78713153720336</v>
+        <v>52.60205051409029</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>23.05842628506039</v>
+        <v>20.83811708821046</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.734647657873297</v>
+        <v>1.049319449664037</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L122" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M122" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-5.390761217192599</v>
+        <v>-0.1078203106482407</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
@@ -7629,21 +7629,21 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>3702</v>
+        <v>3594</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>磐儀</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>437.6737515703883</v>
+        <v>436.4501157044615</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>112.5</v>
+        <v>48</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,49 +7654,49 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>52.59748221158775</v>
+        <v>48.7665729197427</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>28.53854811019093</v>
+        <v>14.06044978876462</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>0.6059772293666649</v>
+        <v>0.8530255202134293</v>
       </c>
       <c r="K136" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L136" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M136" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>-0.8228878063050823</v>
+        <v>0.059573984566036</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>3594</v>
+        <v>3531</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>磐儀</t>
+          <t>先益</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>436.4501157044615</v>
+        <v>436.0423831938822</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>48</v>
+        <v>23.05</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,16 +7707,16 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>48.7665729197427</v>
+        <v>51.76184407994224</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>14.06044978876462</v>
+        <v>8.566357027043663</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.8530255202134293</v>
+        <v>0.7685508972831726</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.059573984566036</v>
+        <v>0.1058383182346062</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, hist_turn_positive, obv_uptrend</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>3531</v>
+        <v>3653</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>先益</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>436.0423831938822</v>
+        <v>430.1338787044289</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>23.05</v>
+        <v>3840</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,16 +7760,16 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>51.76184407994224</v>
+        <v>50.23712379772032</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>8.566357027043663</v>
+        <v>15.33793728776078</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.7685508972831726</v>
+        <v>0.7723170251738766</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.1058383182346062</v>
+        <v>39.19596538187471</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>3653</v>
+        <v>3332</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>幸康</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>430.1338787044289</v>
+        <v>429.394652325315</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>3840</v>
+        <v>64.8</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,16 +7813,16 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>50.23712379772032</v>
+        <v>50.1720612118065</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>15.33793728776078</v>
+        <v>32.05687782614656</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.7723170251738766</v>
+        <v>0.1382597219696227</v>
       </c>
       <c r="K139" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L139" s="2" t="n">
         <v>0</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>39.19596538187471</v>
+        <v>-0.2697245855413001</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>3332</v>
+        <v>3685</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>幸康</t>
+          <t>元創精密</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>429.394652325315</v>
+        <v>428.6524849038919</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>64.8</v>
+        <v>30.3</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,16 +7866,16 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>50.1720612118065</v>
+        <v>55.20776589026109</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>32.05687782614656</v>
+        <v>10.89929141402712</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.1382597219696227</v>
+        <v>1.096061418320755</v>
       </c>
       <c r="K140" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.2697245855413001</v>
+        <v>0.3021544440643859</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>3685</v>
+        <v>3702</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>元創精密</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>428.6524849038919</v>
+        <v>427.6737515703883</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>30.3</v>
+        <v>112.5</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,29 +7919,29 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>55.20776589026109</v>
+        <v>52.59748221158775</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>10.89929141402712</v>
+        <v>28.53854811019093</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>1.096061418320755</v>
+        <v>0.6059772293666649</v>
       </c>
       <c r="K141" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L141" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M141" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.3021544440643859</v>
+        <v>-0.8228878063050823</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>

--- a/output/full_scan/batch_seq4_2026-06-22.xlsx
+++ b/output/full_scan/batch_seq4_2026-06-22.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O222"/>
+  <dimension ref="A1:O224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3707,21 +3707,21 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="n">
-        <v>3152</v>
+        <v>3532</v>
       </c>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>璟德</t>
+          <t>台勝科</t>
         </is>
       </c>
       <c r="C62" s="2" t="n">
         <v/>
       </c>
       <c r="D62" s="2" t="n">
-        <v>723.1797955172814</v>
+        <v>728.797185238893</v>
       </c>
       <c r="E62" s="2" t="n">
-        <v>208</v>
+        <v>378.5</v>
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
@@ -3732,13 +3732,13 @@
         <v>0</v>
       </c>
       <c r="H62" s="2" t="n">
-        <v>58.4627544405232</v>
+        <v>66.41317875542603</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>32.89176024210005</v>
+        <v>33.84210473905223</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>0.5985630969638646</v>
+        <v>0.2359440425631664</v>
       </c>
       <c r="K62" s="2" t="n">
         <v>1</v>
@@ -3750,31 +3750,31 @@
         <v>-1</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>0.56155500913715</v>
+        <v>6.935322393784773</v>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n">
-        <v>3537</v>
+        <v>3152</v>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>堡達</t>
+          <t>璟德</t>
         </is>
       </c>
       <c r="C63" s="2" t="n">
         <v/>
       </c>
       <c r="D63" s="2" t="n">
-        <v>721.6928495148932</v>
+        <v>723.1797955172814</v>
       </c>
       <c r="E63" s="2" t="n">
-        <v>86</v>
+        <v>208</v>
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
@@ -3785,16 +3785,16 @@
         <v>0</v>
       </c>
       <c r="H63" s="2" t="n">
-        <v>63.64374286873901</v>
+        <v>58.4627544405232</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>34.6025918308987</v>
+        <v>32.89176024210005</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>1.429409536032163</v>
+        <v>0.5985630969638646</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L63" s="2" t="n">
         <v>0</v>
@@ -3803,31 +3803,31 @@
         <v>-1</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>-0.1589991774242953</v>
+        <v>0.56155500913715</v>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n">
-        <v>3617</v>
+        <v>3537</v>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>碩天</t>
+          <t>堡達</t>
         </is>
       </c>
       <c r="C64" s="2" t="n">
         <v/>
       </c>
       <c r="D64" s="2" t="n">
-        <v>713.2672101514631</v>
+        <v>721.6928495148932</v>
       </c>
       <c r="E64" s="2" t="n">
-        <v>213</v>
+        <v>86</v>
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
@@ -3838,16 +3838,16 @@
         <v>0</v>
       </c>
       <c r="H64" s="2" t="n">
-        <v>56.29619270328329</v>
+        <v>63.64374286873901</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>28.22183807715288</v>
+        <v>34.6025918308987</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>0.4989182237319065</v>
+        <v>1.429409536032163</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L64" s="2" t="n">
         <v>0</v>
@@ -3856,31 +3856,31 @@
         <v>-1</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>-1.02329573740215</v>
+        <v>-0.1589991774242953</v>
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n">
-        <v>3605</v>
+        <v>3617</v>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>宏致</t>
+          <t>碩天</t>
         </is>
       </c>
       <c r="C65" s="2" t="n">
         <v/>
       </c>
       <c r="D65" s="2" t="n">
-        <v>700.5043490251014</v>
+        <v>713.2672101514631</v>
       </c>
       <c r="E65" s="2" t="n">
-        <v>80.2</v>
+        <v>213</v>
       </c>
       <c r="F65" s="2" t="inlineStr">
         <is>
@@ -3891,16 +3891,16 @@
         <v>0</v>
       </c>
       <c r="H65" s="2" t="n">
-        <v>57.74976513313724</v>
+        <v>56.29619270328329</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>22.30328913982238</v>
+        <v>28.22183807715288</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>1.332644663111232</v>
+        <v>0.4989182237319065</v>
       </c>
       <c r="K65" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L65" s="2" t="n">
         <v>0</v>
@@ -3909,31 +3909,31 @@
         <v>-1</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>0.5099587468884533</v>
+        <v>-1.02329573740215</v>
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="n">
-        <v>3691</v>
+        <v>3605</v>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>碩禾</t>
+          <t>宏致</t>
         </is>
       </c>
       <c r="C66" s="2" t="n">
         <v/>
       </c>
       <c r="D66" s="2" t="n">
-        <v>696.574683141611</v>
+        <v>700.5043490251014</v>
       </c>
       <c r="E66" s="2" t="n">
-        <v>162</v>
+        <v>80.2</v>
       </c>
       <c r="F66" s="2" t="inlineStr">
         <is>
@@ -3944,16 +3944,16 @@
         <v>0</v>
       </c>
       <c r="H66" s="2" t="n">
-        <v>56.49040552017431</v>
+        <v>57.74976513313724</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>25.21773179673659</v>
+        <v>22.30328913982238</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>0.6310335644302323</v>
+        <v>1.332644663111232</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L66" s="2" t="n">
         <v>0</v>
@@ -3962,31 +3962,31 @@
         <v>-1</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>-1.630386512553542</v>
+        <v>0.5099587468884533</v>
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n">
-        <v>3551</v>
+        <v>3691</v>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>世禾</t>
+          <t>碩禾</t>
         </is>
       </c>
       <c r="C67" s="2" t="n">
         <v/>
       </c>
       <c r="D67" s="2" t="n">
-        <v>694.6165921628658</v>
+        <v>696.574683141611</v>
       </c>
       <c r="E67" s="2" t="n">
-        <v>212.5</v>
+        <v>162</v>
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
@@ -3997,16 +3997,16 @@
         <v>0</v>
       </c>
       <c r="H67" s="2" t="n">
-        <v>57.94497946298473</v>
+        <v>56.49040552017431</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>14.22853520471595</v>
+        <v>25.21773179673659</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>0.6749471680373856</v>
+        <v>0.6310335644302323</v>
       </c>
       <c r="K67" s="2" t="n">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="L67" s="2" t="n">
         <v>0</v>
@@ -4015,31 +4015,31 @@
         <v>-1</v>
       </c>
       <c r="N67" s="2" t="n">
-        <v>0.9715458633488698</v>
+        <v>-1.630386512553542</v>
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, kd_golden_cross, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n">
-        <v>3587</v>
+        <v>3551</v>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>閎康</t>
+          <t>世禾</t>
         </is>
       </c>
       <c r="C68" s="2" t="n">
         <v/>
       </c>
       <c r="D68" s="2" t="n">
-        <v>683.8912525246016</v>
+        <v>694.6165921628658</v>
       </c>
       <c r="E68" s="2" t="n">
-        <v>323</v>
+        <v>212.5</v>
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
@@ -4050,16 +4050,16 @@
         <v>0</v>
       </c>
       <c r="H68" s="2" t="n">
-        <v>54.96142086406913</v>
+        <v>57.94497946298473</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>18.46082347652608</v>
+        <v>14.22853520471595</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>1.687489532170112</v>
+        <v>0.6749471680373856</v>
       </c>
       <c r="K68" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L68" s="2" t="n">
         <v>0</v>
@@ -4068,31 +4068,31 @@
         <v>-1</v>
       </c>
       <c r="N68" s="2" t="n">
-        <v>0.6712966603292045</v>
+        <v>0.9715458633488698</v>
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, foreign_buy_3d, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n">
-        <v>3289</v>
+        <v>3587</v>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>宜特</t>
+          <t>閎康</t>
         </is>
       </c>
       <c r="C69" s="2" t="n">
         <v/>
       </c>
       <c r="D69" s="2" t="n">
-        <v>676.7141805571259</v>
+        <v>683.8912525246016</v>
       </c>
       <c r="E69" s="2" t="n">
-        <v>179</v>
+        <v>323</v>
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
@@ -4103,13 +4103,13 @@
         <v>0</v>
       </c>
       <c r="H69" s="2" t="n">
-        <v>56.49400062916702</v>
+        <v>54.96142086406913</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>12.05500683404701</v>
+        <v>18.46082347652608</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>1.315072423113881</v>
+        <v>1.687489532170112</v>
       </c>
       <c r="K69" s="2" t="n">
         <v>0</v>
@@ -4121,31 +4121,31 @@
         <v>-1</v>
       </c>
       <c r="N69" s="2" t="n">
-        <v>0.9553856908225512</v>
+        <v>0.6712966603292045</v>
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="n">
-        <v>3322</v>
+        <v>3289</v>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>建舜電</t>
+          <t>宜特</t>
         </is>
       </c>
       <c r="C70" s="2" t="n">
         <v/>
       </c>
       <c r="D70" s="2" t="n">
-        <v>674.0160676819659</v>
+        <v>676.7141805571259</v>
       </c>
       <c r="E70" s="2" t="n">
-        <v>15.35</v>
+        <v>179</v>
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
@@ -4156,16 +4156,16 @@
         <v>0</v>
       </c>
       <c r="H70" s="2" t="n">
-        <v>59.67475507652277</v>
+        <v>56.49400062916702</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>22.27329145002015</v>
+        <v>12.05500683404701</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>0.8647611637537213</v>
+        <v>1.315072423113881</v>
       </c>
       <c r="K70" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L70" s="2" t="n">
         <v>0</v>
@@ -4174,31 +4174,31 @@
         <v>-1</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>0.0583471080025971</v>
+        <v>0.9553856908225512</v>
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n">
-        <v>3276</v>
+        <v>3322</v>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>宇環</t>
+          <t>建舜電</t>
         </is>
       </c>
       <c r="C71" s="2" t="n">
         <v/>
       </c>
       <c r="D71" s="2" t="n">
-        <v>672.6607241870548</v>
+        <v>674.0160676819659</v>
       </c>
       <c r="E71" s="2" t="n">
-        <v>15.7</v>
+        <v>15.35</v>
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
@@ -4209,16 +4209,16 @@
         <v>0</v>
       </c>
       <c r="H71" s="2" t="n">
-        <v>62.85306430836195</v>
+        <v>59.67475507652277</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>18.59110753880272</v>
+        <v>22.27329145002015</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>1.74850348267479</v>
+        <v>0.8647611637537213</v>
       </c>
       <c r="K71" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L71" s="2" t="n">
         <v>0</v>
@@ -4227,31 +4227,31 @@
         <v>-1</v>
       </c>
       <c r="N71" s="2" t="n">
-        <v>0.1249033462863587</v>
+        <v>0.0583471080025971</v>
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n">
-        <v>3221</v>
+        <v>3276</v>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>台嘉碩</t>
+          <t>宇環</t>
         </is>
       </c>
       <c r="C72" s="2" t="n">
         <v/>
       </c>
       <c r="D72" s="2" t="n">
-        <v>672.1226734922458</v>
+        <v>672.6607241870548</v>
       </c>
       <c r="E72" s="2" t="n">
-        <v>59.1</v>
+        <v>15.7</v>
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
@@ -4262,16 +4262,16 @@
         <v>0</v>
       </c>
       <c r="H72" s="2" t="n">
-        <v>55.27299157354087</v>
+        <v>62.85306430836195</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>28.07678619833897</v>
+        <v>18.59110753880272</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>0.3704270030802346</v>
+        <v>1.74850348267479</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L72" s="2" t="n">
         <v>0</v>
@@ -4280,31 +4280,31 @@
         <v>-1</v>
       </c>
       <c r="N72" s="2" t="n">
-        <v>-0.5450966717648553</v>
+        <v>0.1249033462863587</v>
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, rsi_strong, breakout_20d, market_above_ma60, avoid_chase, obv_uptrend, breakout_volume_confirm, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n">
-        <v>3305</v>
+        <v>3221</v>
       </c>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>昇貿</t>
+          <t>台嘉碩</t>
         </is>
       </c>
       <c r="C73" s="2" t="n">
         <v/>
       </c>
       <c r="D73" s="2" t="n">
-        <v>667.8598628222554</v>
+        <v>672.1226734922458</v>
       </c>
       <c r="E73" s="2" t="n">
-        <v>147</v>
+        <v>59.1</v>
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
@@ -4315,16 +4315,16 @@
         <v>0</v>
       </c>
       <c r="H73" s="2" t="n">
-        <v>53.8819770313798</v>
+        <v>55.27299157354087</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>23.22888525911432</v>
+        <v>28.07678619833897</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>0.5004286825871733</v>
+        <v>0.3704270030802346</v>
       </c>
       <c r="K73" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L73" s="2" t="n">
         <v>0</v>
@@ -4333,31 +4333,31 @@
         <v>-1</v>
       </c>
       <c r="N73" s="2" t="n">
-        <v>-1.993182394523952</v>
+        <v>-0.5450966717648553</v>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n">
-        <v>3511</v>
+        <v>3305</v>
       </c>
       <c r="B74" s="2" t="inlineStr">
         <is>
-          <t>矽瑪</t>
+          <t>昇貿</t>
         </is>
       </c>
       <c r="C74" s="2" t="n">
         <v/>
       </c>
       <c r="D74" s="2" t="n">
-        <v>666.9219370269159</v>
+        <v>667.8598628222554</v>
       </c>
       <c r="E74" s="2" t="n">
-        <v>24.35</v>
+        <v>147</v>
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
@@ -4368,16 +4368,16 @@
         <v>0</v>
       </c>
       <c r="H74" s="2" t="n">
-        <v>55.82011923388609</v>
+        <v>53.8819770313798</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>25.79657284711957</v>
+        <v>23.22888525911432</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>0.5045955250425628</v>
+        <v>0.5004286825871733</v>
       </c>
       <c r="K74" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L74" s="2" t="n">
         <v>0</v>
@@ -4386,31 +4386,31 @@
         <v>-1</v>
       </c>
       <c r="N74" s="2" t="n">
-        <v>-0.0170178285084073</v>
+        <v>-1.993182394523952</v>
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n">
-        <v>3213</v>
+        <v>3511</v>
       </c>
       <c r="B75" s="2" t="inlineStr">
         <is>
-          <t>茂訊</t>
+          <t>矽瑪</t>
         </is>
       </c>
       <c r="C75" s="2" t="n">
         <v/>
       </c>
       <c r="D75" s="2" t="n">
-        <v>664.3478471193284</v>
+        <v>666.9219370269159</v>
       </c>
       <c r="E75" s="2" t="n">
-        <v>132.5</v>
+        <v>24.35</v>
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
@@ -4421,13 +4421,13 @@
         <v>0</v>
       </c>
       <c r="H75" s="2" t="n">
-        <v>59.18147572818523</v>
+        <v>55.82011923388609</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>46.18341317298956</v>
+        <v>25.79657284711957</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>0.5027181212387851</v>
+        <v>0.5045955250425628</v>
       </c>
       <c r="K75" s="2" t="n">
         <v>0</v>
@@ -4439,31 +4439,31 @@
         <v>-1</v>
       </c>
       <c r="N75" s="2" t="n">
-        <v>-0.4039247782962043</v>
+        <v>-0.0170178285084073</v>
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n">
-        <v>3288</v>
+        <v>3213</v>
       </c>
       <c r="B76" s="2" t="inlineStr">
         <is>
-          <t>點晶</t>
+          <t>茂訊</t>
         </is>
       </c>
       <c r="C76" s="2" t="n">
         <v/>
       </c>
       <c r="D76" s="2" t="n">
-        <v>662.9824747315291</v>
+        <v>664.3478471193284</v>
       </c>
       <c r="E76" s="2" t="n">
-        <v>22.95</v>
+        <v>132.5</v>
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
@@ -4474,16 +4474,16 @@
         <v>0</v>
       </c>
       <c r="H76" s="2" t="n">
-        <v>60.35309258837402</v>
+        <v>59.18147572818523</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>26.40584649209521</v>
+        <v>46.18341317298956</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>1.221014750542468</v>
+        <v>0.5027181212387851</v>
       </c>
       <c r="K76" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L76" s="2" t="n">
         <v>0</v>
@@ -4492,31 +4492,31 @@
         <v>-1</v>
       </c>
       <c r="N76" s="2" t="n">
-        <v>-0.1369308662078101</v>
+        <v>-0.4039247782962043</v>
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="n">
-        <v>3294</v>
+        <v>3288</v>
       </c>
       <c r="B77" s="2" t="inlineStr">
         <is>
-          <t>英濟</t>
+          <t>點晶</t>
         </is>
       </c>
       <c r="C77" s="2" t="n">
         <v/>
       </c>
       <c r="D77" s="2" t="n">
-        <v>660.0862145438249</v>
+        <v>662.9824747315291</v>
       </c>
       <c r="E77" s="2" t="n">
-        <v>40</v>
+        <v>22.95</v>
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
@@ -4527,13 +4527,13 @@
         <v>0</v>
       </c>
       <c r="H77" s="2" t="n">
-        <v>57.08527097379158</v>
+        <v>60.35309258837402</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>28.86286057536094</v>
+        <v>26.40584649209521</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>0.9518450041973088</v>
+        <v>1.221014750542468</v>
       </c>
       <c r="K77" s="2" t="n">
         <v>1</v>
@@ -4545,31 +4545,31 @@
         <v>-1</v>
       </c>
       <c r="N77" s="2" t="n">
-        <v>-0.0756514382495552</v>
+        <v>-0.1369308662078101</v>
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n">
-        <v>3673</v>
+        <v>3294</v>
       </c>
       <c r="B78" s="2" t="inlineStr">
         <is>
-          <t>TPK-KY</t>
+          <t>英濟</t>
         </is>
       </c>
       <c r="C78" s="2" t="n">
         <v/>
       </c>
       <c r="D78" s="2" t="n">
-        <v>656.5517330220783</v>
+        <v>660.0862145438249</v>
       </c>
       <c r="E78" s="2" t="n">
-        <v>88.5</v>
+        <v>40</v>
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
@@ -4580,16 +4580,16 @@
         <v>0</v>
       </c>
       <c r="H78" s="2" t="n">
-        <v>61.34263203135525</v>
+        <v>57.08527097379158</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>30.24548072358155</v>
+        <v>28.86286057536094</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>0.9672721619824138</v>
+        <v>0.9518450041973088</v>
       </c>
       <c r="K78" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L78" s="2" t="n">
         <v>0</v>
@@ -4598,31 +4598,31 @@
         <v>-1</v>
       </c>
       <c r="N78" s="2" t="n">
-        <v>-0.6974675989034065</v>
+        <v>-0.0756514382495552</v>
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n">
-        <v>3236</v>
+        <v>3673</v>
       </c>
       <c r="B79" s="2" t="inlineStr">
         <is>
-          <t>千如</t>
+          <t>TPK-KY</t>
         </is>
       </c>
       <c r="C79" s="2" t="n">
         <v/>
       </c>
       <c r="D79" s="2" t="n">
-        <v>654.6048173551286</v>
+        <v>656.5517330220783</v>
       </c>
       <c r="E79" s="2" t="n">
-        <v>66.40000000000001</v>
+        <v>88.5</v>
       </c>
       <c r="F79" s="2" t="inlineStr">
         <is>
@@ -4633,13 +4633,13 @@
         <v>0</v>
       </c>
       <c r="H79" s="2" t="n">
-        <v>63.93624330324199</v>
+        <v>61.34263203135525</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>43.60045416078073</v>
+        <v>30.24548072358155</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>1.46169520160438</v>
+        <v>0.9672721619824138</v>
       </c>
       <c r="K79" s="2" t="n">
         <v>0</v>
@@ -4651,31 +4651,31 @@
         <v>-1</v>
       </c>
       <c r="N79" s="2" t="n">
-        <v>0.6573301835542757</v>
+        <v>-0.6974675989034065</v>
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n">
-        <v>3150</v>
+        <v>3236</v>
       </c>
       <c r="B80" s="2" t="inlineStr">
         <is>
-          <t>鈺寶-創</t>
+          <t>千如</t>
         </is>
       </c>
       <c r="C80" s="2" t="n">
         <v/>
       </c>
       <c r="D80" s="2" t="n">
-        <v>647.4625363841467</v>
+        <v>654.6048173551286</v>
       </c>
       <c r="E80" s="2" t="n">
-        <v>19.95</v>
+        <v>66.40000000000001</v>
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
@@ -4686,16 +4686,16 @@
         <v>0</v>
       </c>
       <c r="H80" s="2" t="n">
-        <v>58.53783006597459</v>
+        <v>63.93624330324199</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>19.06962528602257</v>
+        <v>43.60045416078073</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>4.253070279888108</v>
+        <v>1.46169520160438</v>
       </c>
       <c r="K80" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L80" s="2" t="n">
         <v>0</v>
@@ -4704,31 +4704,31 @@
         <v>-1</v>
       </c>
       <c r="N80" s="2" t="n">
-        <v>-0.0141610044754643</v>
+        <v>0.6573301835542757</v>
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n">
-        <v>3413</v>
+        <v>3150</v>
       </c>
       <c r="B81" s="2" t="inlineStr">
         <is>
-          <t>京鼎</t>
+          <t>鈺寶-創</t>
         </is>
       </c>
       <c r="C81" s="2" t="n">
         <v/>
       </c>
       <c r="D81" s="2" t="n">
-        <v>645.2200816240153</v>
+        <v>647.4625363841467</v>
       </c>
       <c r="E81" s="2" t="n">
-        <v>321</v>
+        <v>19.95</v>
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
@@ -4739,16 +4739,16 @@
         <v>0</v>
       </c>
       <c r="H81" s="2" t="n">
-        <v>52.10140342830383</v>
+        <v>58.53783006597459</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>10.24468087423086</v>
+        <v>19.06962528602257</v>
       </c>
       <c r="J81" s="2" t="n">
-        <v>0.8412369505595663</v>
+        <v>4.253070279888108</v>
       </c>
       <c r="K81" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L81" s="2" t="n">
         <v>0</v>
@@ -4757,31 +4757,31 @@
         <v>-1</v>
       </c>
       <c r="N81" s="2" t="n">
-        <v>1.208203208123707</v>
+        <v>-0.0141610044754643</v>
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, volume_break, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n">
-        <v>3567</v>
+        <v>3413</v>
       </c>
       <c r="B82" s="2" t="inlineStr">
         <is>
-          <t>逸昌</t>
+          <t>京鼎</t>
         </is>
       </c>
       <c r="C82" s="2" t="n">
         <v/>
       </c>
       <c r="D82" s="2" t="n">
-        <v>644.0458144804535</v>
+        <v>645.2200816240153</v>
       </c>
       <c r="E82" s="2" t="n">
-        <v>28.9</v>
+        <v>321</v>
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
@@ -4792,16 +4792,16 @@
         <v>0</v>
       </c>
       <c r="H82" s="2" t="n">
-        <v>56.73442666434198</v>
+        <v>52.10140342830383</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>24.32126978842252</v>
+        <v>10.24468087423086</v>
       </c>
       <c r="J82" s="2" t="n">
-        <v>1.052972433111477</v>
+        <v>0.8412369505595663</v>
       </c>
       <c r="K82" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L82" s="2" t="n">
         <v>0</v>
@@ -4810,31 +4810,31 @@
         <v>-1</v>
       </c>
       <c r="N82" s="2" t="n">
-        <v>0.0285002000028781</v>
+        <v>1.208203208123707</v>
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n">
-        <v>3607</v>
+        <v>3567</v>
       </c>
       <c r="B83" s="2" t="inlineStr">
         <is>
-          <t>谷崧</t>
+          <t>逸昌</t>
         </is>
       </c>
       <c r="C83" s="2" t="n">
         <v/>
       </c>
       <c r="D83" s="2" t="n">
-        <v>642.3773535059206</v>
+        <v>644.0458144804535</v>
       </c>
       <c r="E83" s="2" t="n">
-        <v>16.95</v>
+        <v>28.9</v>
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
@@ -4845,16 +4845,16 @@
         <v>0</v>
       </c>
       <c r="H83" s="2" t="n">
-        <v>58.31456049165313</v>
+        <v>56.73442666434198</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>26.34411820510409</v>
+        <v>24.32126978842252</v>
       </c>
       <c r="J83" s="2" t="n">
-        <v>0.5050372306466751</v>
+        <v>1.052972433111477</v>
       </c>
       <c r="K83" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L83" s="2" t="n">
         <v>0</v>
@@ -4863,31 +4863,31 @@
         <v>-1</v>
       </c>
       <c r="N83" s="2" t="n">
-        <v>-0.0294973190732885</v>
+        <v>0.0285002000028781</v>
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, hist_turn_positive, foreign_buy_3d, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n">
-        <v>3372</v>
+        <v>3607</v>
       </c>
       <c r="B84" s="2" t="inlineStr">
         <is>
-          <t>典範</t>
+          <t>谷崧</t>
         </is>
       </c>
       <c r="C84" s="2" t="n">
         <v/>
       </c>
       <c r="D84" s="2" t="n">
-        <v>636.5292380096338</v>
+        <v>642.3773535059206</v>
       </c>
       <c r="E84" s="2" t="n">
-        <v>21.5</v>
+        <v>16.95</v>
       </c>
       <c r="F84" s="2" t="inlineStr">
         <is>
@@ -4898,16 +4898,16 @@
         <v>0</v>
       </c>
       <c r="H84" s="2" t="n">
-        <v>57.03861193797648</v>
+        <v>58.31456049165313</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>13.0681800824741</v>
+        <v>26.34411820510409</v>
       </c>
       <c r="J84" s="2" t="n">
-        <v>1.298654829671169</v>
+        <v>0.5050372306466751</v>
       </c>
       <c r="K84" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L84" s="2" t="n">
         <v>0</v>
@@ -4916,31 +4916,31 @@
         <v>-1</v>
       </c>
       <c r="N84" s="2" t="n">
-        <v>-0.0447543643904727</v>
+        <v>-0.0294973190732885</v>
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n">
-        <v>3228</v>
+        <v>3372</v>
       </c>
       <c r="B85" s="2" t="inlineStr">
         <is>
-          <t>金麗科</t>
+          <t>典範</t>
         </is>
       </c>
       <c r="C85" s="2" t="n">
         <v/>
       </c>
       <c r="D85" s="2" t="n">
-        <v>618.921997428468</v>
+        <v>636.5292380096338</v>
       </c>
       <c r="E85" s="2" t="n">
-        <v>195.5</v>
+        <v>21.5</v>
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
@@ -4951,49 +4951,49 @@
         <v>0</v>
       </c>
       <c r="H85" s="2" t="n">
-        <v>54.08488757503573</v>
+        <v>57.03861193797648</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>17.96924676661542</v>
+        <v>13.0681800824741</v>
       </c>
       <c r="J85" s="2" t="n">
-        <v>0.9889732085252608</v>
+        <v>1.298654829671169</v>
       </c>
       <c r="K85" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L85" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M85" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N85" s="2" t="n">
-        <v>1.005495077387884</v>
+        <v>-0.0447543643904727</v>
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, foreign_buy_3d, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n">
-        <v>3597</v>
+        <v>3228</v>
       </c>
       <c r="B86" s="2" t="inlineStr">
         <is>
-          <t>映興</t>
+          <t>金麗科</t>
         </is>
       </c>
       <c r="C86" s="2" t="n">
         <v/>
       </c>
       <c r="D86" s="2" t="n">
-        <v>616.1705276730695</v>
+        <v>618.921997428468</v>
       </c>
       <c r="E86" s="2" t="n">
-        <v>26.4</v>
+        <v>195.5</v>
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
@@ -5004,49 +5004,49 @@
         <v>0</v>
       </c>
       <c r="H86" s="2" t="n">
-        <v>44.07647710059231</v>
+        <v>54.08488757503573</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>44.66975737520595</v>
+        <v>17.96924676661542</v>
       </c>
       <c r="J86" s="2" t="n">
-        <v>0.9824837305327409</v>
+        <v>0.9889732085252608</v>
       </c>
       <c r="K86" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L86" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M86" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N86" s="2" t="n">
-        <v>-0.2333070435541196</v>
+        <v>1.005495077387884</v>
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="n">
-        <v>3443</v>
+        <v>3597</v>
       </c>
       <c r="B87" s="2" t="inlineStr">
         <is>
-          <t>創意</t>
+          <t>映興</t>
         </is>
       </c>
       <c r="C87" s="2" t="n">
         <v/>
       </c>
       <c r="D87" s="2" t="n">
-        <v>616.0314776241194</v>
+        <v>616.1705276730695</v>
       </c>
       <c r="E87" s="2" t="n">
-        <v>4755</v>
+        <v>26.4</v>
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
@@ -5057,16 +5057,16 @@
         <v>0</v>
       </c>
       <c r="H87" s="2" t="n">
-        <v>53.44187391595624</v>
+        <v>44.07647710059231</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>20.67801843130609</v>
+        <v>44.66975737520595</v>
       </c>
       <c r="J87" s="2" t="n">
-        <v>1.064498919498527</v>
+        <v>0.9824837305327409</v>
       </c>
       <c r="K87" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L87" s="2" t="n">
         <v>0</v>
@@ -5075,31 +5075,31 @@
         <v>-1</v>
       </c>
       <c r="N87" s="2" t="n">
-        <v>22.85250478543953</v>
+        <v>-0.2333070435541196</v>
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n">
-        <v>3704</v>
+        <v>3443</v>
       </c>
       <c r="B88" s="2" t="inlineStr">
         <is>
-          <t>合勤控</t>
+          <t>創意</t>
         </is>
       </c>
       <c r="C88" s="2" t="n">
         <v/>
       </c>
       <c r="D88" s="2" t="n">
-        <v>614.005842275344</v>
+        <v>616.0314776241194</v>
       </c>
       <c r="E88" s="2" t="n">
-        <v>48.5</v>
+        <v>4755</v>
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
@@ -5110,13 +5110,13 @@
         <v>0</v>
       </c>
       <c r="H88" s="2" t="n">
-        <v>61.77234377406453</v>
+        <v>53.44187391595624</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>34.81809650049303</v>
+        <v>20.67801843130609</v>
       </c>
       <c r="J88" s="2" t="n">
-        <v>0.5307917408635052</v>
+        <v>1.064498919498527</v>
       </c>
       <c r="K88" s="2" t="n">
         <v>1</v>
@@ -5128,31 +5128,31 @@
         <v>-1</v>
       </c>
       <c r="N88" s="2" t="n">
-        <v>-0.2056783609376227</v>
+        <v>22.85250478543953</v>
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n">
-        <v>3687</v>
+        <v>3704</v>
       </c>
       <c r="B89" s="2" t="inlineStr">
         <is>
-          <t>歐買尬</t>
+          <t>合勤控</t>
         </is>
       </c>
       <c r="C89" s="2" t="n">
         <v/>
       </c>
       <c r="D89" s="2" t="n">
-        <v>613.2246935901871</v>
+        <v>614.005842275344</v>
       </c>
       <c r="E89" s="2" t="n">
-        <v>78</v>
+        <v>48.5</v>
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
@@ -5163,16 +5163,16 @@
         <v>0</v>
       </c>
       <c r="H89" s="2" t="n">
-        <v>59.34037101162424</v>
+        <v>61.77234377406453</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>30.49130496562024</v>
+        <v>34.81809650049303</v>
       </c>
       <c r="J89" s="2" t="n">
-        <v>0.8035665119112906</v>
+        <v>0.5307917408635052</v>
       </c>
       <c r="K89" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L89" s="2" t="n">
         <v>0</v>
@@ -5181,31 +5181,31 @@
         <v>-1</v>
       </c>
       <c r="N89" s="2" t="n">
-        <v>-0.0101622140111787</v>
+        <v>-0.2056783609376227</v>
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n">
-        <v>3529</v>
+        <v>3687</v>
       </c>
       <c r="B90" s="2" t="inlineStr">
         <is>
-          <t>力旺</t>
+          <t>歐買尬</t>
         </is>
       </c>
       <c r="C90" s="2" t="n">
         <v/>
       </c>
       <c r="D90" s="2" t="n">
-        <v>613.0972710456424</v>
+        <v>613.2246935901871</v>
       </c>
       <c r="E90" s="2" t="n">
-        <v>3180</v>
+        <v>78</v>
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
@@ -5216,49 +5216,49 @@
         <v>0</v>
       </c>
       <c r="H90" s="2" t="n">
-        <v>43.77208413443387</v>
+        <v>59.34037101162424</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>22.59457460551849</v>
+        <v>30.49130496562024</v>
       </c>
       <c r="J90" s="2" t="n">
-        <v>0.6829393924406626</v>
+        <v>0.8035665119112906</v>
       </c>
       <c r="K90" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L90" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M90" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N90" s="2" t="n">
-        <v>1.70024474034426</v>
+        <v>-0.0101622140111787</v>
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, invest_trust_buy_2d</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n">
-        <v>3206</v>
+        <v>3529</v>
       </c>
       <c r="B91" s="2" t="inlineStr">
         <is>
-          <t>志豐</t>
+          <t>力旺</t>
         </is>
       </c>
       <c r="C91" s="2" t="n">
         <v/>
       </c>
       <c r="D91" s="2" t="n">
-        <v>602.6148621183451</v>
+        <v>613.0972710456424</v>
       </c>
       <c r="E91" s="2" t="n">
-        <v>38.8</v>
+        <v>3180</v>
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
@@ -5269,49 +5269,49 @@
         <v>0</v>
       </c>
       <c r="H91" s="2" t="n">
-        <v>53.79122027656596</v>
+        <v>43.77208413443387</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>15.46325061922687</v>
+        <v>22.59457460551849</v>
       </c>
       <c r="J91" s="2" t="n">
-        <v>0.7290123921393435</v>
+        <v>0.6829393924406626</v>
       </c>
       <c r="K91" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L91" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M91" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N91" s="2" t="n">
-        <v>-0.0889127464088638</v>
+        <v>1.70024474034426</v>
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, hist_turn_positive, adx_trending, invest_trust_buy_2d</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n">
-        <v>3528</v>
+        <v>3206</v>
       </c>
       <c r="B92" s="2" t="inlineStr">
         <is>
-          <t>安馳</t>
+          <t>志豐</t>
         </is>
       </c>
       <c r="C92" s="2" t="n">
         <v/>
       </c>
       <c r="D92" s="2" t="n">
-        <v>593.4887915666071</v>
+        <v>602.6148621183451</v>
       </c>
       <c r="E92" s="2" t="n">
-        <v>110</v>
+        <v>38.8</v>
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
@@ -5322,16 +5322,16 @@
         <v>0</v>
       </c>
       <c r="H92" s="2" t="n">
-        <v>48.64590911986261</v>
+        <v>53.79122027656596</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>36.25792506554193</v>
+        <v>15.46325061922687</v>
       </c>
       <c r="J92" s="2" t="n">
-        <v>1.800079913186131</v>
+        <v>0.7290123921393435</v>
       </c>
       <c r="K92" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L92" s="2" t="n">
         <v>0</v>
@@ -5340,31 +5340,31 @@
         <v>-1</v>
       </c>
       <c r="N92" s="2" t="n">
-        <v>-3.294561298467642</v>
+        <v>-0.0889127464088638</v>
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="2" t="n">
-        <v>3437</v>
+        <v>3528</v>
       </c>
       <c r="B93" s="2" t="inlineStr">
         <is>
-          <t>榮創</t>
+          <t>安馳</t>
         </is>
       </c>
       <c r="C93" s="2" t="n">
         <v/>
       </c>
       <c r="D93" s="2" t="n">
-        <v>583.3230571098701</v>
+        <v>593.4887915666071</v>
       </c>
       <c r="E93" s="2" t="n">
-        <v>23.25</v>
+        <v>110</v>
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
@@ -5375,16 +5375,16 @@
         <v>0</v>
       </c>
       <c r="H93" s="2" t="n">
-        <v>52.04295994582509</v>
+        <v>48.64590911986261</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>15.40889989672093</v>
+        <v>36.25792506554193</v>
       </c>
       <c r="J93" s="2" t="n">
-        <v>1.183646091037796</v>
+        <v>1.800079913186131</v>
       </c>
       <c r="K93" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L93" s="2" t="n">
         <v>0</v>
@@ -5393,31 +5393,31 @@
         <v>-1</v>
       </c>
       <c r="N93" s="2" t="n">
-        <v>0.0133111211328789</v>
+        <v>-3.294561298467642</v>
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n">
-        <v>3402</v>
+        <v>3437</v>
       </c>
       <c r="B94" s="2" t="inlineStr">
         <is>
-          <t>漢科</t>
+          <t>榮創</t>
         </is>
       </c>
       <c r="C94" s="2" t="n">
         <v/>
       </c>
       <c r="D94" s="2" t="n">
-        <v>578.1106665486611</v>
+        <v>583.3230571098701</v>
       </c>
       <c r="E94" s="2" t="n">
-        <v>142</v>
+        <v>23.25</v>
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
@@ -5428,16 +5428,16 @@
         <v>0</v>
       </c>
       <c r="H94" s="2" t="n">
-        <v>52.0613811587011</v>
+        <v>52.04295994582509</v>
       </c>
       <c r="I94" s="2" t="n">
-        <v>12.69427968771115</v>
+        <v>15.40889989672093</v>
       </c>
       <c r="J94" s="2" t="n">
-        <v>0.4606172962761232</v>
+        <v>1.183646091037796</v>
       </c>
       <c r="K94" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L94" s="2" t="n">
         <v>0</v>
@@ -5446,31 +5446,31 @@
         <v>-1</v>
       </c>
       <c r="N94" s="2" t="n">
-        <v>-0.3072279793168131</v>
+        <v>0.0133111211328789</v>
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, hist_turn_positive, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n">
-        <v>3716</v>
+        <v>3402</v>
       </c>
       <c r="B95" s="2" t="inlineStr">
         <is>
-          <t>中化控股</t>
+          <t>漢科</t>
         </is>
       </c>
       <c r="C95" s="2" t="n">
         <v/>
       </c>
       <c r="D95" s="2" t="n">
-        <v>574.2150384201967</v>
+        <v>578.1106665486611</v>
       </c>
       <c r="E95" s="2" t="n">
-        <v>34.65</v>
+        <v>142</v>
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
@@ -5481,16 +5481,16 @@
         <v>0</v>
       </c>
       <c r="H95" s="2" t="n">
-        <v>51.75048830065435</v>
+        <v>52.0613811587011</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>26.50182622730707</v>
+        <v>12.69427968771115</v>
       </c>
       <c r="J95" s="2" t="n">
-        <v>0.6333354945597074</v>
+        <v>0.4606172962761232</v>
       </c>
       <c r="K95" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L95" s="2" t="n">
         <v>0</v>
@@ -5499,31 +5499,31 @@
         <v>-1</v>
       </c>
       <c r="N95" s="2" t="n">
-        <v>-0.09115832818730921</v>
+        <v>-0.3072279793168131</v>
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n">
-        <v>3535</v>
+        <v>3716</v>
       </c>
       <c r="B96" s="2" t="inlineStr">
         <is>
-          <t>晶彩科</t>
+          <t>中化控股</t>
         </is>
       </c>
       <c r="C96" s="2" t="n">
         <v/>
       </c>
       <c r="D96" s="2" t="n">
-        <v>565.3075720515491</v>
+        <v>574.2150384201967</v>
       </c>
       <c r="E96" s="2" t="n">
-        <v>128.5</v>
+        <v>34.65</v>
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
@@ -5534,13 +5534,13 @@
         <v>0</v>
       </c>
       <c r="H96" s="2" t="n">
-        <v>49.93924450260186</v>
+        <v>51.75048830065435</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>21.48660854549847</v>
+        <v>26.50182622730707</v>
       </c>
       <c r="J96" s="2" t="n">
-        <v>0.9566685319898171</v>
+        <v>0.6333354945597074</v>
       </c>
       <c r="K96" s="2" t="n">
         <v>0</v>
@@ -5552,31 +5552,31 @@
         <v>-1</v>
       </c>
       <c r="N96" s="2" t="n">
-        <v>0.0999533335373901</v>
+        <v>-0.09115832818730921</v>
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n">
-        <v>3485</v>
+        <v>3535</v>
       </c>
       <c r="B97" s="2" t="inlineStr">
         <is>
-          <t>敘豐</t>
+          <t>晶彩科</t>
         </is>
       </c>
       <c r="C97" s="2" t="n">
         <v/>
       </c>
       <c r="D97" s="2" t="n">
-        <v>560.9676459472147</v>
+        <v>565.3075720515491</v>
       </c>
       <c r="E97" s="2" t="n">
-        <v>319.5</v>
+        <v>128.5</v>
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
@@ -5587,13 +5587,13 @@
         <v>0</v>
       </c>
       <c r="H97" s="2" t="n">
-        <v>50.9395206635207</v>
+        <v>49.93924450260186</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>15.08510163478094</v>
+        <v>21.48660854549847</v>
       </c>
       <c r="J97" s="2" t="n">
-        <v>0.699872054699514</v>
+        <v>0.9566685319898171</v>
       </c>
       <c r="K97" s="2" t="n">
         <v>0</v>
@@ -5605,31 +5605,31 @@
         <v>-1</v>
       </c>
       <c r="N97" s="2" t="n">
-        <v>-3.854686862928744</v>
+        <v>0.0999533335373901</v>
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n">
-        <v>3628</v>
+        <v>3485</v>
       </c>
       <c r="B98" s="2" t="inlineStr">
         <is>
-          <t>盈正</t>
+          <t>敘豐</t>
         </is>
       </c>
       <c r="C98" s="2" t="n">
         <v/>
       </c>
       <c r="D98" s="2" t="n">
-        <v>556.4868513390937</v>
+        <v>560.9676459472147</v>
       </c>
       <c r="E98" s="2" t="n">
-        <v>75.7</v>
+        <v>319.5</v>
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
@@ -5640,13 +5640,13 @@
         <v>0</v>
       </c>
       <c r="H98" s="2" t="n">
-        <v>62.16723123119153</v>
+        <v>50.9395206635207</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>20.73866163025856</v>
+        <v>15.08510163478094</v>
       </c>
       <c r="J98" s="2" t="n">
-        <v>0.8536886664345359</v>
+        <v>0.699872054699514</v>
       </c>
       <c r="K98" s="2" t="n">
         <v>0</v>
@@ -5658,31 +5658,31 @@
         <v>-1</v>
       </c>
       <c r="N98" s="2" t="n">
-        <v>0.217092646513074</v>
+        <v>-3.854686862928744</v>
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n">
-        <v>3576</v>
+        <v>3628</v>
       </c>
       <c r="B99" s="2" t="inlineStr">
         <is>
-          <t>聯合再生</t>
+          <t>盈正</t>
         </is>
       </c>
       <c r="C99" s="2" t="n">
         <v/>
       </c>
       <c r="D99" s="2" t="n">
-        <v>555.082146079221</v>
+        <v>556.4868513390937</v>
       </c>
       <c r="E99" s="2" t="n">
-        <v>18.05</v>
+        <v>75.7</v>
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
@@ -5693,16 +5693,16 @@
         <v>0</v>
       </c>
       <c r="H99" s="2" t="n">
-        <v>49.00828303919488</v>
+        <v>62.16723123119153</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>22.66382837815692</v>
+        <v>20.73866163025856</v>
       </c>
       <c r="J99" s="2" t="n">
-        <v>0.5326935002116774</v>
+        <v>0.8536886664345359</v>
       </c>
       <c r="K99" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L99" s="2" t="n">
         <v>0</v>
@@ -5711,31 +5711,31 @@
         <v>-1</v>
       </c>
       <c r="N99" s="2" t="n">
-        <v>0.0071920028934981</v>
+        <v>0.217092646513074</v>
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n">
-        <v>3324</v>
+        <v>3576</v>
       </c>
       <c r="B100" s="2" t="inlineStr">
         <is>
-          <t>雙鴻</t>
+          <t>聯合再生</t>
         </is>
       </c>
       <c r="C100" s="2" t="n">
         <v/>
       </c>
       <c r="D100" s="2" t="n">
-        <v>553.6037982710222</v>
+        <v>555.082146079221</v>
       </c>
       <c r="E100" s="2" t="n">
-        <v>1075</v>
+        <v>18.05</v>
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
@@ -5746,49 +5746,49 @@
         <v>0</v>
       </c>
       <c r="H100" s="2" t="n">
-        <v>50.85437726347062</v>
+        <v>49.00828303919488</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>11.33012934655402</v>
+        <v>22.66382837815692</v>
       </c>
       <c r="J100" s="2" t="n">
-        <v>0.621935027336374</v>
+        <v>0.5326935002116774</v>
       </c>
       <c r="K100" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L100" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M100" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N100" s="2" t="n">
-        <v>-3.932814520373212</v>
+        <v>0.0071920028934981</v>
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n">
-        <v>3260</v>
+        <v>3324</v>
       </c>
       <c r="B101" s="2" t="inlineStr">
         <is>
-          <t>威剛</t>
+          <t>雙鴻</t>
         </is>
       </c>
       <c r="C101" s="2" t="n">
         <v/>
       </c>
       <c r="D101" s="2" t="n">
-        <v>547.6208307809079</v>
+        <v>553.6037982710222</v>
       </c>
       <c r="E101" s="2" t="n">
-        <v>434</v>
+        <v>1075</v>
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
@@ -5799,13 +5799,13 @@
         <v>0</v>
       </c>
       <c r="H101" s="2" t="n">
-        <v>54.16201399605727</v>
+        <v>50.85437726347062</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>9.947799263289086</v>
+        <v>11.33012934655402</v>
       </c>
       <c r="J101" s="2" t="n">
-        <v>0.8817451523155216</v>
+        <v>0.621935027336374</v>
       </c>
       <c r="K101" s="2" t="n">
         <v>0</v>
@@ -5817,31 +5817,31 @@
         <v>-1</v>
       </c>
       <c r="N101" s="2" t="n">
-        <v>0.4368142011342901</v>
+        <v>-3.932814520373212</v>
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n">
-        <v>3580</v>
+        <v>3260</v>
       </c>
       <c r="B102" s="2" t="inlineStr">
         <is>
-          <t>友威科</t>
+          <t>威剛</t>
         </is>
       </c>
       <c r="C102" s="2" t="n">
         <v/>
       </c>
       <c r="D102" s="2" t="n">
-        <v>544.2001915357313</v>
+        <v>547.6208307809079</v>
       </c>
       <c r="E102" s="2" t="n">
-        <v>102.5</v>
+        <v>434</v>
       </c>
       <c r="F102" s="2" t="inlineStr">
         <is>
@@ -5852,49 +5852,49 @@
         <v>0</v>
       </c>
       <c r="H102" s="2" t="n">
-        <v>53.15448475430663</v>
+        <v>54.16201399605727</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>16.1185076952791</v>
+        <v>9.947799263289086</v>
       </c>
       <c r="J102" s="2" t="n">
-        <v>0.6523173142845111</v>
+        <v>0.8817451523155216</v>
       </c>
       <c r="K102" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L102" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="L102" s="2" t="n">
-        <v>0</v>
-      </c>
       <c r="M102" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N102" s="2" t="n">
-        <v>-0.8045741381087064</v>
+        <v>0.4368142011342901</v>
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, hist_turn_positive, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="n">
-        <v>3526</v>
+        <v>3580</v>
       </c>
       <c r="B103" s="2" t="inlineStr">
         <is>
-          <t>凡甲</t>
+          <t>友威科</t>
         </is>
       </c>
       <c r="C103" s="2" t="n">
         <v/>
       </c>
       <c r="D103" s="2" t="n">
-        <v>543.6626323041551</v>
+        <v>544.2001915357313</v>
       </c>
       <c r="E103" s="2" t="n">
-        <v>323.5</v>
+        <v>102.5</v>
       </c>
       <c r="F103" s="2" t="inlineStr">
         <is>
@@ -5905,16 +5905,16 @@
         <v>0</v>
       </c>
       <c r="H103" s="2" t="n">
-        <v>40.41041828980634</v>
+        <v>53.15448475430663</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>25.27482873159911</v>
+        <v>16.1185076952791</v>
       </c>
       <c r="J103" s="2" t="n">
-        <v>1.446758273964226</v>
+        <v>0.6523173142845111</v>
       </c>
       <c r="K103" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L103" s="2" t="n">
         <v>0</v>
@@ -5923,31 +5923,31 @@
         <v>-1</v>
       </c>
       <c r="N103" s="2" t="n">
-        <v>-5.807231855111356</v>
+        <v>-0.8045741381087064</v>
       </c>
       <c r="O103" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n">
-        <v>3564</v>
+        <v>3526</v>
       </c>
       <c r="B104" s="2" t="inlineStr">
         <is>
-          <t>其陽</t>
+          <t>凡甲</t>
         </is>
       </c>
       <c r="C104" s="2" t="n">
         <v/>
       </c>
       <c r="D104" s="2" t="n">
-        <v>538.5155984557849</v>
+        <v>543.6626323041551</v>
       </c>
       <c r="E104" s="2" t="n">
-        <v>47.35</v>
+        <v>323.5</v>
       </c>
       <c r="F104" s="2" t="inlineStr">
         <is>
@@ -5958,16 +5958,16 @@
         <v>0</v>
       </c>
       <c r="H104" s="2" t="n">
-        <v>50.2266777849328</v>
+        <v>40.41041828980634</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>26.65190102536375</v>
+        <v>25.27482873159911</v>
       </c>
       <c r="J104" s="2" t="n">
-        <v>0.3143473699393899</v>
+        <v>1.446758273964226</v>
       </c>
       <c r="K104" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="L104" s="2" t="n">
         <v>0</v>
@@ -5976,31 +5976,31 @@
         <v>-1</v>
       </c>
       <c r="N104" s="2" t="n">
-        <v>-0.6122588529440889</v>
+        <v>-5.807231855111356</v>
       </c>
       <c r="O104" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n">
-        <v>3230</v>
+        <v>3564</v>
       </c>
       <c r="B105" s="2" t="inlineStr">
         <is>
-          <t>錦明</t>
+          <t>其陽</t>
         </is>
       </c>
       <c r="C105" s="2" t="n">
         <v/>
       </c>
       <c r="D105" s="2" t="n">
-        <v>538.4420277703068</v>
+        <v>538.5155984557849</v>
       </c>
       <c r="E105" s="2" t="n">
-        <v>31.35</v>
+        <v>47.35</v>
       </c>
       <c r="F105" s="2" t="inlineStr">
         <is>
@@ -6011,16 +6011,16 @@
         <v>0</v>
       </c>
       <c r="H105" s="2" t="n">
-        <v>52.06723219982984</v>
+        <v>50.2266777849328</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>22.87888155426564</v>
+        <v>26.65190102536375</v>
       </c>
       <c r="J105" s="2" t="n">
-        <v>4.985059924586356</v>
+        <v>0.3143473699393899</v>
       </c>
       <c r="K105" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L105" s="2" t="n">
         <v>0</v>
@@ -6029,31 +6029,31 @@
         <v>-1</v>
       </c>
       <c r="N105" s="2" t="n">
-        <v>0.3168067818585431</v>
+        <v>-0.6122588529440889</v>
       </c>
       <c r="O105" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n">
-        <v>3717</v>
+        <v>3230</v>
       </c>
       <c r="B106" s="2" t="inlineStr">
         <is>
-          <t>聯嘉投控</t>
+          <t>錦明</t>
         </is>
       </c>
       <c r="C106" s="2" t="n">
         <v/>
       </c>
       <c r="D106" s="2" t="n">
-        <v>538.3454085566063</v>
+        <v>538.4420277703068</v>
       </c>
       <c r="E106" s="2" t="n">
-        <v>22.2</v>
+        <v>31.35</v>
       </c>
       <c r="F106" s="2" t="inlineStr">
         <is>
@@ -6064,13 +6064,13 @@
         <v>0</v>
       </c>
       <c r="H106" s="2" t="n">
-        <v>51.54623638672183</v>
+        <v>52.06723219982984</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>18.0693092600979</v>
+        <v>22.87888155426564</v>
       </c>
       <c r="J106" s="2" t="n">
-        <v>0.9345408556606296</v>
+        <v>4.985059924586356</v>
       </c>
       <c r="K106" s="2" t="n">
         <v>0</v>
@@ -6082,31 +6082,31 @@
         <v>-1</v>
       </c>
       <c r="N106" s="2" t="n">
-        <v>0.0560537735319875</v>
+        <v>0.3168067818585431</v>
       </c>
       <c r="O106" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, adx_trending, stronger_than_market, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n">
-        <v>3665</v>
+        <v>3717</v>
       </c>
       <c r="B107" s="2" t="inlineStr">
         <is>
-          <t>貿聯-KY</t>
+          <t>聯嘉投控</t>
         </is>
       </c>
       <c r="C107" s="2" t="n">
         <v/>
       </c>
       <c r="D107" s="2" t="n">
-        <v>528.7865460514956</v>
+        <v>538.3454085566063</v>
       </c>
       <c r="E107" s="2" t="n">
-        <v>1990</v>
+        <v>22.2</v>
       </c>
       <c r="F107" s="2" t="inlineStr">
         <is>
@@ -6117,13 +6117,13 @@
         <v>0</v>
       </c>
       <c r="H107" s="2" t="n">
-        <v>48.34993815947458</v>
+        <v>51.54623638672183</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>14.54011199665573</v>
+        <v>18.0693092600979</v>
       </c>
       <c r="J107" s="2" t="n">
-        <v>1.711340230965312</v>
+        <v>0.9345408556606296</v>
       </c>
       <c r="K107" s="2" t="n">
         <v>0</v>
@@ -6135,31 +6135,31 @@
         <v>-1</v>
       </c>
       <c r="N107" s="2" t="n">
-        <v>23.4372724602461</v>
+        <v>0.0560537735319875</v>
       </c>
       <c r="O107" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n">
-        <v>4164</v>
+        <v>3665</v>
       </c>
       <c r="B108" s="2" t="inlineStr">
         <is>
-          <t>承業醫</t>
+          <t>貿聯-KY</t>
         </is>
       </c>
       <c r="C108" s="2" t="n">
         <v/>
       </c>
       <c r="D108" s="2" t="n">
-        <v>526.9653161361404</v>
+        <v>528.7865460514956</v>
       </c>
       <c r="E108" s="2" t="n">
-        <v>30.4</v>
+        <v>1990</v>
       </c>
       <c r="F108" s="2" t="inlineStr">
         <is>
@@ -6170,13 +6170,13 @@
         <v>0</v>
       </c>
       <c r="H108" s="2" t="n">
-        <v>55.27205094025119</v>
+        <v>48.34993815947458</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>23.79749039236203</v>
+        <v>14.54011199665573</v>
       </c>
       <c r="J108" s="2" t="n">
-        <v>1.359930967196206</v>
+        <v>1.711340230965312</v>
       </c>
       <c r="K108" s="2" t="n">
         <v>0</v>
@@ -6188,31 +6188,31 @@
         <v>-1</v>
       </c>
       <c r="N108" s="2" t="n">
-        <v>0.1391555926643869</v>
+        <v>23.4372724602461</v>
       </c>
       <c r="O108" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, obv_uptrend, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n">
-        <v>3467</v>
+        <v>4164</v>
       </c>
       <c r="B109" s="2" t="inlineStr">
         <is>
-          <t>台灣精材</t>
+          <t>承業醫</t>
         </is>
       </c>
       <c r="C109" s="2" t="n">
         <v/>
       </c>
       <c r="D109" s="2" t="n">
-        <v>523.9569283555318</v>
+        <v>526.9653161361404</v>
       </c>
       <c r="E109" s="2" t="n">
-        <v>68.90000000000001</v>
+        <v>30.4</v>
       </c>
       <c r="F109" s="2" t="inlineStr">
         <is>
@@ -6223,16 +6223,16 @@
         <v>0</v>
       </c>
       <c r="H109" s="2" t="n">
-        <v>55.39346251438909</v>
+        <v>55.27205094025119</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>20.02440961965675</v>
+        <v>23.79749039236203</v>
       </c>
       <c r="J109" s="2" t="n">
-        <v>1.485892694247638</v>
+        <v>1.359930967196206</v>
       </c>
       <c r="K109" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L109" s="2" t="n">
         <v>0</v>
@@ -6241,31 +6241,31 @@
         <v>-1</v>
       </c>
       <c r="N109" s="2" t="n">
-        <v>-0.583388482176999</v>
+        <v>0.1391555926643869</v>
       </c>
       <c r="O109" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n">
-        <v>3310</v>
+        <v>3467</v>
       </c>
       <c r="B110" s="2" t="inlineStr">
         <is>
-          <t>佳穎</t>
+          <t>台灣精材</t>
         </is>
       </c>
       <c r="C110" s="2" t="n">
         <v/>
       </c>
       <c r="D110" s="2" t="n">
-        <v>523.2241660824084</v>
+        <v>523.9569283555318</v>
       </c>
       <c r="E110" s="2" t="n">
-        <v>65.3</v>
+        <v>68.90000000000001</v>
       </c>
       <c r="F110" s="2" t="inlineStr">
         <is>
@@ -6276,16 +6276,16 @@
         <v>0</v>
       </c>
       <c r="H110" s="2" t="n">
-        <v>36.61559641737997</v>
+        <v>55.39346251438909</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>25.28208280167298</v>
+        <v>20.02440961965675</v>
       </c>
       <c r="J110" s="2" t="n">
-        <v>0.1829002293350219</v>
+        <v>1.485892694247638</v>
       </c>
       <c r="K110" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L110" s="2" t="n">
         <v>0</v>
@@ -6294,31 +6294,31 @@
         <v>-1</v>
       </c>
       <c r="N110" s="2" t="n">
-        <v>-0.6082838961956392</v>
+        <v>-0.583388482176999</v>
       </c>
       <c r="O110" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="n">
-        <v>3338</v>
+        <v>3310</v>
       </c>
       <c r="B111" s="2" t="inlineStr">
         <is>
-          <t>泰碩</t>
+          <t>佳穎</t>
         </is>
       </c>
       <c r="C111" s="2" t="n">
         <v/>
       </c>
       <c r="D111" s="2" t="n">
-        <v>522.6669566225755</v>
+        <v>523.2241660824084</v>
       </c>
       <c r="E111" s="2" t="n">
-        <v>75.8</v>
+        <v>65.3</v>
       </c>
       <c r="F111" s="2" t="inlineStr">
         <is>
@@ -6329,16 +6329,16 @@
         <v>0</v>
       </c>
       <c r="H111" s="2" t="n">
-        <v>50.81590118399173</v>
+        <v>36.61559641737997</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>20.34985830804227</v>
+        <v>25.28208280167298</v>
       </c>
       <c r="J111" s="2" t="n">
-        <v>0.428837398548475</v>
+        <v>0.1829002293350219</v>
       </c>
       <c r="K111" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L111" s="2" t="n">
         <v>0</v>
@@ -6347,31 +6347,31 @@
         <v>-1</v>
       </c>
       <c r="N111" s="2" t="n">
-        <v>-0.628664225846808</v>
+        <v>-0.6082838961956392</v>
       </c>
       <c r="O111" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n">
-        <v>3349</v>
+        <v>3338</v>
       </c>
       <c r="B112" s="2" t="inlineStr">
         <is>
-          <t>寶德</t>
+          <t>泰碩</t>
         </is>
       </c>
       <c r="C112" s="2" t="n">
         <v/>
       </c>
       <c r="D112" s="2" t="n">
-        <v>520.379234637475</v>
+        <v>522.6669566225755</v>
       </c>
       <c r="E112" s="2" t="n">
-        <v>18.2</v>
+        <v>75.8</v>
       </c>
       <c r="F112" s="2" t="inlineStr">
         <is>
@@ -6382,16 +6382,16 @@
         <v>0</v>
       </c>
       <c r="H112" s="2" t="n">
-        <v>36.09463411555595</v>
+        <v>50.81590118399173</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>35.48188579722371</v>
+        <v>20.34985830804227</v>
       </c>
       <c r="J112" s="2" t="n">
-        <v>0.3209816010080105</v>
+        <v>0.428837398548475</v>
       </c>
       <c r="K112" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L112" s="2" t="n">
         <v>0</v>
@@ -6400,31 +6400,31 @@
         <v>-1</v>
       </c>
       <c r="N112" s="2" t="n">
-        <v>0.3085544494177639</v>
+        <v>-0.628664225846808</v>
       </c>
       <c r="O112" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n">
-        <v>3694</v>
+        <v>3349</v>
       </c>
       <c r="B113" s="2" t="inlineStr">
         <is>
-          <t>海華</t>
+          <t>寶德</t>
         </is>
       </c>
       <c r="C113" s="2" t="n">
         <v/>
       </c>
       <c r="D113" s="2" t="n">
-        <v>519.9125470989625</v>
+        <v>520.379234637475</v>
       </c>
       <c r="E113" s="2" t="n">
-        <v>62</v>
+        <v>18.2</v>
       </c>
       <c r="F113" s="2" t="inlineStr">
         <is>
@@ -6435,13 +6435,13 @@
         <v>0</v>
       </c>
       <c r="H113" s="2" t="n">
-        <v>46.31765249756896</v>
+        <v>36.09463411555595</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>22.54579079579567</v>
+        <v>35.48188579722371</v>
       </c>
       <c r="J113" s="2" t="n">
-        <v>1.00217363805531</v>
+        <v>0.3209816010080105</v>
       </c>
       <c r="K113" s="2" t="n">
         <v>3</v>
@@ -6453,31 +6453,31 @@
         <v>-1</v>
       </c>
       <c r="N113" s="2" t="n">
-        <v>-0.6414765884472859</v>
+        <v>0.3085544494177639</v>
       </c>
       <c r="O113" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n">
-        <v>3339</v>
+        <v>3694</v>
       </c>
       <c r="B114" s="2" t="inlineStr">
         <is>
-          <t>泰谷</t>
+          <t>海華</t>
         </is>
       </c>
       <c r="C114" s="2" t="n">
         <v/>
       </c>
       <c r="D114" s="2" t="n">
-        <v>518.821804164223</v>
+        <v>519.9125470989625</v>
       </c>
       <c r="E114" s="2" t="n">
-        <v>48.2</v>
+        <v>62</v>
       </c>
       <c r="F114" s="2" t="inlineStr">
         <is>
@@ -6488,16 +6488,16 @@
         <v>0</v>
       </c>
       <c r="H114" s="2" t="n">
-        <v>50.47543531032404</v>
+        <v>46.31765249756896</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>13.24783712705956</v>
+        <v>22.54579079579567</v>
       </c>
       <c r="J114" s="2" t="n">
-        <v>0.8344587325729846</v>
+        <v>1.00217363805531</v>
       </c>
       <c r="K114" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L114" s="2" t="n">
         <v>0</v>
@@ -6506,31 +6506,31 @@
         <v>-1</v>
       </c>
       <c r="N114" s="2" t="n">
-        <v>0.4837216903125196</v>
+        <v>-0.6414765884472859</v>
       </c>
       <c r="O114" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="n">
-        <v>3533</v>
+        <v>3339</v>
       </c>
       <c r="B115" s="2" t="inlineStr">
         <is>
-          <t>嘉澤</t>
+          <t>泰谷</t>
         </is>
       </c>
       <c r="C115" s="2" t="n">
         <v/>
       </c>
       <c r="D115" s="2" t="n">
-        <v>514.1720697366537</v>
+        <v>518.821804164223</v>
       </c>
       <c r="E115" s="2" t="n">
-        <v>2315</v>
+        <v>48.2</v>
       </c>
       <c r="F115" s="2" t="inlineStr">
         <is>
@@ -6541,16 +6541,16 @@
         <v>0</v>
       </c>
       <c r="H115" s="2" t="n">
-        <v>45.56583291802475</v>
+        <v>50.47543531032404</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>20.47655975537912</v>
+        <v>13.24783712705956</v>
       </c>
       <c r="J115" s="2" t="n">
-        <v>0.6167123724564944</v>
+        <v>0.8344587325729846</v>
       </c>
       <c r="K115" s="2" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="L115" s="2" t="n">
         <v>0</v>
@@ -6559,31 +6559,31 @@
         <v>-1</v>
       </c>
       <c r="N115" s="2" t="n">
-        <v>-10.00377851514086</v>
+        <v>0.4837216903125196</v>
       </c>
       <c r="O115" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, stronger_than_market, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n">
-        <v>3287</v>
+        <v>3533</v>
       </c>
       <c r="B116" s="2" t="inlineStr">
         <is>
-          <t>廣寰科</t>
+          <t>嘉澤</t>
         </is>
       </c>
       <c r="C116" s="2" t="n">
         <v/>
       </c>
       <c r="D116" s="2" t="n">
-        <v>512.8739784481096</v>
+        <v>514.1720697366537</v>
       </c>
       <c r="E116" s="2" t="n">
-        <v>33.75</v>
+        <v>2315</v>
       </c>
       <c r="F116" s="2" t="inlineStr">
         <is>
@@ -6594,16 +6594,16 @@
         <v>0</v>
       </c>
       <c r="H116" s="2" t="n">
-        <v>49.8258516986627</v>
+        <v>45.56583291802475</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>22.13024044625012</v>
+        <v>20.47655975537912</v>
       </c>
       <c r="J116" s="2" t="n">
-        <v>0.2045152005819464</v>
+        <v>0.6167123724564944</v>
       </c>
       <c r="K116" s="2" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="L116" s="2" t="n">
         <v>0</v>
@@ -6612,31 +6612,31 @@
         <v>-1</v>
       </c>
       <c r="N116" s="2" t="n">
-        <v>-0.4486717113953127</v>
+        <v>-10.00377851514086</v>
       </c>
       <c r="O116" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n">
-        <v>3631</v>
+        <v>3287</v>
       </c>
       <c r="B117" s="2" t="inlineStr">
         <is>
-          <t>晟楠</t>
+          <t>廣寰科</t>
         </is>
       </c>
       <c r="C117" s="2" t="n">
         <v/>
       </c>
       <c r="D117" s="2" t="n">
-        <v>507.7750723209273</v>
+        <v>512.8739784481096</v>
       </c>
       <c r="E117" s="2" t="n">
-        <v>34.1</v>
+        <v>33.75</v>
       </c>
       <c r="F117" s="2" t="inlineStr">
         <is>
@@ -6647,16 +6647,16 @@
         <v>0</v>
       </c>
       <c r="H117" s="2" t="n">
-        <v>43.85271424885941</v>
+        <v>49.8258516986627</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>21.75119201002221</v>
+        <v>22.13024044625012</v>
       </c>
       <c r="J117" s="2" t="n">
-        <v>0.2701622803005868</v>
+        <v>0.2045152005819464</v>
       </c>
       <c r="K117" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L117" s="2" t="n">
         <v>0</v>
@@ -6665,31 +6665,31 @@
         <v>-1</v>
       </c>
       <c r="N117" s="2" t="n">
-        <v>-0.06461261773186081</v>
+        <v>-0.4486717113953127</v>
       </c>
       <c r="O117" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n">
-        <v>3346</v>
+        <v>3631</v>
       </c>
       <c r="B118" s="2" t="inlineStr">
         <is>
-          <t>麗清</t>
+          <t>晟楠</t>
         </is>
       </c>
       <c r="C118" s="2" t="n">
         <v/>
       </c>
       <c r="D118" s="2" t="n">
-        <v>505.1045854584756</v>
+        <v>507.7750723209273</v>
       </c>
       <c r="E118" s="2" t="n">
-        <v>25</v>
+        <v>34.1</v>
       </c>
       <c r="F118" s="2" t="inlineStr">
         <is>
@@ -6700,16 +6700,16 @@
         <v>0</v>
       </c>
       <c r="H118" s="2" t="n">
-        <v>63.61580326705245</v>
+        <v>43.85271424885941</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>28.30834942262581</v>
+        <v>21.75119201002221</v>
       </c>
       <c r="J118" s="2" t="n">
-        <v>1.025789032038756</v>
+        <v>0.2701622803005868</v>
       </c>
       <c r="K118" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L118" s="2" t="n">
         <v>0</v>
@@ -6718,31 +6718,31 @@
         <v>-1</v>
       </c>
       <c r="N118" s="2" t="n">
-        <v>-0.0525620040461332</v>
+        <v>-0.06461261773186081</v>
       </c>
       <c r="O118" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n">
-        <v>3558</v>
+        <v>3346</v>
       </c>
       <c r="B119" s="2" t="inlineStr">
         <is>
-          <t>神準</t>
+          <t>麗清</t>
         </is>
       </c>
       <c r="C119" s="2" t="n">
         <v/>
       </c>
       <c r="D119" s="2" t="n">
-        <v>503.5864042712982</v>
+        <v>505.1045854584756</v>
       </c>
       <c r="E119" s="2" t="n">
-        <v>133.5</v>
+        <v>25</v>
       </c>
       <c r="F119" s="2" t="inlineStr">
         <is>
@@ -6753,13 +6753,13 @@
         <v>0</v>
       </c>
       <c r="H119" s="2" t="n">
-        <v>52.69626138268642</v>
+        <v>63.61580326705245</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>32.37545941186773</v>
+        <v>28.30834942262581</v>
       </c>
       <c r="J119" s="2" t="n">
-        <v>0.2435806676827513</v>
+        <v>1.025789032038756</v>
       </c>
       <c r="K119" s="2" t="n">
         <v>2</v>
@@ -6771,31 +6771,31 @@
         <v>-1</v>
       </c>
       <c r="N119" s="2" t="n">
-        <v>-1.032968677201041</v>
+        <v>-0.0525620040461332</v>
       </c>
       <c r="O119" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, adx_trending, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n">
-        <v>3523</v>
+        <v>3558</v>
       </c>
       <c r="B120" s="2" t="inlineStr">
         <is>
-          <t>迎輝</t>
+          <t>神準</t>
         </is>
       </c>
       <c r="C120" s="2" t="n">
         <v/>
       </c>
       <c r="D120" s="2" t="n">
-        <v>502.5040834535494</v>
+        <v>503.5864042712982</v>
       </c>
       <c r="E120" s="2" t="n">
-        <v>18.2</v>
+        <v>133.5</v>
       </c>
       <c r="F120" s="2" t="inlineStr">
         <is>
@@ -6806,16 +6806,16 @@
         <v>0</v>
       </c>
       <c r="H120" s="2" t="n">
-        <v>57.51789188440914</v>
+        <v>52.69626138268642</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>12.56291043388217</v>
+        <v>32.37545941186773</v>
       </c>
       <c r="J120" s="2" t="n">
-        <v>1.062249529358316</v>
+        <v>0.2435806676827513</v>
       </c>
       <c r="K120" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L120" s="2" t="n">
         <v>0</v>
@@ -6824,31 +6824,31 @@
         <v>-1</v>
       </c>
       <c r="N120" s="2" t="n">
-        <v>-0.2379981234660941</v>
+        <v>-1.032968677201041</v>
       </c>
       <c r="O120" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n">
-        <v>3209</v>
+        <v>3523</v>
       </c>
       <c r="B121" s="2" t="inlineStr">
         <is>
-          <t>全科</t>
+          <t>迎輝</t>
         </is>
       </c>
       <c r="C121" s="2" t="n">
         <v/>
       </c>
       <c r="D121" s="2" t="n">
-        <v>502.1494297536957</v>
+        <v>502.5040834535494</v>
       </c>
       <c r="E121" s="2" t="n">
-        <v>62.8</v>
+        <v>18.2</v>
       </c>
       <c r="F121" s="2" t="inlineStr">
         <is>
@@ -6859,16 +6859,16 @@
         <v>0</v>
       </c>
       <c r="H121" s="2" t="n">
-        <v>43.34583487084502</v>
+        <v>57.51789188440914</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>31.7177758085504</v>
+        <v>12.56291043388217</v>
       </c>
       <c r="J121" s="2" t="n">
-        <v>0.6048040663134628</v>
+        <v>1.062249529358316</v>
       </c>
       <c r="K121" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L121" s="2" t="n">
         <v>0</v>
@@ -6877,31 +6877,31 @@
         <v>-1</v>
       </c>
       <c r="N121" s="2" t="n">
-        <v>-1.946743783177783</v>
+        <v>-0.2379981234660941</v>
       </c>
       <c r="O121" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, stronger_than_market, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="2" t="n">
-        <v>3135</v>
+        <v>3209</v>
       </c>
       <c r="B122" s="2" t="inlineStr">
         <is>
-          <t>凌航</t>
+          <t>全科</t>
         </is>
       </c>
       <c r="C122" s="2" t="n">
         <v/>
       </c>
       <c r="D122" s="2" t="n">
-        <v>493.9945230066066</v>
+        <v>502.1494297536957</v>
       </c>
       <c r="E122" s="2" t="n">
-        <v>207</v>
+        <v>62.8</v>
       </c>
       <c r="F122" s="2" t="inlineStr">
         <is>
@@ -6912,13 +6912,13 @@
         <v>0</v>
       </c>
       <c r="H122" s="2" t="n">
-        <v>51.78713153013416</v>
+        <v>43.34583487084502</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>23.05842628506039</v>
+        <v>31.7177758085504</v>
       </c>
       <c r="J122" s="2" t="n">
-        <v>0.734647657873297</v>
+        <v>0.6048040663134628</v>
       </c>
       <c r="K122" s="2" t="n">
         <v>0</v>
@@ -6930,31 +6930,31 @@
         <v>-1</v>
       </c>
       <c r="N122" s="2" t="n">
-        <v>-5.390761217151395</v>
+        <v>-1.946743783177783</v>
       </c>
       <c r="O122" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n">
-        <v>3596</v>
+        <v>3135</v>
       </c>
       <c r="B123" s="2" t="inlineStr">
         <is>
-          <t>智易</t>
+          <t>凌航</t>
         </is>
       </c>
       <c r="C123" s="2" t="n">
         <v/>
       </c>
       <c r="D123" s="2" t="n">
-        <v>487.6751988455001</v>
+        <v>493.9945230066066</v>
       </c>
       <c r="E123" s="2" t="n">
-        <v>188</v>
+        <v>207</v>
       </c>
       <c r="F123" s="2" t="inlineStr">
         <is>
@@ -6965,49 +6965,49 @@
         <v>0</v>
       </c>
       <c r="H123" s="2" t="n">
-        <v>52.60205047418167</v>
+        <v>51.78713153013416</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>20.8381171137185</v>
+        <v>23.05842628506039</v>
       </c>
       <c r="J123" s="2" t="n">
-        <v>1.049319449664037</v>
+        <v>0.734647657873297</v>
       </c>
       <c r="K123" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L123" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M123" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N123" s="2" t="n">
-        <v>-0.1078203100300942</v>
+        <v>-5.390761217151395</v>
       </c>
       <c r="O123" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, dealer_buy_3d, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n">
-        <v>4155</v>
+        <v>3596</v>
       </c>
       <c r="B124" s="2" t="inlineStr">
         <is>
-          <t>訊映</t>
+          <t>智易</t>
         </is>
       </c>
       <c r="C124" s="2" t="n">
         <v/>
       </c>
       <c r="D124" s="2" t="n">
-        <v>474.2779219273294</v>
+        <v>487.6751988455001</v>
       </c>
       <c r="E124" s="2" t="n">
-        <v>15</v>
+        <v>188</v>
       </c>
       <c r="F124" s="2" t="inlineStr">
         <is>
@@ -7018,49 +7018,49 @@
         <v>0</v>
       </c>
       <c r="H124" s="2" t="n">
-        <v>53.68227238840266</v>
+        <v>52.60205047418167</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>27.51302373354916</v>
+        <v>20.8381171137185</v>
       </c>
       <c r="J124" s="2" t="n">
-        <v>0.497928934265723</v>
+        <v>1.049319449664037</v>
       </c>
       <c r="K124" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L124" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M124" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N124" s="2" t="n">
-        <v>-0.0472588057517753</v>
+        <v>-0.1078203100300942</v>
       </c>
       <c r="O124" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n">
-        <v>3168</v>
+        <v>4155</v>
       </c>
       <c r="B125" s="2" t="inlineStr">
         <is>
-          <t>眾福科</t>
+          <t>訊映</t>
         </is>
       </c>
       <c r="C125" s="2" t="n">
         <v/>
       </c>
       <c r="D125" s="2" t="n">
-        <v>471.781307458334</v>
+        <v>474.2779219273294</v>
       </c>
       <c r="E125" s="2" t="n">
-        <v>45.1</v>
+        <v>15</v>
       </c>
       <c r="F125" s="2" t="inlineStr">
         <is>
@@ -7071,16 +7071,16 @@
         <v>0</v>
       </c>
       <c r="H125" s="2" t="n">
-        <v>43.04407006750487</v>
+        <v>53.68227238840266</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>26.36120571599666</v>
+        <v>27.51302373354916</v>
       </c>
       <c r="J125" s="2" t="n">
-        <v>1.605765392193476</v>
+        <v>0.497928934265723</v>
       </c>
       <c r="K125" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L125" s="2" t="n">
         <v>0</v>
@@ -7089,31 +7089,31 @@
         <v>-1</v>
       </c>
       <c r="N125" s="2" t="n">
-        <v>-0.3219356299720243</v>
+        <v>-0.0472588057517753</v>
       </c>
       <c r="O125" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n">
-        <v>3130</v>
+        <v>3168</v>
       </c>
       <c r="B126" s="2" t="inlineStr">
         <is>
-          <t>一零四</t>
+          <t>眾福科</t>
         </is>
       </c>
       <c r="C126" s="2" t="n">
         <v/>
       </c>
       <c r="D126" s="2" t="n">
-        <v>469.9151003461616</v>
+        <v>471.781307458334</v>
       </c>
       <c r="E126" s="2" t="n">
-        <v>223.5</v>
+        <v>45.1</v>
       </c>
       <c r="F126" s="2" t="inlineStr">
         <is>
@@ -7124,16 +7124,16 @@
         <v>0</v>
       </c>
       <c r="H126" s="2" t="n">
-        <v>53.93134011053408</v>
+        <v>43.04407006750487</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>22.25315872696339</v>
+        <v>26.36120571599666</v>
       </c>
       <c r="J126" s="2" t="n">
-        <v>1.144866832794302</v>
+        <v>1.605765392193476</v>
       </c>
       <c r="K126" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L126" s="2" t="n">
         <v>0</v>
@@ -7142,31 +7142,31 @@
         <v>-1</v>
       </c>
       <c r="N126" s="2" t="n">
-        <v>0.18580158235643</v>
+        <v>-0.3219356299720243</v>
       </c>
       <c r="O126" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n">
-        <v>3498</v>
+        <v>3130</v>
       </c>
       <c r="B127" s="2" t="inlineStr">
         <is>
-          <t>陽程</t>
+          <t>一零四</t>
         </is>
       </c>
       <c r="C127" s="2" t="n">
         <v/>
       </c>
       <c r="D127" s="2" t="n">
-        <v>469.3669002817722</v>
+        <v>469.9151003461616</v>
       </c>
       <c r="E127" s="2" t="n">
-        <v>123</v>
+        <v>223.5</v>
       </c>
       <c r="F127" s="2" t="inlineStr">
         <is>
@@ -7177,13 +7177,13 @@
         <v>0</v>
       </c>
       <c r="H127" s="2" t="n">
-        <v>47.93526396469358</v>
+        <v>53.93134011053408</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>24.79450541828891</v>
+        <v>22.25315872696339</v>
       </c>
       <c r="J127" s="2" t="n">
-        <v>0.6519521997114077</v>
+        <v>1.144866832794302</v>
       </c>
       <c r="K127" s="2" t="n">
         <v>0</v>
@@ -7195,28 +7195,28 @@
         <v>-1</v>
       </c>
       <c r="N127" s="2" t="n">
-        <v>-3.040468751942162</v>
+        <v>0.18580158235643</v>
       </c>
       <c r="O127" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n">
-        <v>3577</v>
+        <v>3498</v>
       </c>
       <c r="B128" s="2" t="inlineStr">
         <is>
-          <t>泓格</t>
+          <t>陽程</t>
         </is>
       </c>
       <c r="C128" s="2" t="n">
         <v/>
       </c>
       <c r="D128" s="2" t="n">
-        <v>469.1010500361998</v>
+        <v>469.3669002817722</v>
       </c>
       <c r="E128" s="2" t="n">
         <v>123</v>
@@ -7230,13 +7230,13 @@
         <v>0</v>
       </c>
       <c r="H128" s="2" t="n">
-        <v>48.41379239165018</v>
+        <v>47.93526396469358</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>31.74159520746511</v>
+        <v>24.79450541828891</v>
       </c>
       <c r="J128" s="2" t="n">
-        <v>0.4995520518665973</v>
+        <v>0.6519521997114077</v>
       </c>
       <c r="K128" s="2" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
         <v>-1</v>
       </c>
       <c r="N128" s="2" t="n">
-        <v>-4.102486790259638</v>
+        <v>-3.040468751942162</v>
       </c>
       <c r="O128" s="2" t="inlineStr">
         <is>
@@ -7258,21 +7258,21 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="n">
-        <v>3701</v>
+        <v>3577</v>
       </c>
       <c r="B129" s="2" t="inlineStr">
         <is>
-          <t>大眾控</t>
+          <t>泓格</t>
         </is>
       </c>
       <c r="C129" s="2" t="n">
         <v/>
       </c>
       <c r="D129" s="2" t="n">
-        <v>467.1656265958664</v>
+        <v>469.1010500361998</v>
       </c>
       <c r="E129" s="2" t="n">
-        <v>48.35</v>
+        <v>123</v>
       </c>
       <c r="F129" s="2" t="inlineStr">
         <is>
@@ -7283,16 +7283,16 @@
         <v>0</v>
       </c>
       <c r="H129" s="2" t="n">
-        <v>37.33926814754953</v>
+        <v>48.41379239165018</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>29.44696349284253</v>
+        <v>31.74159520746511</v>
       </c>
       <c r="J129" s="2" t="n">
-        <v>0.7496660627527587</v>
+        <v>0.4995520518665973</v>
       </c>
       <c r="K129" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L129" s="2" t="n">
         <v>0</v>
@@ -7301,51 +7301,51 @@
         <v>-1</v>
       </c>
       <c r="N129" s="2" t="n">
-        <v>-0.2442041556460701</v>
+        <v>-4.102486790259638</v>
       </c>
       <c r="O129" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n">
-        <v>3454</v>
+        <v>3701</v>
       </c>
       <c r="B130" s="2" t="inlineStr">
         <is>
-          <t>晶睿</t>
+          <t>大眾控</t>
         </is>
       </c>
       <c r="C130" s="2" t="n">
         <v/>
       </c>
       <c r="D130" s="2" t="n">
-        <v>456.3789192122704</v>
+        <v>467.1656265958664</v>
       </c>
       <c r="E130" s="2" t="n">
-        <v>80.8</v>
+        <v>48.35</v>
       </c>
       <c r="F130" s="2" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="G130" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H130" s="2" t="n">
-        <v>4.286335297009472</v>
+        <v>37.33926814754953</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>58.10942737719737</v>
+        <v>29.44696349284253</v>
       </c>
       <c r="J130" s="2" t="n">
-        <v>0.1127673925682696</v>
+        <v>0.7496660627527587</v>
       </c>
       <c r="K130" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L130" s="2" t="n">
         <v>0</v>
@@ -7354,31 +7354,31 @@
         <v>-1</v>
       </c>
       <c r="N130" s="2" t="n">
-        <v>-1.353741947495876</v>
+        <v>-0.2442041556460701</v>
       </c>
       <c r="O130" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n">
-        <v>3625</v>
+        <v>3167</v>
       </c>
       <c r="B131" s="2" t="inlineStr">
         <is>
-          <t>西勝</t>
+          <t>大量</t>
         </is>
       </c>
       <c r="C131" s="2" t="n">
         <v/>
       </c>
       <c r="D131" s="2" t="n">
-        <v>454.6647733254905</v>
+        <v>465.2456881810246</v>
       </c>
       <c r="E131" s="2" t="n">
-        <v>15.9</v>
+        <v>805</v>
       </c>
       <c r="F131" s="2" t="inlineStr">
         <is>
@@ -7389,16 +7389,16 @@
         <v>0</v>
       </c>
       <c r="H131" s="2" t="n">
-        <v>55.81473978417433</v>
+        <v>49.27972313664575</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>12.93482748093394</v>
+        <v>26.13921213746944</v>
       </c>
       <c r="J131" s="2" t="n">
-        <v>0.8385393530817313</v>
+        <v>0.2333558348072571</v>
       </c>
       <c r="K131" s="2" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L131" s="2" t="n">
         <v>0</v>
@@ -7407,51 +7407,51 @@
         <v>-1</v>
       </c>
       <c r="N131" s="2" t="n">
-        <v>0.1089634546115882</v>
+        <v>-15.11459257868671</v>
       </c>
       <c r="O131" s="2" t="inlineStr">
         <is>
-          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n">
-        <v>3490</v>
+        <v>3454</v>
       </c>
       <c r="B132" s="2" t="inlineStr">
         <is>
-          <t>單井</t>
+          <t>晶睿</t>
         </is>
       </c>
       <c r="C132" s="2" t="n">
         <v/>
       </c>
       <c r="D132" s="2" t="n">
-        <v>452.5835864300942</v>
+        <v>456.3789192122704</v>
       </c>
       <c r="E132" s="2" t="n">
-        <v>33.4</v>
+        <v>80.8</v>
       </c>
       <c r="F132" s="2" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G132" s="2" t="b">
         <v>0</v>
       </c>
       <c r="H132" s="2" t="n">
-        <v>45.97116978550491</v>
+        <v>4.286335297009472</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>24.84180203554006</v>
+        <v>58.10942737719737</v>
       </c>
       <c r="J132" s="2" t="n">
-        <v>0.4535052322515051</v>
+        <v>0.1127673925682696</v>
       </c>
       <c r="K132" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L132" s="2" t="n">
         <v>0</v>
@@ -7460,31 +7460,31 @@
         <v>-1</v>
       </c>
       <c r="N132" s="2" t="n">
-        <v>-0.601895833103774</v>
+        <v>-1.353741947495876</v>
       </c>
       <c r="O132" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n">
-        <v>3703</v>
+        <v>3625</v>
       </c>
       <c r="B133" s="2" t="inlineStr">
         <is>
-          <t>欣陸</t>
+          <t>西勝</t>
         </is>
       </c>
       <c r="C133" s="2" t="n">
         <v/>
       </c>
       <c r="D133" s="2" t="n">
-        <v>449.7613114426896</v>
+        <v>454.6647733254905</v>
       </c>
       <c r="E133" s="2" t="n">
-        <v>21.45</v>
+        <v>15.9</v>
       </c>
       <c r="F133" s="2" t="inlineStr">
         <is>
@@ -7495,16 +7495,16 @@
         <v>0</v>
       </c>
       <c r="H133" s="2" t="n">
-        <v>53.51033667180196</v>
+        <v>55.81473978417433</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>32.78299136444975</v>
+        <v>12.93482748093394</v>
       </c>
       <c r="J133" s="2" t="n">
-        <v>1.064083110814707</v>
+        <v>0.8385393530817313</v>
       </c>
       <c r="K133" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="L133" s="2" t="n">
         <v>0</v>
@@ -7513,31 +7513,31 @@
         <v>-1</v>
       </c>
       <c r="N133" s="2" t="n">
-        <v>0.0591316597645437</v>
+        <v>0.1089634546115882</v>
       </c>
       <c r="O133" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>rsi_strong, market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n">
-        <v>3308</v>
+        <v>3490</v>
       </c>
       <c r="B134" s="2" t="inlineStr">
         <is>
-          <t>聯德</t>
+          <t>單井</t>
         </is>
       </c>
       <c r="C134" s="2" t="n">
         <v/>
       </c>
       <c r="D134" s="2" t="n">
-        <v>448.6987288708636</v>
+        <v>452.5835864300942</v>
       </c>
       <c r="E134" s="2" t="n">
-        <v>22.15</v>
+        <v>33.4</v>
       </c>
       <c r="F134" s="2" t="inlineStr">
         <is>
@@ -7548,13 +7548,13 @@
         <v>0</v>
       </c>
       <c r="H134" s="2" t="n">
-        <v>58.88320132817515</v>
+        <v>45.97116978550491</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>18.56392177938816</v>
+        <v>24.84180203554006</v>
       </c>
       <c r="J134" s="2" t="n">
-        <v>0.9186732129217736</v>
+        <v>0.4535052322515051</v>
       </c>
       <c r="K134" s="2" t="n">
         <v>1</v>
@@ -7566,31 +7566,31 @@
         <v>-1</v>
       </c>
       <c r="N134" s="2" t="n">
-        <v>0.0845267459085831</v>
+        <v>-0.601895833103774</v>
       </c>
       <c r="O134" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n">
-        <v>3491</v>
+        <v>3703</v>
       </c>
       <c r="B135" s="2" t="inlineStr">
         <is>
-          <t>昇達科</t>
+          <t>欣陸</t>
         </is>
       </c>
       <c r="C135" s="2" t="n">
         <v/>
       </c>
       <c r="D135" s="2" t="n">
-        <v>448.0650725011026</v>
+        <v>449.7613114426896</v>
       </c>
       <c r="E135" s="2" t="n">
-        <v>1470</v>
+        <v>21.45</v>
       </c>
       <c r="F135" s="2" t="inlineStr">
         <is>
@@ -7601,13 +7601,13 @@
         <v>0</v>
       </c>
       <c r="H135" s="2" t="n">
-        <v>34.27507557850262</v>
+        <v>53.51033667180196</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>20.67177131300901</v>
+        <v>32.78299136444975</v>
       </c>
       <c r="J135" s="2" t="n">
-        <v>1.682643869530403</v>
+        <v>1.064083110814707</v>
       </c>
       <c r="K135" s="2" t="n">
         <v>0</v>
@@ -7619,31 +7619,31 @@
         <v>-1</v>
       </c>
       <c r="N135" s="2" t="n">
-        <v>-54.43798297718874</v>
+        <v>0.0591316597645437</v>
       </c>
       <c r="O135" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n">
-        <v>3306</v>
+        <v>3308</v>
       </c>
       <c r="B136" s="2" t="inlineStr">
         <is>
-          <t>鼎天</t>
+          <t>聯德</t>
         </is>
       </c>
       <c r="C136" s="2" t="n">
         <v/>
       </c>
       <c r="D136" s="2" t="n">
-        <v>442.3022110288781</v>
+        <v>448.6987288708636</v>
       </c>
       <c r="E136" s="2" t="n">
-        <v>49.35</v>
+        <v>22.15</v>
       </c>
       <c r="F136" s="2" t="inlineStr">
         <is>
@@ -7654,13 +7654,13 @@
         <v>0</v>
       </c>
       <c r="H136" s="2" t="n">
-        <v>60.6399956781041</v>
+        <v>58.88320132817515</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>17.82735299727746</v>
+        <v>18.56392177938816</v>
       </c>
       <c r="J136" s="2" t="n">
-        <v>1.180866068904268</v>
+        <v>0.9186732129217736</v>
       </c>
       <c r="K136" s="2" t="n">
         <v>1</v>
@@ -7672,31 +7672,31 @@
         <v>-1</v>
       </c>
       <c r="N136" s="2" t="n">
-        <v>0.1080780278082022</v>
+        <v>0.0845267459085831</v>
       </c>
       <c r="O136" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, obv_uptrend, cci_momentum, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n">
-        <v>3594</v>
+        <v>3491</v>
       </c>
       <c r="B137" s="2" t="inlineStr">
         <is>
-          <t>磐儀</t>
+          <t>昇達科</t>
         </is>
       </c>
       <c r="C137" s="2" t="n">
         <v/>
       </c>
       <c r="D137" s="2" t="n">
-        <v>436.4501157044615</v>
+        <v>448.0650725011026</v>
       </c>
       <c r="E137" s="2" t="n">
-        <v>48</v>
+        <v>1470</v>
       </c>
       <c r="F137" s="2" t="inlineStr">
         <is>
@@ -7707,16 +7707,16 @@
         <v>0</v>
       </c>
       <c r="H137" s="2" t="n">
-        <v>48.76657284435035</v>
+        <v>34.27507557850262</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>14.06044986459563</v>
+        <v>20.67177131300901</v>
       </c>
       <c r="J137" s="2" t="n">
-        <v>0.8530255202134293</v>
+        <v>1.682643869530403</v>
       </c>
       <c r="K137" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L137" s="2" t="n">
         <v>0</v>
@@ -7725,31 +7725,31 @@
         <v>-1</v>
       </c>
       <c r="N137" s="2" t="n">
-        <v>0.0595739848545244</v>
+        <v>-54.43798297718874</v>
       </c>
       <c r="O137" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, hist_turn_positive, obv_uptrend</t>
+          <t>ema60_gt_ema120, volume_break, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n">
-        <v>3531</v>
+        <v>3306</v>
       </c>
       <c r="B138" s="2" t="inlineStr">
         <is>
-          <t>先益</t>
+          <t>鼎天</t>
         </is>
       </c>
       <c r="C138" s="2" t="n">
         <v/>
       </c>
       <c r="D138" s="2" t="n">
-        <v>436.0423831938822</v>
+        <v>442.3022110288781</v>
       </c>
       <c r="E138" s="2" t="n">
-        <v>23.05</v>
+        <v>49.35</v>
       </c>
       <c r="F138" s="2" t="inlineStr">
         <is>
@@ -7760,16 +7760,16 @@
         <v>0</v>
       </c>
       <c r="H138" s="2" t="n">
-        <v>51.76184408071256</v>
+        <v>60.6399956781041</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>8.5663570925083</v>
+        <v>17.82735299727746</v>
       </c>
       <c r="J138" s="2" t="n">
-        <v>0.7685508972831726</v>
+        <v>1.180866068904268</v>
       </c>
       <c r="K138" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L138" s="2" t="n">
         <v>0</v>
@@ -7778,31 +7778,31 @@
         <v>-1</v>
       </c>
       <c r="N138" s="2" t="n">
-        <v>0.1058383181315774</v>
+        <v>0.1080780278082022</v>
       </c>
       <c r="O138" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, obv_uptrend, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n">
-        <v>3653</v>
+        <v>3594</v>
       </c>
       <c r="B139" s="2" t="inlineStr">
         <is>
-          <t>健策</t>
+          <t>磐儀</t>
         </is>
       </c>
       <c r="C139" s="2" t="n">
         <v/>
       </c>
       <c r="D139" s="2" t="n">
-        <v>430.1338787044289</v>
+        <v>436.4501157044615</v>
       </c>
       <c r="E139" s="2" t="n">
-        <v>3840</v>
+        <v>48</v>
       </c>
       <c r="F139" s="2" t="inlineStr">
         <is>
@@ -7813,13 +7813,13 @@
         <v>0</v>
       </c>
       <c r="H139" s="2" t="n">
-        <v>50.23712378688845</v>
+        <v>48.76657284435035</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>15.33793728776077</v>
+        <v>14.06044986459563</v>
       </c>
       <c r="J139" s="2" t="n">
-        <v>0.7723170251738766</v>
+        <v>0.8530255202134293</v>
       </c>
       <c r="K139" s="2" t="n">
         <v>2</v>
@@ -7831,31 +7831,31 @@
         <v>-1</v>
       </c>
       <c r="N139" s="2" t="n">
-        <v>39.19596538290489</v>
+        <v>0.0595739848545244</v>
       </c>
       <c r="O139" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, hist_turn_positive, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n">
-        <v>3332</v>
+        <v>3531</v>
       </c>
       <c r="B140" s="2" t="inlineStr">
         <is>
-          <t>幸康</t>
+          <t>先益</t>
         </is>
       </c>
       <c r="C140" s="2" t="n">
         <v/>
       </c>
       <c r="D140" s="2" t="n">
-        <v>429.394652325315</v>
+        <v>436.0423831938822</v>
       </c>
       <c r="E140" s="2" t="n">
-        <v>64.8</v>
+        <v>23.05</v>
       </c>
       <c r="F140" s="2" t="inlineStr">
         <is>
@@ -7866,13 +7866,13 @@
         <v>0</v>
       </c>
       <c r="H140" s="2" t="n">
-        <v>50.17206297741185</v>
+        <v>51.76184408071256</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>32.0568804743076</v>
+        <v>8.5663570925083</v>
       </c>
       <c r="J140" s="2" t="n">
-        <v>0.1382597219696227</v>
+        <v>0.7685508972831726</v>
       </c>
       <c r="K140" s="2" t="n">
         <v>0</v>
@@ -7884,31 +7884,31 @@
         <v>-1</v>
       </c>
       <c r="N140" s="2" t="n">
-        <v>-0.2697245935981641</v>
+        <v>0.1058383181315774</v>
       </c>
       <c r="O140" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n">
-        <v>3685</v>
+        <v>3653</v>
       </c>
       <c r="B141" s="2" t="inlineStr">
         <is>
-          <t>元創精密</t>
+          <t>健策</t>
         </is>
       </c>
       <c r="C141" s="2" t="n">
         <v/>
       </c>
       <c r="D141" s="2" t="n">
-        <v>428.6524849038919</v>
+        <v>430.1338787044289</v>
       </c>
       <c r="E141" s="2" t="n">
-        <v>30.3</v>
+        <v>3840</v>
       </c>
       <c r="F141" s="2" t="inlineStr">
         <is>
@@ -7919,16 +7919,16 @@
         <v>0</v>
       </c>
       <c r="H141" s="2" t="n">
-        <v>55.20776584904218</v>
+        <v>50.23712378688845</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>10.89929153088304</v>
+        <v>15.33793728776077</v>
       </c>
       <c r="J141" s="2" t="n">
-        <v>1.096061418320755</v>
+        <v>0.7723170251738766</v>
       </c>
       <c r="K141" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L141" s="2" t="n">
         <v>0</v>
@@ -7937,31 +7937,31 @@
         <v>-1</v>
       </c>
       <c r="N141" s="2" t="n">
-        <v>0.3021544441571112</v>
+        <v>39.19596538290489</v>
       </c>
       <c r="O141" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n">
-        <v>3702</v>
+        <v>3332</v>
       </c>
       <c r="B142" s="2" t="inlineStr">
         <is>
-          <t>大聯大</t>
+          <t>幸康</t>
         </is>
       </c>
       <c r="C142" s="2" t="n">
         <v/>
       </c>
       <c r="D142" s="2" t="n">
-        <v>427.6737515703883</v>
+        <v>429.394652325315</v>
       </c>
       <c r="E142" s="2" t="n">
-        <v>112.5</v>
+        <v>64.8</v>
       </c>
       <c r="F142" s="2" t="inlineStr">
         <is>
@@ -7972,49 +7972,49 @@
         <v>0</v>
       </c>
       <c r="H142" s="2" t="n">
-        <v>52.59748221387073</v>
+        <v>50.17206297741185</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>28.53854809218693</v>
+        <v>32.0568804743076</v>
       </c>
       <c r="J142" s="2" t="n">
-        <v>0.6059772293666649</v>
+        <v>0.1382597219696227</v>
       </c>
       <c r="K142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L142" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M142" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N142" s="2" t="n">
-        <v>-0.8228878063256806</v>
+        <v>-0.2697245935981641</v>
       </c>
       <c r="O142" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n">
-        <v>3444</v>
+        <v>3685</v>
       </c>
       <c r="B143" s="2" t="inlineStr">
         <is>
-          <t>利機</t>
+          <t>元創精密</t>
         </is>
       </c>
       <c r="C143" s="2" t="n">
         <v/>
       </c>
       <c r="D143" s="2" t="n">
-        <v>427.2138445581874</v>
+        <v>428.6524849038919</v>
       </c>
       <c r="E143" s="2" t="n">
-        <v>95.59999999999999</v>
+        <v>30.3</v>
       </c>
       <c r="F143" s="2" t="inlineStr">
         <is>
@@ -8025,16 +8025,16 @@
         <v>0</v>
       </c>
       <c r="H143" s="2" t="n">
-        <v>49.95256115212616</v>
+        <v>55.20776584904218</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>23.39844942877617</v>
+        <v>10.89929153088304</v>
       </c>
       <c r="J143" s="2" t="n">
-        <v>0.5112415617064874</v>
+        <v>1.096061418320755</v>
       </c>
       <c r="K143" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L143" s="2" t="n">
         <v>0</v>
@@ -8043,31 +8043,31 @@
         <v>-1</v>
       </c>
       <c r="N143" s="2" t="n">
-        <v>-1.242336675686875</v>
+        <v>0.3021544441571112</v>
       </c>
       <c r="O143" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n">
-        <v>4137</v>
+        <v>3702</v>
       </c>
       <c r="B144" s="2" t="inlineStr">
         <is>
-          <t>麗豐-KY</t>
+          <t>大聯大</t>
         </is>
       </c>
       <c r="C144" s="2" t="n">
         <v/>
       </c>
       <c r="D144" s="2" t="n">
-        <v>424.9827217669008</v>
+        <v>427.6737515703883</v>
       </c>
       <c r="E144" s="2" t="n">
-        <v>110</v>
+        <v>112.5</v>
       </c>
       <c r="F144" s="2" t="inlineStr">
         <is>
@@ -8078,49 +8078,49 @@
         <v>0</v>
       </c>
       <c r="H144" s="2" t="n">
-        <v>56.08984101435404</v>
+        <v>52.59748221387073</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>26.28514231571081</v>
+        <v>28.53854809218693</v>
       </c>
       <c r="J144" s="2" t="n">
-        <v>0.6764901095667947</v>
+        <v>0.6059772293666649</v>
       </c>
       <c r="K144" s="2" t="n">
         <v>1</v>
       </c>
       <c r="L144" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M144" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N144" s="2" t="n">
-        <v>0.0703250170159813</v>
+        <v>-0.8228878063256806</v>
       </c>
       <c r="O144" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n">
-        <v>3483</v>
+        <v>3444</v>
       </c>
       <c r="B145" s="2" t="inlineStr">
         <is>
-          <t>力致</t>
+          <t>利機</t>
         </is>
       </c>
       <c r="C145" s="2" t="n">
         <v/>
       </c>
       <c r="D145" s="2" t="n">
-        <v>421.7100147479502</v>
+        <v>427.2138445581874</v>
       </c>
       <c r="E145" s="2" t="n">
-        <v>94.7</v>
+        <v>95.59999999999999</v>
       </c>
       <c r="F145" s="2" t="inlineStr">
         <is>
@@ -8131,16 +8131,16 @@
         <v>0</v>
       </c>
       <c r="H145" s="2" t="n">
-        <v>51.05445231853944</v>
+        <v>49.95256115212616</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>19.53242777282233</v>
+        <v>23.39844942877617</v>
       </c>
       <c r="J145" s="2" t="n">
-        <v>0.3844562992563745</v>
+        <v>0.5112415617064874</v>
       </c>
       <c r="K145" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L145" s="2" t="n">
         <v>0</v>
@@ -8149,31 +8149,31 @@
         <v>-1</v>
       </c>
       <c r="N145" s="2" t="n">
-        <v>-0.7141652754272243</v>
+        <v>-1.242336675686875</v>
       </c>
       <c r="O145" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n">
-        <v>3518</v>
+        <v>4137</v>
       </c>
       <c r="B146" s="2" t="inlineStr">
         <is>
-          <t>柏騰</t>
+          <t>麗豐-KY</t>
         </is>
       </c>
       <c r="C146" s="2" t="n">
         <v/>
       </c>
       <c r="D146" s="2" t="n">
-        <v>420.9055153341761</v>
+        <v>424.9827217669008</v>
       </c>
       <c r="E146" s="2" t="n">
-        <v>30.9</v>
+        <v>110</v>
       </c>
       <c r="F146" s="2" t="inlineStr">
         <is>
@@ -8184,16 +8184,16 @@
         <v>0</v>
       </c>
       <c r="H146" s="2" t="n">
-        <v>50.78900839820299</v>
+        <v>56.08984101435404</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>25.13950461218356</v>
+        <v>26.28514231571081</v>
       </c>
       <c r="J146" s="2" t="n">
-        <v>1.271634037936032</v>
+        <v>0.6764901095667947</v>
       </c>
       <c r="K146" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L146" s="2" t="n">
         <v>0</v>
@@ -8202,31 +8202,31 @@
         <v>-1</v>
       </c>
       <c r="N146" s="2" t="n">
-        <v>-0.2528093365805167</v>
+        <v>0.0703250170159813</v>
       </c>
       <c r="O146" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, rsi_strong, market_above_ma60, avoid_chase, adx_trending, kd_golden_cross</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="2" t="n">
-        <v>3259</v>
+        <v>3483</v>
       </c>
       <c r="B147" s="2" t="inlineStr">
         <is>
-          <t>鑫創</t>
+          <t>力致</t>
         </is>
       </c>
       <c r="C147" s="2" t="n">
         <v/>
       </c>
       <c r="D147" s="2" t="n">
-        <v>418.376526288707</v>
+        <v>421.7100147479502</v>
       </c>
       <c r="E147" s="2" t="n">
-        <v>17.05</v>
+        <v>94.7</v>
       </c>
       <c r="F147" s="2" t="inlineStr">
         <is>
@@ -8237,16 +8237,16 @@
         <v>0</v>
       </c>
       <c r="H147" s="2" t="n">
-        <v>51.4629286245998</v>
+        <v>51.05445231853944</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>17.77304653627238</v>
+        <v>19.53242777282233</v>
       </c>
       <c r="J147" s="2" t="n">
-        <v>1.598990125007318</v>
+        <v>0.3844562992563745</v>
       </c>
       <c r="K147" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L147" s="2" t="n">
         <v>0</v>
@@ -8255,31 +8255,31 @@
         <v>-1</v>
       </c>
       <c r="N147" s="2" t="n">
-        <v>-0.0036031036055289</v>
+        <v>-0.7141652754272243</v>
       </c>
       <c r="O147" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n">
-        <v>3563</v>
+        <v>3518</v>
       </c>
       <c r="B148" s="2" t="inlineStr">
         <is>
-          <t>牧德</t>
+          <t>柏騰</t>
         </is>
       </c>
       <c r="C148" s="2" t="n">
         <v/>
       </c>
       <c r="D148" s="2" t="n">
-        <v>413.935751136978</v>
+        <v>420.9055153341761</v>
       </c>
       <c r="E148" s="2" t="n">
-        <v>728</v>
+        <v>30.9</v>
       </c>
       <c r="F148" s="2" t="inlineStr">
         <is>
@@ -8290,13 +8290,13 @@
         <v>0</v>
       </c>
       <c r="H148" s="2" t="n">
-        <v>41.15219055659215</v>
+        <v>50.78900839820299</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>27.67761813068549</v>
+        <v>25.13950461218356</v>
       </c>
       <c r="J148" s="2" t="n">
-        <v>0.7041906533549622</v>
+        <v>1.271634037936032</v>
       </c>
       <c r="K148" s="2" t="n">
         <v>0</v>
@@ -8308,31 +8308,31 @@
         <v>-1</v>
       </c>
       <c r="N148" s="2" t="n">
-        <v>-3.859428125895171</v>
+        <v>-0.2528093365805167</v>
       </c>
       <c r="O148" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, stronger_than_market, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n">
-        <v>3266</v>
+        <v>3259</v>
       </c>
       <c r="B149" s="2" t="inlineStr">
         <is>
-          <t>昇陽</t>
+          <t>鑫創</t>
         </is>
       </c>
       <c r="C149" s="2" t="n">
         <v/>
       </c>
       <c r="D149" s="2" t="n">
-        <v>410.895267062777</v>
+        <v>418.376526288707</v>
       </c>
       <c r="E149" s="2" t="n">
-        <v>13.5</v>
+        <v>17.05</v>
       </c>
       <c r="F149" s="2" t="inlineStr">
         <is>
@@ -8343,13 +8343,13 @@
         <v>0</v>
       </c>
       <c r="H149" s="2" t="n">
-        <v>57.14061713542353</v>
+        <v>51.4629286245998</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>16.37406201732169</v>
+        <v>17.77304653627238</v>
       </c>
       <c r="J149" s="2" t="n">
-        <v>0.386816986981241</v>
+        <v>1.598990125007318</v>
       </c>
       <c r="K149" s="2" t="n">
         <v>1</v>
@@ -8361,31 +8361,31 @@
         <v>-1</v>
       </c>
       <c r="N149" s="2" t="n">
-        <v>0.1054929232879018</v>
+        <v>-0.0036031036055289</v>
       </c>
       <c r="O149" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, kd_golden_cross, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n">
-        <v>3169</v>
+        <v>3563</v>
       </c>
       <c r="B150" s="2" t="inlineStr">
         <is>
-          <t>亞信</t>
+          <t>牧德</t>
         </is>
       </c>
       <c r="C150" s="2" t="n">
         <v/>
       </c>
       <c r="D150" s="2" t="n">
-        <v>407.5564411437988</v>
+        <v>413.935751136978</v>
       </c>
       <c r="E150" s="2" t="n">
-        <v>113</v>
+        <v>728</v>
       </c>
       <c r="F150" s="2" t="inlineStr">
         <is>
@@ -8396,16 +8396,16 @@
         <v>0</v>
       </c>
       <c r="H150" s="2" t="n">
-        <v>52.64991619611048</v>
+        <v>41.15219055659215</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>19.94878441277049</v>
+        <v>27.67761813068549</v>
       </c>
       <c r="J150" s="2" t="n">
-        <v>0.7544747997797083</v>
+        <v>0.7041906533549622</v>
       </c>
       <c r="K150" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L150" s="2" t="n">
         <v>0</v>
@@ -8414,31 +8414,31 @@
         <v>-1</v>
       </c>
       <c r="N150" s="2" t="n">
-        <v>-0.5745310030018888</v>
+        <v>-3.859428125895171</v>
       </c>
       <c r="O150" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n">
-        <v>3207</v>
+        <v>3266</v>
       </c>
       <c r="B151" s="2" t="inlineStr">
         <is>
-          <t>耀勝</t>
+          <t>昇陽</t>
         </is>
       </c>
       <c r="C151" s="2" t="n">
         <v/>
       </c>
       <c r="D151" s="2" t="n">
-        <v>405.1658387928071</v>
+        <v>410.895267062777</v>
       </c>
       <c r="E151" s="2" t="n">
-        <v>67.3</v>
+        <v>13.5</v>
       </c>
       <c r="F151" s="2" t="inlineStr">
         <is>
@@ -8449,16 +8449,16 @@
         <v>0</v>
       </c>
       <c r="H151" s="2" t="n">
-        <v>53.97687417131505</v>
+        <v>57.14061713542353</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>21.35882615094375</v>
+        <v>16.37406201732169</v>
       </c>
       <c r="J151" s="2" t="n">
-        <v>0.8035255478931962</v>
+        <v>0.386816986981241</v>
       </c>
       <c r="K151" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L151" s="2" t="n">
         <v>0</v>
@@ -8467,31 +8467,31 @@
         <v>-1</v>
       </c>
       <c r="N151" s="2" t="n">
-        <v>0.0015464042792081</v>
+        <v>0.1054929232879018</v>
       </c>
       <c r="O151" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n">
-        <v>3712</v>
+        <v>3169</v>
       </c>
       <c r="B152" s="2" t="inlineStr">
         <is>
-          <t>永崴投控</t>
+          <t>亞信</t>
         </is>
       </c>
       <c r="C152" s="2" t="n">
         <v/>
       </c>
       <c r="D152" s="2" t="n">
-        <v>401.8504569590509</v>
+        <v>407.5564411437988</v>
       </c>
       <c r="E152" s="2" t="n">
-        <v>18.05</v>
+        <v>113</v>
       </c>
       <c r="F152" s="2" t="inlineStr">
         <is>
@@ -8502,16 +8502,16 @@
         <v>0</v>
       </c>
       <c r="H152" s="2" t="n">
-        <v>50.6474310023078</v>
+        <v>52.64991619611048</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>6.203867349283319</v>
+        <v>19.94878441277049</v>
       </c>
       <c r="J152" s="2" t="n">
-        <v>0.6198124177178126</v>
+        <v>0.7544747997797083</v>
       </c>
       <c r="K152" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L152" s="2" t="n">
         <v>0</v>
@@ -8520,31 +8520,31 @@
         <v>-1</v>
       </c>
       <c r="N152" s="2" t="n">
-        <v>0.0447449782901964</v>
+        <v>-0.5745310030018888</v>
       </c>
       <c r="O152" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n">
-        <v>4106</v>
+        <v>3207</v>
       </c>
       <c r="B153" s="2" t="inlineStr">
         <is>
-          <t>雃博</t>
+          <t>耀勝</t>
         </is>
       </c>
       <c r="C153" s="2" t="n">
         <v/>
       </c>
       <c r="D153" s="2" t="n">
-        <v>401.6388080911793</v>
+        <v>405.1658387928071</v>
       </c>
       <c r="E153" s="2" t="n">
-        <v>23.3</v>
+        <v>67.3</v>
       </c>
       <c r="F153" s="2" t="inlineStr">
         <is>
@@ -8555,13 +8555,13 @@
         <v>0</v>
       </c>
       <c r="H153" s="2" t="n">
-        <v>47.00305731333836</v>
+        <v>53.97687417131505</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>31.31110493991196</v>
+        <v>21.35882615094375</v>
       </c>
       <c r="J153" s="2" t="n">
-        <v>0.7309240828504644</v>
+        <v>0.8035255478931962</v>
       </c>
       <c r="K153" s="2" t="n">
         <v>0</v>
@@ -8573,31 +8573,31 @@
         <v>-1</v>
       </c>
       <c r="N153" s="2" t="n">
-        <v>-0.1178708290423445</v>
+        <v>0.0015464042792081</v>
       </c>
       <c r="O153" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n">
-        <v>3629</v>
+        <v>3712</v>
       </c>
       <c r="B154" s="2" t="inlineStr">
         <is>
-          <t>地心引力</t>
+          <t>永崴投控</t>
         </is>
       </c>
       <c r="C154" s="2" t="n">
         <v/>
       </c>
       <c r="D154" s="2" t="n">
-        <v>395.7780660347726</v>
+        <v>401.8504569590509</v>
       </c>
       <c r="E154" s="2" t="n">
-        <v>16.6</v>
+        <v>18.05</v>
       </c>
       <c r="F154" s="2" t="inlineStr">
         <is>
@@ -8608,16 +8608,16 @@
         <v>0</v>
       </c>
       <c r="H154" s="2" t="n">
-        <v>55.08016478659633</v>
+        <v>50.6474310023078</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>8.152311660142963</v>
+        <v>6.203867349283319</v>
       </c>
       <c r="J154" s="2" t="n">
-        <v>0.1487896957583833</v>
+        <v>0.6198124177178126</v>
       </c>
       <c r="K154" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L154" s="2" t="n">
         <v>0</v>
@@ -8626,31 +8626,31 @@
         <v>-1</v>
       </c>
       <c r="N154" s="2" t="n">
-        <v>1.421043008376735</v>
+        <v>0.0447449782901964</v>
       </c>
       <c r="O154" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, rsi_strong, market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, kd_golden_cross, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n">
-        <v>3432</v>
+        <v>4106</v>
       </c>
       <c r="B155" s="2" t="inlineStr">
         <is>
-          <t>台端</t>
+          <t>雃博</t>
         </is>
       </c>
       <c r="C155" s="2" t="n">
         <v/>
       </c>
       <c r="D155" s="2" t="n">
-        <v>392.8482887015857</v>
+        <v>401.6388080911793</v>
       </c>
       <c r="E155" s="2" t="n">
-        <v>18.95</v>
+        <v>23.3</v>
       </c>
       <c r="F155" s="2" t="inlineStr">
         <is>
@@ -8661,16 +8661,16 @@
         <v>0</v>
       </c>
       <c r="H155" s="2" t="n">
-        <v>51.71048992927787</v>
+        <v>47.00305731333836</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>15.73240416968428</v>
+        <v>31.31110493991196</v>
       </c>
       <c r="J155" s="2" t="n">
-        <v>0.8483808076049071</v>
+        <v>0.7309240828504644</v>
       </c>
       <c r="K155" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L155" s="2" t="n">
         <v>0</v>
@@ -8679,31 +8679,31 @@
         <v>-1</v>
       </c>
       <c r="N155" s="2" t="n">
-        <v>0.0122308445401474</v>
+        <v>-0.1178708290423445</v>
       </c>
       <c r="O155" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n">
-        <v>3416</v>
+        <v>3629</v>
       </c>
       <c r="B156" s="2" t="inlineStr">
         <is>
-          <t>融程電</t>
+          <t>地心引力</t>
         </is>
       </c>
       <c r="C156" s="2" t="n">
         <v/>
       </c>
       <c r="D156" s="2" t="n">
-        <v>389.8853604420775</v>
+        <v>395.7780660347726</v>
       </c>
       <c r="E156" s="2" t="n">
-        <v>177.5</v>
+        <v>16.6</v>
       </c>
       <c r="F156" s="2" t="inlineStr">
         <is>
@@ -8714,16 +8714,16 @@
         <v>0</v>
       </c>
       <c r="H156" s="2" t="n">
-        <v>53.79833129383218</v>
+        <v>55.08016478659633</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>16.62386739315426</v>
+        <v>8.152311660142963</v>
       </c>
       <c r="J156" s="2" t="n">
-        <v>0.4947509928245933</v>
+        <v>0.1487896957583833</v>
       </c>
       <c r="K156" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L156" s="2" t="n">
         <v>0</v>
@@ -8732,31 +8732,31 @@
         <v>-1</v>
       </c>
       <c r="N156" s="2" t="n">
-        <v>-1.016253969814936</v>
+        <v>1.421043008376735</v>
       </c>
       <c r="O156" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>above_ema60, rsi_strong, market_above_ma60, stronger_than_market, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n">
-        <v>3217</v>
+        <v>3432</v>
       </c>
       <c r="B157" s="2" t="inlineStr">
         <is>
-          <t>優群</t>
+          <t>台端</t>
         </is>
       </c>
       <c r="C157" s="2" t="n">
         <v/>
       </c>
       <c r="D157" s="2" t="n">
-        <v>386.0686139482075</v>
+        <v>392.8482887015857</v>
       </c>
       <c r="E157" s="2" t="n">
-        <v>176.5</v>
+        <v>18.95</v>
       </c>
       <c r="F157" s="2" t="inlineStr">
         <is>
@@ -8767,13 +8767,13 @@
         <v>0</v>
       </c>
       <c r="H157" s="2" t="n">
-        <v>47.89537419169122</v>
+        <v>51.71048992927787</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>22.49876516573422</v>
+        <v>15.73240416968428</v>
       </c>
       <c r="J157" s="2" t="n">
-        <v>0.8030780071179461</v>
+        <v>0.8483808076049071</v>
       </c>
       <c r="K157" s="2" t="n">
         <v>1</v>
@@ -8785,31 +8785,31 @@
         <v>-1</v>
       </c>
       <c r="N157" s="2" t="n">
-        <v>-1.7826635564385</v>
+        <v>0.0122308445401474</v>
       </c>
       <c r="O157" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
+          <t>macd_golden_cross, above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, hist_turn_positive</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n">
-        <v>3229</v>
+        <v>3416</v>
       </c>
       <c r="B158" s="2" t="inlineStr">
         <is>
-          <t>晟鈦</t>
+          <t>融程電</t>
         </is>
       </c>
       <c r="C158" s="2" t="n">
         <v/>
       </c>
       <c r="D158" s="2" t="n">
-        <v>383.442889465717</v>
+        <v>389.8853604420775</v>
       </c>
       <c r="E158" s="2" t="n">
-        <v>45</v>
+        <v>177.5</v>
       </c>
       <c r="F158" s="2" t="inlineStr">
         <is>
@@ -8820,16 +8820,16 @@
         <v>0</v>
       </c>
       <c r="H158" s="2" t="n">
-        <v>53.14283301592094</v>
+        <v>53.79833129383218</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>27.77152278720425</v>
+        <v>16.62386739315426</v>
       </c>
       <c r="J158" s="2" t="n">
-        <v>0.5632349427245639</v>
+        <v>0.4947509928245933</v>
       </c>
       <c r="K158" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L158" s="2" t="n">
         <v>0</v>
@@ -8838,31 +8838,31 @@
         <v>-1</v>
       </c>
       <c r="N158" s="2" t="n">
-        <v>-0.4442923927084181</v>
+        <v>-1.016253969814936</v>
       </c>
       <c r="O158" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n">
-        <v>3313</v>
+        <v>3217</v>
       </c>
       <c r="B159" s="2" t="inlineStr">
         <is>
-          <t>斐成</t>
+          <t>優群</t>
         </is>
       </c>
       <c r="C159" s="2" t="n">
         <v/>
       </c>
       <c r="D159" s="2" t="n">
-        <v>380.7761081037619</v>
+        <v>386.0686139482075</v>
       </c>
       <c r="E159" s="2" t="n">
-        <v>11.8</v>
+        <v>176.5</v>
       </c>
       <c r="F159" s="2" t="inlineStr">
         <is>
@@ -8873,16 +8873,16 @@
         <v>0</v>
       </c>
       <c r="H159" s="2" t="n">
-        <v>51.91837141607565</v>
+        <v>47.89537419169122</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>23.71704840162863</v>
+        <v>22.49876516573422</v>
       </c>
       <c r="J159" s="2" t="n">
-        <v>0.5753822052357835</v>
+        <v>0.8030780071179461</v>
       </c>
       <c r="K159" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L159" s="2" t="n">
         <v>0</v>
@@ -8891,31 +8891,31 @@
         <v>-1</v>
       </c>
       <c r="N159" s="2" t="n">
-        <v>0.0795643857721481</v>
+        <v>-1.7826635564385</v>
       </c>
       <c r="O159" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending, dealer_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n">
-        <v>3501</v>
+        <v>3229</v>
       </c>
       <c r="B160" s="2" t="inlineStr">
         <is>
-          <t>維熹</t>
+          <t>晟鈦</t>
         </is>
       </c>
       <c r="C160" s="2" t="n">
         <v/>
       </c>
       <c r="D160" s="2" t="n">
-        <v>378.1691424675556</v>
+        <v>383.442889465717</v>
       </c>
       <c r="E160" s="2" t="n">
-        <v>40.9</v>
+        <v>45</v>
       </c>
       <c r="F160" s="2" t="inlineStr">
         <is>
@@ -8926,16 +8926,16 @@
         <v>0</v>
       </c>
       <c r="H160" s="2" t="n">
-        <v>41.64169242356763</v>
+        <v>53.14283301592094</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>20.37341557528433</v>
+        <v>27.77152278720425</v>
       </c>
       <c r="J160" s="2" t="n">
-        <v>2.290216265941098</v>
+        <v>0.5632349427245639</v>
       </c>
       <c r="K160" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L160" s="2" t="n">
         <v>0</v>
@@ -8944,31 +8944,31 @@
         <v>-1</v>
       </c>
       <c r="N160" s="2" t="n">
-        <v>0.1772314984240773</v>
+        <v>-0.4442923927084181</v>
       </c>
       <c r="O160" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, adx_trending, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n">
-        <v>3419</v>
+        <v>3313</v>
       </c>
       <c r="B161" s="2" t="inlineStr">
         <is>
-          <t>譁裕</t>
+          <t>斐成</t>
         </is>
       </c>
       <c r="C161" s="2" t="n">
         <v/>
       </c>
       <c r="D161" s="2" t="n">
-        <v>377.6792348264257</v>
+        <v>380.7761081037619</v>
       </c>
       <c r="E161" s="2" t="n">
-        <v>14.3</v>
+        <v>11.8</v>
       </c>
       <c r="F161" s="2" t="inlineStr">
         <is>
@@ -8979,16 +8979,16 @@
         <v>0</v>
       </c>
       <c r="H161" s="2" t="n">
-        <v>50.16933181330603</v>
+        <v>51.91837141607565</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>14.27816221972504</v>
+        <v>23.71704840162863</v>
       </c>
       <c r="J161" s="2" t="n">
-        <v>1.187442087212995</v>
+        <v>0.5753822052357835</v>
       </c>
       <c r="K161" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L161" s="2" t="n">
         <v>0</v>
@@ -8997,31 +8997,31 @@
         <v>-1</v>
       </c>
       <c r="N161" s="2" t="n">
-        <v>0.079823131032266</v>
+        <v>0.0795643857721481</v>
       </c>
       <c r="O161" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n">
-        <v>3373</v>
+        <v>3501</v>
       </c>
       <c r="B162" s="2" t="inlineStr">
         <is>
-          <t>熱映</t>
+          <t>維熹</t>
         </is>
       </c>
       <c r="C162" s="2" t="n">
         <v/>
       </c>
       <c r="D162" s="2" t="n">
-        <v>373.6386553081506</v>
+        <v>378.1691424675556</v>
       </c>
       <c r="E162" s="2" t="n">
-        <v>16.75</v>
+        <v>40.9</v>
       </c>
       <c r="F162" s="2" t="inlineStr">
         <is>
@@ -9032,16 +9032,16 @@
         <v>0</v>
       </c>
       <c r="H162" s="2" t="n">
-        <v>46.4753503415263</v>
+        <v>41.64169242356763</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>28.85169771234908</v>
+        <v>20.37341557528433</v>
       </c>
       <c r="J162" s="2" t="n">
-        <v>1.538296082209028</v>
+        <v>2.290216265941098</v>
       </c>
       <c r="K162" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L162" s="2" t="n">
         <v>0</v>
@@ -9050,7 +9050,7 @@
         <v>-1</v>
       </c>
       <c r="N162" s="2" t="n">
-        <v>-0.0012479773436476</v>
+        <v>0.1772314984240773</v>
       </c>
       <c r="O162" s="2" t="inlineStr">
         <is>
@@ -9060,21 +9060,21 @@
     </row>
     <row r="163">
       <c r="A163" s="2" t="n">
-        <v>3521</v>
+        <v>3419</v>
       </c>
       <c r="B163" s="2" t="inlineStr">
         <is>
-          <t>鴻翊</t>
+          <t>譁裕</t>
         </is>
       </c>
       <c r="C163" s="2" t="n">
         <v/>
       </c>
       <c r="D163" s="2" t="n">
-        <v>369.3543381254113</v>
+        <v>377.6792348264257</v>
       </c>
       <c r="E163" s="2" t="n">
-        <v>12.25</v>
+        <v>14.3</v>
       </c>
       <c r="F163" s="2" t="inlineStr">
         <is>
@@ -9085,16 +9085,16 @@
         <v>0</v>
       </c>
       <c r="H163" s="2" t="n">
-        <v>40.20773104310064</v>
+        <v>50.16933181330603</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>20.01872254823133</v>
+        <v>14.27816221972504</v>
       </c>
       <c r="J163" s="2" t="n">
-        <v>0.5748859446920243</v>
+        <v>1.187442087212995</v>
       </c>
       <c r="K163" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L163" s="2" t="n">
         <v>0</v>
@@ -9103,31 +9103,31 @@
         <v>-1</v>
       </c>
       <c r="N163" s="2" t="n">
-        <v>0.055969041276716</v>
+        <v>0.079823131032266</v>
       </c>
       <c r="O163" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n">
-        <v>3555</v>
+        <v>3373</v>
       </c>
       <c r="B164" s="2" t="inlineStr">
         <is>
-          <t>博士旺</t>
+          <t>熱映</t>
         </is>
       </c>
       <c r="C164" s="2" t="n">
         <v/>
       </c>
       <c r="D164" s="2" t="n">
-        <v>366.3472842672787</v>
+        <v>373.6386553081506</v>
       </c>
       <c r="E164" s="2" t="n">
-        <v>202</v>
+        <v>16.75</v>
       </c>
       <c r="F164" s="2" t="inlineStr">
         <is>
@@ -9138,16 +9138,16 @@
         <v>0</v>
       </c>
       <c r="H164" s="2" t="n">
-        <v>46.5387755021487</v>
+        <v>46.4753503415263</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>14.24661734371623</v>
+        <v>28.85169771234908</v>
       </c>
       <c r="J164" s="2" t="n">
-        <v>0.2905462023412094</v>
+        <v>1.538296082209028</v>
       </c>
       <c r="K164" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L164" s="2" t="n">
         <v>0</v>
@@ -9156,31 +9156,31 @@
         <v>-1</v>
       </c>
       <c r="N164" s="2" t="n">
-        <v>-1.106138771144852</v>
+        <v>-0.0012479773436476</v>
       </c>
       <c r="O164" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n">
-        <v>3380</v>
+        <v>3521</v>
       </c>
       <c r="B165" s="2" t="inlineStr">
         <is>
-          <t>明泰</t>
+          <t>鴻翊</t>
         </is>
       </c>
       <c r="C165" s="2" t="n">
         <v/>
       </c>
       <c r="D165" s="2" t="n">
-        <v>361.9973403891273</v>
+        <v>369.3543381254113</v>
       </c>
       <c r="E165" s="2" t="n">
-        <v>35.8</v>
+        <v>12.25</v>
       </c>
       <c r="F165" s="2" t="inlineStr">
         <is>
@@ -9191,16 +9191,16 @@
         <v>0</v>
       </c>
       <c r="H165" s="2" t="n">
-        <v>51.92967849293954</v>
+        <v>40.20773104310064</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>16.19569749871696</v>
+        <v>20.01872254823133</v>
       </c>
       <c r="J165" s="2" t="n">
-        <v>0.7635921882424906</v>
+        <v>0.5748859446920243</v>
       </c>
       <c r="K165" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L165" s="2" t="n">
         <v>0</v>
@@ -9209,31 +9209,31 @@
         <v>-1</v>
       </c>
       <c r="N165" s="2" t="n">
-        <v>-0.1241873425932556</v>
+        <v>0.055969041276716</v>
       </c>
       <c r="O165" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n">
-        <v>3164</v>
+        <v>3555</v>
       </c>
       <c r="B166" s="2" t="inlineStr">
         <is>
-          <t>景岳</t>
+          <t>博士旺</t>
         </is>
       </c>
       <c r="C166" s="2" t="n">
         <v/>
       </c>
       <c r="D166" s="2" t="n">
-        <v>361.607380462866</v>
+        <v>366.3472842672787</v>
       </c>
       <c r="E166" s="2" t="n">
-        <v>16.3</v>
+        <v>202</v>
       </c>
       <c r="F166" s="2" t="inlineStr">
         <is>
@@ -9244,13 +9244,13 @@
         <v>0</v>
       </c>
       <c r="H166" s="2" t="n">
-        <v>36.99205871273872</v>
+        <v>46.5387755021487</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>28.5050047972829</v>
+        <v>14.24661734371623</v>
       </c>
       <c r="J166" s="2" t="n">
-        <v>1.019919649790619</v>
+        <v>0.2905462023412094</v>
       </c>
       <c r="K166" s="2" t="n">
         <v>1</v>
@@ -9262,31 +9262,31 @@
         <v>-1</v>
       </c>
       <c r="N166" s="2" t="n">
-        <v>0.0426158187786881</v>
+        <v>-1.106138771144852</v>
       </c>
       <c r="O166" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n">
-        <v>3672</v>
+        <v>3380</v>
       </c>
       <c r="B167" s="2" t="inlineStr">
         <is>
-          <t>康聯訊</t>
+          <t>明泰</t>
         </is>
       </c>
       <c r="C167" s="2" t="n">
         <v/>
       </c>
       <c r="D167" s="2" t="n">
-        <v>358.9345082784151</v>
+        <v>361.9973403891273</v>
       </c>
       <c r="E167" s="2" t="n">
-        <v>11.9</v>
+        <v>35.8</v>
       </c>
       <c r="F167" s="2" t="inlineStr">
         <is>
@@ -9297,16 +9297,16 @@
         <v>0</v>
       </c>
       <c r="H167" s="2" t="n">
-        <v>54.01343762179948</v>
+        <v>51.92967849293954</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>16.61476698632166</v>
+        <v>16.19569749871696</v>
       </c>
       <c r="J167" s="2" t="n">
-        <v>0.8242220995720188</v>
+        <v>0.7635921882424906</v>
       </c>
       <c r="K167" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L167" s="2" t="n">
         <v>0</v>
@@ -9315,31 +9315,31 @@
         <v>-1</v>
       </c>
       <c r="N167" s="2" t="n">
-        <v>0.0742356030193628</v>
+        <v>-0.1241873425932556</v>
       </c>
       <c r="O167" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n">
-        <v>3693</v>
+        <v>3164</v>
       </c>
       <c r="B168" s="2" t="inlineStr">
         <is>
-          <t>營邦</t>
+          <t>景岳</t>
         </is>
       </c>
       <c r="C168" s="2" t="n">
         <v/>
       </c>
       <c r="D168" s="2" t="n">
-        <v>358.5252143436605</v>
+        <v>361.607380462866</v>
       </c>
       <c r="E168" s="2" t="n">
-        <v>513</v>
+        <v>16.3</v>
       </c>
       <c r="F168" s="2" t="inlineStr">
         <is>
@@ -9350,16 +9350,16 @@
         <v>0</v>
       </c>
       <c r="H168" s="2" t="n">
-        <v>42.88869061580685</v>
+        <v>36.99205871273872</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>15.59883583721342</v>
+        <v>28.5050047972829</v>
       </c>
       <c r="J168" s="2" t="n">
-        <v>0.5131208068135502</v>
+        <v>1.019919649790619</v>
       </c>
       <c r="K168" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L168" s="2" t="n">
         <v>0</v>
@@ -9368,31 +9368,31 @@
         <v>-1</v>
       </c>
       <c r="N168" s="2" t="n">
-        <v>-4.409779927712712</v>
+        <v>0.0426158187786881</v>
       </c>
       <c r="O168" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, kd_golden_cross, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="n">
-        <v>3661</v>
+        <v>3672</v>
       </c>
       <c r="B169" s="2" t="inlineStr">
         <is>
-          <t>世芯-KY</t>
+          <t>康聯訊</t>
         </is>
       </c>
       <c r="C169" s="2" t="n">
         <v/>
       </c>
       <c r="D169" s="2" t="n">
-        <v>356.5781533465166</v>
+        <v>358.9345082784151</v>
       </c>
       <c r="E169" s="2" t="n">
-        <v>4325</v>
+        <v>11.9</v>
       </c>
       <c r="F169" s="2" t="inlineStr">
         <is>
@@ -9403,49 +9403,49 @@
         <v>0</v>
       </c>
       <c r="H169" s="2" t="n">
-        <v>49.64382102535584</v>
+        <v>54.01343762179948</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>15.81520570626223</v>
+        <v>16.61476698632166</v>
       </c>
       <c r="J169" s="2" t="n">
-        <v>1.32160270510814</v>
+        <v>0.8242220995720188</v>
       </c>
       <c r="K169" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L169" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M169" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N169" s="2" t="n">
-        <v>-15.87559283786412</v>
+        <v>0.0742356030193628</v>
       </c>
       <c r="O169" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n">
-        <v>3543</v>
+        <v>3693</v>
       </c>
       <c r="B170" s="2" t="inlineStr">
         <is>
-          <t>州巧</t>
+          <t>營邦</t>
         </is>
       </c>
       <c r="C170" s="2" t="n">
         <v/>
       </c>
       <c r="D170" s="2" t="n">
-        <v>355.4028816753766</v>
+        <v>358.5252143436605</v>
       </c>
       <c r="E170" s="2" t="n">
-        <v>30.95</v>
+        <v>513</v>
       </c>
       <c r="F170" s="2" t="inlineStr">
         <is>
@@ -9456,16 +9456,16 @@
         <v>0</v>
       </c>
       <c r="H170" s="2" t="n">
-        <v>27.84418988634521</v>
+        <v>42.88869061580685</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>25.83520011258137</v>
+        <v>15.59883583721342</v>
       </c>
       <c r="J170" s="2" t="n">
-        <v>0.7928284770770987</v>
+        <v>0.5131208068135502</v>
       </c>
       <c r="K170" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L170" s="2" t="n">
         <v>0</v>
@@ -9474,31 +9474,31 @@
         <v>-1</v>
       </c>
       <c r="N170" s="2" t="n">
-        <v>-0.0890117302123196</v>
+        <v>-4.409779927712712</v>
       </c>
       <c r="O170" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n">
-        <v>3552</v>
+        <v>3661</v>
       </c>
       <c r="B171" s="2" t="inlineStr">
         <is>
-          <t>同致</t>
+          <t>世芯-KY</t>
         </is>
       </c>
       <c r="C171" s="2" t="n">
         <v/>
       </c>
       <c r="D171" s="2" t="n">
-        <v>354.0529810989802</v>
+        <v>356.5781533465166</v>
       </c>
       <c r="E171" s="2" t="n">
-        <v>51.8</v>
+        <v>4325</v>
       </c>
       <c r="F171" s="2" t="inlineStr">
         <is>
@@ -9509,49 +9509,49 @@
         <v>0</v>
       </c>
       <c r="H171" s="2" t="n">
-        <v>48.97050201564745</v>
+        <v>49.64382102535584</v>
       </c>
       <c r="I171" s="2" t="n">
-        <v>14.48808834995088</v>
+        <v>15.81520570626223</v>
       </c>
       <c r="J171" s="2" t="n">
-        <v>0.7085078073920895</v>
+        <v>1.32160270510814</v>
       </c>
       <c r="K171" s="2" t="n">
         <v>0</v>
       </c>
       <c r="L171" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M171" s="2" t="n">
         <v>-1</v>
       </c>
       <c r="N171" s="2" t="n">
-        <v>0.0665152716827257</v>
+        <v>-15.87559283786412</v>
       </c>
       <c r="O171" s="2" t="inlineStr">
         <is>
-          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n">
-        <v>3492</v>
+        <v>3543</v>
       </c>
       <c r="B172" s="2" t="inlineStr">
         <is>
-          <t>長盛</t>
+          <t>州巧</t>
         </is>
       </c>
       <c r="C172" s="2" t="n">
         <v/>
       </c>
       <c r="D172" s="2" t="n">
-        <v>339.1963046625691</v>
+        <v>355.4028816753766</v>
       </c>
       <c r="E172" s="2" t="n">
-        <v>22.9</v>
+        <v>30.95</v>
       </c>
       <c r="F172" s="2" t="inlineStr">
         <is>
@@ -9562,16 +9562,16 @@
         <v>0</v>
       </c>
       <c r="H172" s="2" t="n">
-        <v>51.56562601273554</v>
+        <v>27.84418988634521</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>12.72046628067763</v>
+        <v>25.83520011258137</v>
       </c>
       <c r="J172" s="2" t="n">
-        <v>0.6710299936713066</v>
+        <v>0.7928284770770987</v>
       </c>
       <c r="K172" s="2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L172" s="2" t="n">
         <v>0</v>
@@ -9580,31 +9580,31 @@
         <v>-1</v>
       </c>
       <c r="N172" s="2" t="n">
-        <v>0.0318053911354158</v>
+        <v>-0.0890117302123196</v>
       </c>
       <c r="O172" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n">
-        <v>3645</v>
+        <v>3552</v>
       </c>
       <c r="B173" s="2" t="inlineStr">
         <is>
-          <t>達邁</t>
+          <t>同致</t>
         </is>
       </c>
       <c r="C173" s="2" t="n">
         <v/>
       </c>
       <c r="D173" s="2" t="n">
-        <v>338.6091177562424</v>
+        <v>354.0529810989802</v>
       </c>
       <c r="E173" s="2" t="n">
-        <v>96.09999999999999</v>
+        <v>51.8</v>
       </c>
       <c r="F173" s="2" t="inlineStr">
         <is>
@@ -9615,16 +9615,16 @@
         <v>0</v>
       </c>
       <c r="H173" s="2" t="n">
-        <v>47.26424428426737</v>
+        <v>48.97050201564745</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>16.11092444165972</v>
+        <v>14.48808834995088</v>
       </c>
       <c r="J173" s="2" t="n">
-        <v>0.407686415873054</v>
+        <v>0.7085078073920895</v>
       </c>
       <c r="K173" s="2" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L173" s="2" t="n">
         <v>0</v>
@@ -9633,31 +9633,31 @@
         <v>-1</v>
       </c>
       <c r="N173" s="2" t="n">
-        <v>-0.7015600536629738</v>
+        <v>0.0665152716827257</v>
       </c>
       <c r="O173" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d</t>
+          <t>macd_golden_cross, market_above_ma60, avoid_chase, hist_turn_positive, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n">
-        <v>3709</v>
+        <v>3492</v>
       </c>
       <c r="B174" s="2" t="inlineStr">
         <is>
-          <t>鑫聯大投控</t>
+          <t>長盛</t>
         </is>
       </c>
       <c r="C174" s="2" t="n">
         <v/>
       </c>
       <c r="D174" s="2" t="n">
-        <v>331.5151502022911</v>
+        <v>339.1963046625691</v>
       </c>
       <c r="E174" s="2" t="n">
-        <v>74.59999999999999</v>
+        <v>22.9</v>
       </c>
       <c r="F174" s="2" t="inlineStr">
         <is>
@@ -9668,16 +9668,16 @@
         <v>0</v>
       </c>
       <c r="H174" s="2" t="n">
-        <v>39.44036754534594</v>
+        <v>51.56562601273554</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>29.55752214006882</v>
+        <v>12.72046628067763</v>
       </c>
       <c r="J174" s="2" t="n">
-        <v>0.3473000351711972</v>
+        <v>0.6710299936713066</v>
       </c>
       <c r="K174" s="2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="L174" s="2" t="n">
         <v>0</v>
@@ -9686,31 +9686,31 @@
         <v>-1</v>
       </c>
       <c r="N174" s="2" t="n">
-        <v>-1.04837579933668</v>
+        <v>0.0318053911354158</v>
       </c>
       <c r="O174" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n">
-        <v>3376</v>
+        <v>3645</v>
       </c>
       <c r="B175" s="2" t="inlineStr">
         <is>
-          <t>新日興</t>
+          <t>達邁</t>
         </is>
       </c>
       <c r="C175" s="2" t="n">
         <v/>
       </c>
       <c r="D175" s="2" t="n">
-        <v>330.4841170340927</v>
+        <v>338.6091177562424</v>
       </c>
       <c r="E175" s="2" t="n">
-        <v>209</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="F175" s="2" t="inlineStr">
         <is>
@@ -9721,16 +9721,16 @@
         <v>0</v>
       </c>
       <c r="H175" s="2" t="n">
-        <v>49.46893868924995</v>
+        <v>47.26424428426737</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>17.74793642325059</v>
+        <v>16.11092444165972</v>
       </c>
       <c r="J175" s="2" t="n">
-        <v>0.4815058938766778</v>
+        <v>0.407686415873054</v>
       </c>
       <c r="K175" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L175" s="2" t="n">
         <v>0</v>
@@ -9739,31 +9739,31 @@
         <v>-1</v>
       </c>
       <c r="N175" s="2" t="n">
-        <v>-1.894602908561085</v>
+        <v>-0.7015600536629738</v>
       </c>
       <c r="O175" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, liquidity_ok, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n">
-        <v>4119</v>
+        <v>3709</v>
       </c>
       <c r="B176" s="2" t="inlineStr">
         <is>
-          <t>旭富</t>
+          <t>鑫聯大投控</t>
         </is>
       </c>
       <c r="C176" s="2" t="n">
         <v/>
       </c>
       <c r="D176" s="2" t="n">
-        <v>328.1160198886919</v>
+        <v>331.5151502022911</v>
       </c>
       <c r="E176" s="2" t="n">
-        <v>42.8</v>
+        <v>74.59999999999999</v>
       </c>
       <c r="F176" s="2" t="inlineStr">
         <is>
@@ -9774,13 +9774,13 @@
         <v>0</v>
       </c>
       <c r="H176" s="2" t="n">
-        <v>49.58735331073623</v>
+        <v>39.44036754534594</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>21.09904369673718</v>
+        <v>29.55752214006882</v>
       </c>
       <c r="J176" s="2" t="n">
-        <v>0.9023535631622236</v>
+        <v>0.3473000351711972</v>
       </c>
       <c r="K176" s="2" t="n">
         <v>0</v>
@@ -9792,31 +9792,31 @@
         <v>-1</v>
       </c>
       <c r="N176" s="2" t="n">
-        <v>0.4436359524529758</v>
+        <v>-1.04837579933668</v>
       </c>
       <c r="O176" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n">
-        <v>3325</v>
+        <v>3376</v>
       </c>
       <c r="B177" s="2" t="inlineStr">
         <is>
-          <t>旭品</t>
+          <t>新日興</t>
         </is>
       </c>
       <c r="C177" s="2" t="n">
         <v/>
       </c>
       <c r="D177" s="2" t="n">
-        <v>328.0111191521602</v>
+        <v>330.4841170340927</v>
       </c>
       <c r="E177" s="2" t="n">
-        <v>12.7</v>
+        <v>209</v>
       </c>
       <c r="F177" s="2" t="inlineStr">
         <is>
@@ -9827,16 +9827,16 @@
         <v>0</v>
       </c>
       <c r="H177" s="2" t="n">
-        <v>50.2802694196654</v>
+        <v>49.46893868924995</v>
       </c>
       <c r="I177" s="2" t="n">
-        <v>15.55744760715258</v>
+        <v>17.74793642325059</v>
       </c>
       <c r="J177" s="2" t="n">
-        <v>0.4183066648985867</v>
+        <v>0.4815058938766778</v>
       </c>
       <c r="K177" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L177" s="2" t="n">
         <v>0</v>
@@ -9845,31 +9845,31 @@
         <v>-1</v>
       </c>
       <c r="N177" s="2" t="n">
-        <v>-0.0241686344650845</v>
+        <v>-1.894602908561085</v>
       </c>
       <c r="O177" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, dealer_buy_3d, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n">
-        <v>3515</v>
+        <v>4119</v>
       </c>
       <c r="B178" s="2" t="inlineStr">
         <is>
-          <t>華擎</t>
+          <t>旭富</t>
         </is>
       </c>
       <c r="C178" s="2" t="n">
         <v/>
       </c>
       <c r="D178" s="2" t="n">
-        <v>325.1616289519483</v>
+        <v>328.1160198886919</v>
       </c>
       <c r="E178" s="2" t="n">
-        <v>246</v>
+        <v>42.8</v>
       </c>
       <c r="F178" s="2" t="inlineStr">
         <is>
@@ -9880,16 +9880,16 @@
         <v>0</v>
       </c>
       <c r="H178" s="2" t="n">
-        <v>52.36056432970958</v>
+        <v>49.58735331073623</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>15.39880118468069</v>
+        <v>21.09904369673718</v>
       </c>
       <c r="J178" s="2" t="n">
-        <v>0.5562727596157154</v>
+        <v>0.9023535631622236</v>
       </c>
       <c r="K178" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L178" s="2" t="n">
         <v>0</v>
@@ -9898,31 +9898,31 @@
         <v>-1</v>
       </c>
       <c r="N178" s="2" t="n">
-        <v>-1.010702092293894</v>
+        <v>0.4436359524529758</v>
       </c>
       <c r="O178" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n">
-        <v>3138</v>
+        <v>3325</v>
       </c>
       <c r="B179" s="2" t="inlineStr">
         <is>
-          <t>耀登</t>
+          <t>旭品</t>
         </is>
       </c>
       <c r="C179" s="2" t="n">
         <v/>
       </c>
       <c r="D179" s="2" t="n">
-        <v>325.0002407036279</v>
+        <v>328.0111191521602</v>
       </c>
       <c r="E179" s="2" t="n">
-        <v>138</v>
+        <v>12.7</v>
       </c>
       <c r="F179" s="2" t="inlineStr">
         <is>
@@ -9933,16 +9933,16 @@
         <v>0</v>
       </c>
       <c r="H179" s="2" t="n">
-        <v>34.90466704980545</v>
+        <v>50.2802694196654</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>24.22691881718027</v>
+        <v>15.55744760715258</v>
       </c>
       <c r="J179" s="2" t="n">
-        <v>0.5814828807107465</v>
+        <v>0.4183066648985867</v>
       </c>
       <c r="K179" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="L179" s="2" t="n">
         <v>0</v>
@@ -9951,31 +9951,31 @@
         <v>-1</v>
       </c>
       <c r="N179" s="2" t="n">
-        <v>-1.875194833715553</v>
+        <v>-0.0241686344650845</v>
       </c>
       <c r="O179" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, foreign_buy_3d, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n">
-        <v>3323</v>
+        <v>3515</v>
       </c>
       <c r="B180" s="2" t="inlineStr">
         <is>
-          <t>加百裕</t>
+          <t>華擎</t>
         </is>
       </c>
       <c r="C180" s="2" t="n">
         <v/>
       </c>
       <c r="D180" s="2" t="n">
-        <v>313.2325048994726</v>
+        <v>325.1616289519483</v>
       </c>
       <c r="E180" s="2" t="n">
-        <v>36</v>
+        <v>246</v>
       </c>
       <c r="F180" s="2" t="inlineStr">
         <is>
@@ -9986,13 +9986,13 @@
         <v>0</v>
       </c>
       <c r="H180" s="2" t="n">
-        <v>50.4687223957513</v>
+        <v>52.36056432970958</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>19.04259769826005</v>
+        <v>15.39880118468069</v>
       </c>
       <c r="J180" s="2" t="n">
-        <v>0.3395729942222509</v>
+        <v>0.5562727596157154</v>
       </c>
       <c r="K180" s="2" t="n">
         <v>1</v>
@@ -10004,31 +10004,31 @@
         <v>-1</v>
       </c>
       <c r="N180" s="2" t="n">
-        <v>-0.2031882769409243</v>
+        <v>-1.010702092293894</v>
       </c>
       <c r="O180" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="n">
-        <v>3512</v>
+        <v>3138</v>
       </c>
       <c r="B181" s="2" t="inlineStr">
         <is>
-          <t>皇龍</t>
+          <t>耀登</t>
         </is>
       </c>
       <c r="C181" s="2" t="n">
         <v/>
       </c>
       <c r="D181" s="2" t="n">
-        <v>310.4026477287934</v>
+        <v>325.0002407036279</v>
       </c>
       <c r="E181" s="2" t="n">
-        <v>20.65</v>
+        <v>138</v>
       </c>
       <c r="F181" s="2" t="inlineStr">
         <is>
@@ -10039,16 +10039,16 @@
         <v>0</v>
       </c>
       <c r="H181" s="2" t="n">
-        <v>48.34216903404833</v>
+        <v>34.90466704980545</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>31.20578420514097</v>
+        <v>24.22691881718027</v>
       </c>
       <c r="J181" s="2" t="n">
-        <v>2.355708633554188</v>
+        <v>0.5814828807107465</v>
       </c>
       <c r="K181" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L181" s="2" t="n">
         <v>0</v>
@@ -10057,31 +10057,31 @@
         <v>-1</v>
       </c>
       <c r="N181" s="2" t="n">
-        <v>0.0305801707454973</v>
+        <v>-1.875194833715553</v>
       </c>
       <c r="O181" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="n">
-        <v>4142</v>
+        <v>3323</v>
       </c>
       <c r="B182" s="2" t="inlineStr">
         <is>
-          <t>國光生</t>
+          <t>加百裕</t>
         </is>
       </c>
       <c r="C182" s="2" t="n">
         <v/>
       </c>
       <c r="D182" s="2" t="n">
-        <v>307.3137989593369</v>
+        <v>313.2325048994726</v>
       </c>
       <c r="E182" s="2" t="n">
-        <v>17.2</v>
+        <v>36</v>
       </c>
       <c r="F182" s="2" t="inlineStr">
         <is>
@@ -10092,16 +10092,16 @@
         <v>0</v>
       </c>
       <c r="H182" s="2" t="n">
-        <v>41.4325429025569</v>
+        <v>50.4687223957513</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>8.627578585811337</v>
+        <v>19.04259769826005</v>
       </c>
       <c r="J182" s="2" t="n">
-        <v>1.111945279396683</v>
+        <v>0.3395729942222509</v>
       </c>
       <c r="K182" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L182" s="2" t="n">
         <v>0</v>
@@ -10110,31 +10110,31 @@
         <v>-1</v>
       </c>
       <c r="N182" s="2" t="n">
-        <v>-0.0063382101475981</v>
+        <v>-0.2031882769409243</v>
       </c>
       <c r="O182" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, liquidity_ok, mfi_strong, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="n">
-        <v>3447</v>
+        <v>3512</v>
       </c>
       <c r="B183" s="2" t="inlineStr">
         <is>
-          <t>展達</t>
+          <t>皇龍</t>
         </is>
       </c>
       <c r="C183" s="2" t="n">
         <v/>
       </c>
       <c r="D183" s="2" t="n">
-        <v>293.3105985571208</v>
+        <v>310.4026477287934</v>
       </c>
       <c r="E183" s="2" t="n">
-        <v>39.4</v>
+        <v>20.65</v>
       </c>
       <c r="F183" s="2" t="inlineStr">
         <is>
@@ -10145,16 +10145,16 @@
         <v>0</v>
       </c>
       <c r="H183" s="2" t="n">
-        <v>50.8774348419601</v>
+        <v>48.34216903404833</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>18.57422501193964</v>
+        <v>31.20578420514097</v>
       </c>
       <c r="J183" s="2" t="n">
-        <v>0.3931389664489633</v>
+        <v>2.355708633554188</v>
       </c>
       <c r="K183" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L183" s="2" t="n">
         <v>0</v>
@@ -10163,31 +10163,31 @@
         <v>-1</v>
       </c>
       <c r="N183" s="2" t="n">
-        <v>-0.0123492481539977</v>
+        <v>0.0305801707454973</v>
       </c>
       <c r="O183" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="n">
-        <v>4104</v>
+        <v>4142</v>
       </c>
       <c r="B184" s="2" t="inlineStr">
         <is>
-          <t>佳醫</t>
+          <t>國光生</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
         <v/>
       </c>
       <c r="D184" s="2" t="n">
-        <v>291.4954816296328</v>
+        <v>307.3137989593369</v>
       </c>
       <c r="E184" s="2" t="n">
-        <v>68.8</v>
+        <v>17.2</v>
       </c>
       <c r="F184" s="2" t="inlineStr">
         <is>
@@ -10198,13 +10198,13 @@
         <v>0</v>
       </c>
       <c r="H184" s="2" t="n">
-        <v>34.16771204081418</v>
+        <v>41.4325429025569</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>21.99659569220935</v>
+        <v>8.627578585811337</v>
       </c>
       <c r="J184" s="2" t="n">
-        <v>1.505416103350449</v>
+        <v>1.111945279396683</v>
       </c>
       <c r="K184" s="2" t="n">
         <v>0</v>
@@ -10216,31 +10216,31 @@
         <v>-1</v>
       </c>
       <c r="N184" s="2" t="n">
-        <v>-0.0122604941540742</v>
+        <v>-0.0063382101475981</v>
       </c>
       <c r="O184" s="2" t="inlineStr">
         <is>
-          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="n">
-        <v>4108</v>
+        <v>3447</v>
       </c>
       <c r="B185" s="2" t="inlineStr">
         <is>
-          <t>懷特</t>
+          <t>展達</t>
         </is>
       </c>
       <c r="C185" s="2" t="n">
         <v/>
       </c>
       <c r="D185" s="2" t="n">
-        <v>288.629222688266</v>
+        <v>293.3105985571208</v>
       </c>
       <c r="E185" s="2" t="n">
-        <v>12.15</v>
+        <v>39.4</v>
       </c>
       <c r="F185" s="2" t="inlineStr">
         <is>
@@ -10251,13 +10251,13 @@
         <v>0</v>
       </c>
       <c r="H185" s="2" t="n">
-        <v>48.06086517741527</v>
+        <v>50.8774348419601</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>22.62353867374173</v>
+        <v>18.57422501193964</v>
       </c>
       <c r="J185" s="2" t="n">
-        <v>0.7777088692762549</v>
+        <v>0.3931389664489633</v>
       </c>
       <c r="K185" s="2" t="n">
         <v>0</v>
@@ -10269,31 +10269,31 @@
         <v>-1</v>
       </c>
       <c r="N185" s="2" t="n">
-        <v>-0.0243833074697221</v>
+        <v>-0.0123492481539977</v>
       </c>
       <c r="O185" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="n">
-        <v>3646</v>
+        <v>4104</v>
       </c>
       <c r="B186" s="2" t="inlineStr">
         <is>
-          <t>艾恩特</t>
+          <t>佳醫</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
         <v/>
       </c>
       <c r="D186" s="2" t="n">
-        <v>285.0109122268509</v>
+        <v>291.4954816296328</v>
       </c>
       <c r="E186" s="2" t="n">
-        <v>23.35</v>
+        <v>68.8</v>
       </c>
       <c r="F186" s="2" t="inlineStr">
         <is>
@@ -10304,13 +10304,13 @@
         <v>0</v>
       </c>
       <c r="H186" s="2" t="n">
-        <v>49.84438862984464</v>
+        <v>34.16771204081418</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>14.37775317657027</v>
+        <v>21.99659569220935</v>
       </c>
       <c r="J186" s="2" t="n">
-        <v>0.4147454667472429</v>
+        <v>1.505416103350449</v>
       </c>
       <c r="K186" s="2" t="n">
         <v>0</v>
@@ -10322,31 +10322,31 @@
         <v>-1</v>
       </c>
       <c r="N186" s="2" t="n">
-        <v>-0.09186041802000119</v>
+        <v>-0.0122604941540742</v>
       </c>
       <c r="O186" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>volume_break, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="n">
-        <v>3191</v>
+        <v>4108</v>
       </c>
       <c r="B187" s="2" t="inlineStr">
         <is>
-          <t>雲嘉南</t>
+          <t>懷特</t>
         </is>
       </c>
       <c r="C187" s="2" t="n">
         <v/>
       </c>
       <c r="D187" s="2" t="n">
-        <v>283.9214632598855</v>
+        <v>288.629222688266</v>
       </c>
       <c r="E187" s="2" t="n">
-        <v>19.95</v>
+        <v>12.15</v>
       </c>
       <c r="F187" s="2" t="inlineStr">
         <is>
@@ -10357,13 +10357,13 @@
         <v>0</v>
       </c>
       <c r="H187" s="2" t="n">
-        <v>54.52084499047844</v>
+        <v>48.06086517741527</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>14.23308611106397</v>
+        <v>22.62353867374173</v>
       </c>
       <c r="J187" s="2" t="n">
-        <v>0.4832906122083221</v>
+        <v>0.7777088692762549</v>
       </c>
       <c r="K187" s="2" t="n">
         <v>0</v>
@@ -10375,31 +10375,31 @@
         <v>-1</v>
       </c>
       <c r="N187" s="2" t="n">
-        <v>-0.4136783678188478</v>
+        <v>-0.0243833074697221</v>
       </c>
       <c r="O187" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="n">
-        <v>3684</v>
+        <v>3646</v>
       </c>
       <c r="B188" s="2" t="inlineStr">
         <is>
-          <t>榮昌</t>
+          <t>艾恩特</t>
         </is>
       </c>
       <c r="C188" s="2" t="n">
         <v/>
       </c>
       <c r="D188" s="2" t="n">
-        <v>282.7928802540219</v>
+        <v>285.0109122268509</v>
       </c>
       <c r="E188" s="2" t="n">
-        <v>59.8</v>
+        <v>23.35</v>
       </c>
       <c r="F188" s="2" t="inlineStr">
         <is>
@@ -10410,16 +10410,16 @@
         <v>0</v>
       </c>
       <c r="H188" s="2" t="n">
-        <v>50.19292743595334</v>
+        <v>49.84438862984464</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>11.71641311644088</v>
+        <v>14.37775317657027</v>
       </c>
       <c r="J188" s="2" t="n">
-        <v>0.6936584799159828</v>
+        <v>0.4147454667472429</v>
       </c>
       <c r="K188" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L188" s="2" t="n">
         <v>0</v>
@@ -10428,31 +10428,31 @@
         <v>-1</v>
       </c>
       <c r="N188" s="2" t="n">
-        <v>-0.0976280706816534</v>
+        <v>-0.09186041802000119</v>
       </c>
       <c r="O188" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="n">
-        <v>3224</v>
+        <v>3191</v>
       </c>
       <c r="B189" s="2" t="inlineStr">
         <is>
-          <t>三顧</t>
+          <t>雲嘉南</t>
         </is>
       </c>
       <c r="C189" s="2" t="n">
         <v/>
       </c>
       <c r="D189" s="2" t="n">
-        <v>280.6561069827913</v>
+        <v>283.9214632598855</v>
       </c>
       <c r="E189" s="2" t="n">
-        <v>38.8</v>
+        <v>19.95</v>
       </c>
       <c r="F189" s="2" t="inlineStr">
         <is>
@@ -10463,16 +10463,16 @@
         <v>0</v>
       </c>
       <c r="H189" s="2" t="n">
-        <v>46.57393255017862</v>
+        <v>54.52084499047844</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>18.46837286975088</v>
+        <v>14.23308611106397</v>
       </c>
       <c r="J189" s="2" t="n">
-        <v>1.018028609828388</v>
+        <v>0.4832906122083221</v>
       </c>
       <c r="K189" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L189" s="2" t="n">
         <v>0</v>
@@ -10481,31 +10481,31 @@
         <v>-1</v>
       </c>
       <c r="N189" s="2" t="n">
-        <v>0.2580450131449521</v>
+        <v>-0.4136783678188478</v>
       </c>
       <c r="O189" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="n">
-        <v>4178</v>
+        <v>3684</v>
       </c>
       <c r="B190" s="2" t="inlineStr">
         <is>
-          <t>永笙-KY</t>
+          <t>榮昌</t>
         </is>
       </c>
       <c r="C190" s="2" t="n">
         <v/>
       </c>
       <c r="D190" s="2" t="n">
-        <v>279.059657663656</v>
+        <v>282.7928802540219</v>
       </c>
       <c r="E190" s="2" t="n">
-        <v>17.2</v>
+        <v>59.8</v>
       </c>
       <c r="F190" s="2" t="inlineStr">
         <is>
@@ -10516,16 +10516,16 @@
         <v>0</v>
       </c>
       <c r="H190" s="2" t="n">
-        <v>23.39492886290931</v>
+        <v>50.19292743595334</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>58.46339584482742</v>
+        <v>11.71641311644088</v>
       </c>
       <c r="J190" s="2" t="n">
-        <v>1.152793231499703</v>
+        <v>0.6936584799159828</v>
       </c>
       <c r="K190" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L190" s="2" t="n">
         <v>0</v>
@@ -10534,31 +10534,31 @@
         <v>-1</v>
       </c>
       <c r="N190" s="2" t="n">
-        <v>0.0475194419643587</v>
+        <v>-0.0976280706816534</v>
       </c>
       <c r="O190" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="n">
-        <v>3297</v>
+        <v>3224</v>
       </c>
       <c r="B191" s="2" t="inlineStr">
         <is>
-          <t>杭特</t>
+          <t>三顧</t>
         </is>
       </c>
       <c r="C191" s="2" t="n">
         <v/>
       </c>
       <c r="D191" s="2" t="n">
-        <v>275.2312917753184</v>
+        <v>280.6561069827913</v>
       </c>
       <c r="E191" s="2" t="n">
-        <v>31.25</v>
+        <v>38.8</v>
       </c>
       <c r="F191" s="2" t="inlineStr">
         <is>
@@ -10569,13 +10569,13 @@
         <v>0</v>
       </c>
       <c r="H191" s="2" t="n">
-        <v>47.28319070342984</v>
+        <v>46.57393255017862</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>14.79492302497501</v>
+        <v>18.46837286975088</v>
       </c>
       <c r="J191" s="2" t="n">
-        <v>0.4231208155100484</v>
+        <v>1.018028609828388</v>
       </c>
       <c r="K191" s="2" t="n">
         <v>1</v>
@@ -10587,7 +10587,7 @@
         <v>-1</v>
       </c>
       <c r="N191" s="2" t="n">
-        <v>0.0179799365181075</v>
+        <v>0.2580450131449521</v>
       </c>
       <c r="O191" s="2" t="inlineStr">
         <is>
@@ -10597,21 +10597,21 @@
     </row>
     <row r="192">
       <c r="A192" s="2" t="n">
-        <v>3363</v>
+        <v>4178</v>
       </c>
       <c r="B192" s="2" t="inlineStr">
         <is>
-          <t>上詮</t>
+          <t>永笙-KY</t>
         </is>
       </c>
       <c r="C192" s="2" t="n">
         <v/>
       </c>
       <c r="D192" s="2" t="n">
-        <v>273.4089795702635</v>
+        <v>279.059657663656</v>
       </c>
       <c r="E192" s="2" t="n">
-        <v>712</v>
+        <v>17.2</v>
       </c>
       <c r="F192" s="2" t="inlineStr">
         <is>
@@ -10622,13 +10622,13 @@
         <v>0</v>
       </c>
       <c r="H192" s="2" t="n">
-        <v>41.70182809443223</v>
+        <v>23.39492886290931</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>21.18202872864169</v>
+        <v>58.46339584482742</v>
       </c>
       <c r="J192" s="2" t="n">
-        <v>0.5149030328123567</v>
+        <v>1.152793231499703</v>
       </c>
       <c r="K192" s="2" t="n">
         <v>0</v>
@@ -10640,31 +10640,31 @@
         <v>-1</v>
       </c>
       <c r="N192" s="2" t="n">
-        <v>-13.75982500361082</v>
+        <v>0.0475194419643587</v>
       </c>
       <c r="O192" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="n">
-        <v>3623</v>
+        <v>3297</v>
       </c>
       <c r="B193" s="2" t="inlineStr">
         <is>
-          <t>富晶通</t>
+          <t>杭特</t>
         </is>
       </c>
       <c r="C193" s="2" t="n">
         <v/>
       </c>
       <c r="D193" s="2" t="n">
-        <v>271.9630388245888</v>
+        <v>275.2312917753184</v>
       </c>
       <c r="E193" s="2" t="n">
-        <v>23.3</v>
+        <v>31.25</v>
       </c>
       <c r="F193" s="2" t="inlineStr">
         <is>
@@ -10675,16 +10675,16 @@
         <v>0</v>
       </c>
       <c r="H193" s="2" t="n">
-        <v>49.2169839154753</v>
+        <v>47.28319070342984</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>12.93809821070489</v>
+        <v>14.79492302497501</v>
       </c>
       <c r="J193" s="2" t="n">
-        <v>0.3120562538084329</v>
+        <v>0.4231208155100484</v>
       </c>
       <c r="K193" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L193" s="2" t="n">
         <v>0</v>
@@ -10693,31 +10693,31 @@
         <v>-1</v>
       </c>
       <c r="N193" s="2" t="n">
-        <v>-0.079231080629642</v>
+        <v>0.0179799365181075</v>
       </c>
       <c r="O193" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="n">
-        <v>3689</v>
+        <v>3363</v>
       </c>
       <c r="B194" s="2" t="inlineStr">
         <is>
-          <t>湧德</t>
+          <t>上詮</t>
         </is>
       </c>
       <c r="C194" s="2" t="n">
         <v/>
       </c>
       <c r="D194" s="2" t="n">
-        <v>266.812771719711</v>
+        <v>273.4089795702635</v>
       </c>
       <c r="E194" s="2" t="n">
-        <v>120.5</v>
+        <v>712</v>
       </c>
       <c r="F194" s="2" t="inlineStr">
         <is>
@@ -10728,13 +10728,13 @@
         <v>0</v>
       </c>
       <c r="H194" s="2" t="n">
-        <v>44.75923535507079</v>
+        <v>41.70182809443223</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>17.95187561343488</v>
+        <v>21.18202872864169</v>
       </c>
       <c r="J194" s="2" t="n">
-        <v>0.3445587334200762</v>
+        <v>0.5149030328123567</v>
       </c>
       <c r="K194" s="2" t="n">
         <v>0</v>
@@ -10746,31 +10746,31 @@
         <v>-1</v>
       </c>
       <c r="N194" s="2" t="n">
-        <v>-1.023602208917537</v>
+        <v>-13.75982500361082</v>
       </c>
       <c r="O194" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="n">
-        <v>3669</v>
+        <v>3623</v>
       </c>
       <c r="B195" s="2" t="inlineStr">
         <is>
-          <t>圓展</t>
+          <t>富晶通</t>
         </is>
       </c>
       <c r="C195" s="2" t="n">
         <v/>
       </c>
       <c r="D195" s="2" t="n">
-        <v>266.1467657044014</v>
+        <v>271.9630388245888</v>
       </c>
       <c r="E195" s="2" t="n">
-        <v>35.85</v>
+        <v>23.3</v>
       </c>
       <c r="F195" s="2" t="inlineStr">
         <is>
@@ -10781,16 +10781,16 @@
         <v>0</v>
       </c>
       <c r="H195" s="2" t="n">
-        <v>42.17153960620906</v>
+        <v>49.2169839154753</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>19.97921248187038</v>
+        <v>12.93809821070489</v>
       </c>
       <c r="J195" s="2" t="n">
-        <v>0.251284910075081</v>
+        <v>0.3120562538084329</v>
       </c>
       <c r="K195" s="2" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="L195" s="2" t="n">
         <v>0</v>
@@ -10799,31 +10799,31 @@
         <v>-1</v>
       </c>
       <c r="N195" s="2" t="n">
-        <v>-0.3267112287330006</v>
+        <v>-0.079231080629642</v>
       </c>
       <c r="O195" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="n">
-        <v>3708</v>
+        <v>3689</v>
       </c>
       <c r="B196" s="2" t="inlineStr">
         <is>
-          <t>上緯投控</t>
+          <t>湧德</t>
         </is>
       </c>
       <c r="C196" s="2" t="n">
         <v/>
       </c>
       <c r="D196" s="2" t="n">
-        <v>265.3201162610261</v>
+        <v>266.812771719711</v>
       </c>
       <c r="E196" s="2" t="n">
-        <v>115.5</v>
+        <v>120.5</v>
       </c>
       <c r="F196" s="2" t="inlineStr">
         <is>
@@ -10834,13 +10834,13 @@
         <v>0</v>
       </c>
       <c r="H196" s="2" t="n">
-        <v>43.6482987726066</v>
+        <v>44.75923535507079</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>10.55835727565716</v>
+        <v>17.95187561343488</v>
       </c>
       <c r="J196" s="2" t="n">
-        <v>0.7418708561903884</v>
+        <v>0.3445587334200762</v>
       </c>
       <c r="K196" s="2" t="n">
         <v>0</v>
@@ -10852,7 +10852,7 @@
         <v>-1</v>
       </c>
       <c r="N196" s="2" t="n">
-        <v>-0.647703496783568</v>
+        <v>-1.023602208917537</v>
       </c>
       <c r="O196" s="2" t="inlineStr">
         <is>
@@ -10862,21 +10862,21 @@
     </row>
     <row r="197">
       <c r="A197" s="2" t="n">
-        <v>3219</v>
+        <v>3669</v>
       </c>
       <c r="B197" s="2" t="inlineStr">
         <is>
-          <t>倚強股份</t>
+          <t>圓展</t>
         </is>
       </c>
       <c r="C197" s="2" t="n">
         <v/>
       </c>
       <c r="D197" s="2" t="n">
-        <v>259.4777013575965</v>
+        <v>266.1467657044014</v>
       </c>
       <c r="E197" s="2" t="n">
-        <v>74.3</v>
+        <v>35.85</v>
       </c>
       <c r="F197" s="2" t="inlineStr">
         <is>
@@ -10887,16 +10887,16 @@
         <v>0</v>
       </c>
       <c r="H197" s="2" t="n">
-        <v>45.80210638438658</v>
+        <v>42.17153960620906</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>14.30130612308958</v>
+        <v>19.97921248187038</v>
       </c>
       <c r="J197" s="2" t="n">
-        <v>0.4575262452484781</v>
+        <v>0.251284910075081</v>
       </c>
       <c r="K197" s="2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="L197" s="2" t="n">
         <v>0</v>
@@ -10905,31 +10905,31 @@
         <v>-1</v>
       </c>
       <c r="N197" s="2" t="n">
-        <v>-0.8941203889615392</v>
+        <v>-0.3267112287330006</v>
       </c>
       <c r="O197" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, foreign_buy_3d</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="n">
-        <v>3232</v>
+        <v>3708</v>
       </c>
       <c r="B198" s="2" t="inlineStr">
         <is>
-          <t>昱捷</t>
+          <t>上緯投控</t>
         </is>
       </c>
       <c r="C198" s="2" t="n">
         <v/>
       </c>
       <c r="D198" s="2" t="n">
-        <v>252.9212317883492</v>
+        <v>265.3201162610261</v>
       </c>
       <c r="E198" s="2" t="n">
-        <v>22.55</v>
+        <v>115.5</v>
       </c>
       <c r="F198" s="2" t="inlineStr">
         <is>
@@ -10940,16 +10940,16 @@
         <v>0</v>
       </c>
       <c r="H198" s="2" t="n">
-        <v>48.96167885844847</v>
+        <v>43.6482987726066</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>19.23980470988415</v>
+        <v>10.55835727565716</v>
       </c>
       <c r="J198" s="2" t="n">
-        <v>1.455063681157233</v>
+        <v>0.7418708561903884</v>
       </c>
       <c r="K198" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L198" s="2" t="n">
         <v>0</v>
@@ -10958,31 +10958,31 @@
         <v>-1</v>
       </c>
       <c r="N198" s="2" t="n">
-        <v>-0.1003423995568155</v>
+        <v>-0.647703496783568</v>
       </c>
       <c r="O198" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="n">
-        <v>3499</v>
+        <v>3219</v>
       </c>
       <c r="B199" s="2" t="inlineStr">
         <is>
-          <t>環天科</t>
+          <t>倚強股份</t>
         </is>
       </c>
       <c r="C199" s="2" t="n">
         <v/>
       </c>
       <c r="D199" s="2" t="n">
-        <v>251.3114140552183</v>
+        <v>259.4777013575965</v>
       </c>
       <c r="E199" s="2" t="n">
-        <v>14.7</v>
+        <v>74.3</v>
       </c>
       <c r="F199" s="2" t="inlineStr">
         <is>
@@ -10993,16 +10993,16 @@
         <v>0</v>
       </c>
       <c r="H199" s="2" t="n">
-        <v>44.3951553654942</v>
+        <v>45.80210638438658</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>27.88635873370767</v>
+        <v>14.30130612308958</v>
       </c>
       <c r="J199" s="2" t="n">
-        <v>1.184896804443052</v>
+        <v>0.4575262452484781</v>
       </c>
       <c r="K199" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L199" s="2" t="n">
         <v>0</v>
@@ -11011,31 +11011,31 @@
         <v>-1</v>
       </c>
       <c r="N199" s="2" t="n">
-        <v>0.0336904458479322</v>
+        <v>-0.8941203889615392</v>
       </c>
       <c r="O199" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60, avoid_chase</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="n">
-        <v>3622</v>
+        <v>3232</v>
       </c>
       <c r="B200" s="2" t="inlineStr">
         <is>
-          <t>洋華</t>
+          <t>昱捷</t>
         </is>
       </c>
       <c r="C200" s="2" t="n">
         <v/>
       </c>
       <c r="D200" s="2" t="n">
-        <v>251.0182033207657</v>
+        <v>252.9212317883492</v>
       </c>
       <c r="E200" s="2" t="n">
-        <v>56.5</v>
+        <v>22.55</v>
       </c>
       <c r="F200" s="2" t="inlineStr">
         <is>
@@ -11046,16 +11046,16 @@
         <v>0</v>
       </c>
       <c r="H200" s="2" t="n">
-        <v>50.34087844686182</v>
+        <v>48.96167885844847</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>15.52627012663402</v>
+        <v>19.23980470988415</v>
       </c>
       <c r="J200" s="2" t="n">
-        <v>0.5687089927209985</v>
+        <v>1.455063681157233</v>
       </c>
       <c r="K200" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L200" s="2" t="n">
         <v>0</v>
@@ -11064,31 +11064,31 @@
         <v>-1</v>
       </c>
       <c r="N200" s="2" t="n">
-        <v>-0.1776076344673831</v>
+        <v>-0.1003423995568155</v>
       </c>
       <c r="O200" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
+          <t>above_ema60, market_above_ma60, avoid_chase, above_ichimoku_cloud</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="n">
-        <v>3388</v>
+        <v>3499</v>
       </c>
       <c r="B201" s="2" t="inlineStr">
         <is>
-          <t>崇越電</t>
+          <t>環天科</t>
         </is>
       </c>
       <c r="C201" s="2" t="n">
         <v/>
       </c>
       <c r="D201" s="2" t="n">
-        <v>248.8782971235258</v>
+        <v>251.3114140552183</v>
       </c>
       <c r="E201" s="2" t="n">
-        <v>92.2</v>
+        <v>14.7</v>
       </c>
       <c r="F201" s="2" t="inlineStr">
         <is>
@@ -11099,16 +11099,16 @@
         <v>0</v>
       </c>
       <c r="H201" s="2" t="n">
-        <v>44.20111460937794</v>
+        <v>44.3951553654942</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>19.5184427460274</v>
+        <v>27.88635873370767</v>
       </c>
       <c r="J201" s="2" t="n">
-        <v>0.3707270733027903</v>
+        <v>1.184896804443052</v>
       </c>
       <c r="K201" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L201" s="2" t="n">
         <v>0</v>
@@ -11117,31 +11117,31 @@
         <v>-1</v>
       </c>
       <c r="N201" s="2" t="n">
-        <v>-0.8131239572691222</v>
+        <v>0.0336904458479322</v>
       </c>
       <c r="O201" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="n">
-        <v>3466</v>
+        <v>3622</v>
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>德晉</t>
+          <t>洋華</t>
         </is>
       </c>
       <c r="C202" s="2" t="n">
         <v/>
       </c>
       <c r="D202" s="2" t="n">
-        <v>245.0900878065954</v>
+        <v>251.0182033207657</v>
       </c>
       <c r="E202" s="2" t="n">
-        <v>33.05</v>
+        <v>56.5</v>
       </c>
       <c r="F202" s="2" t="inlineStr">
         <is>
@@ -11152,13 +11152,13 @@
         <v>0</v>
       </c>
       <c r="H202" s="2" t="n">
-        <v>46.11175035960725</v>
+        <v>50.34087844686182</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>16.1328832950927</v>
+        <v>15.52627012663402</v>
       </c>
       <c r="J202" s="2" t="n">
-        <v>0.4752301247570609</v>
+        <v>0.5687089927209985</v>
       </c>
       <c r="K202" s="2" t="n">
         <v>0</v>
@@ -11170,31 +11170,31 @@
         <v>-1</v>
       </c>
       <c r="N202" s="2" t="n">
-        <v>0.2878114801183742</v>
+        <v>-0.1776076344673831</v>
       </c>
       <c r="O202" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="n">
-        <v>3713</v>
+        <v>3388</v>
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>新晶投控</t>
+          <t>崇越電</t>
         </is>
       </c>
       <c r="C203" s="2" t="n">
         <v/>
       </c>
       <c r="D203" s="2" t="n">
-        <v>234.2371842246896</v>
+        <v>248.8782971235258</v>
       </c>
       <c r="E203" s="2" t="n">
-        <v>15.05</v>
+        <v>92.2</v>
       </c>
       <c r="F203" s="2" t="inlineStr">
         <is>
@@ -11205,13 +11205,13 @@
         <v>0</v>
       </c>
       <c r="H203" s="2" t="n">
-        <v>44.63244454586199</v>
+        <v>44.20111460937794</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>18.80425148907214</v>
+        <v>19.5184427460274</v>
       </c>
       <c r="J203" s="2" t="n">
-        <v>0.7752905906462106</v>
+        <v>0.3707270733027903</v>
       </c>
       <c r="K203" s="2" t="n">
         <v>0</v>
@@ -11223,31 +11223,31 @@
         <v>-1</v>
       </c>
       <c r="N203" s="2" t="n">
-        <v>-0.1242272435775178</v>
+        <v>-0.8131239572691222</v>
       </c>
       <c r="O203" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="n">
-        <v>3593</v>
+        <v>3466</v>
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>力銘</t>
+          <t>德晉</t>
         </is>
       </c>
       <c r="C204" s="2" t="n">
         <v/>
       </c>
       <c r="D204" s="2" t="n">
-        <v>233.256466265823</v>
+        <v>245.0900878065954</v>
       </c>
       <c r="E204" s="2" t="n">
-        <v>16</v>
+        <v>33.05</v>
       </c>
       <c r="F204" s="2" t="inlineStr">
         <is>
@@ -11258,13 +11258,13 @@
         <v>0</v>
       </c>
       <c r="H204" s="2" t="n">
-        <v>40.76431774701384</v>
+        <v>46.11175035960725</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>20.6795735780122</v>
+        <v>16.1328832950927</v>
       </c>
       <c r="J204" s="2" t="n">
-        <v>0.8129488525133071</v>
+        <v>0.4752301247570609</v>
       </c>
       <c r="K204" s="2" t="n">
         <v>0</v>
@@ -11276,31 +11276,31 @@
         <v>-1</v>
       </c>
       <c r="N204" s="2" t="n">
-        <v>-0.08382234100752931</v>
+        <v>0.2878114801183742</v>
       </c>
       <c r="O204" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, obv_uptrend, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="n">
-        <v>4148</v>
+        <v>3713</v>
       </c>
       <c r="B205" s="2" t="inlineStr">
         <is>
-          <t>全宇生技-KY</t>
+          <t>新晶投控</t>
         </is>
       </c>
       <c r="C205" s="2" t="n">
         <v/>
       </c>
       <c r="D205" s="2" t="n">
-        <v>229.0930906651811</v>
+        <v>234.2371842246896</v>
       </c>
       <c r="E205" s="2" t="n">
-        <v>30.65</v>
+        <v>15.05</v>
       </c>
       <c r="F205" s="2" t="inlineStr">
         <is>
@@ -11311,13 +11311,13 @@
         <v>0</v>
       </c>
       <c r="H205" s="2" t="n">
-        <v>38.01328002965563</v>
+        <v>44.63244454586199</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>22.87129576352825</v>
+        <v>18.80425148907214</v>
       </c>
       <c r="J205" s="2" t="n">
-        <v>1.465955008307782</v>
+        <v>0.7752905906462106</v>
       </c>
       <c r="K205" s="2" t="n">
         <v>0</v>
@@ -11329,31 +11329,31 @@
         <v>-1</v>
       </c>
       <c r="N205" s="2" t="n">
-        <v>0.1587910253246383</v>
+        <v>-0.1242272435775178</v>
       </c>
       <c r="O205" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="n">
-        <v>3354</v>
+        <v>3593</v>
       </c>
       <c r="B206" s="2" t="inlineStr">
         <is>
-          <t>律勝</t>
+          <t>力銘</t>
         </is>
       </c>
       <c r="C206" s="2" t="n">
         <v/>
       </c>
       <c r="D206" s="2" t="n">
-        <v>226.2932770591245</v>
+        <v>233.256466265823</v>
       </c>
       <c r="E206" s="2" t="n">
-        <v>29.4</v>
+        <v>16</v>
       </c>
       <c r="F206" s="2" t="inlineStr">
         <is>
@@ -11364,16 +11364,16 @@
         <v>0</v>
       </c>
       <c r="H206" s="2" t="n">
-        <v>48.41770238226951</v>
+        <v>40.76431774701384</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>21.13928662519362</v>
+        <v>20.6795735780122</v>
       </c>
       <c r="J206" s="2" t="n">
-        <v>0.762236609663261</v>
+        <v>0.8129488525133071</v>
       </c>
       <c r="K206" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L206" s="2" t="n">
         <v>0</v>
@@ -11382,31 +11382,31 @@
         <v>-1</v>
       </c>
       <c r="N206" s="2" t="n">
-        <v>-0.2200916167583875</v>
+        <v>-0.08382234100752931</v>
       </c>
       <c r="O206" s="2" t="inlineStr">
         <is>
-          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
+          <t>ema60_gt_ema120, market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="n">
-        <v>3434</v>
+        <v>4148</v>
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>哲固</t>
+          <t>全宇生技-KY</t>
         </is>
       </c>
       <c r="C207" s="2" t="n">
         <v/>
       </c>
       <c r="D207" s="2" t="n">
-        <v>221.5681720430988</v>
+        <v>229.0930906651811</v>
       </c>
       <c r="E207" s="2" t="n">
-        <v>29.75</v>
+        <v>30.65</v>
       </c>
       <c r="F207" s="2" t="inlineStr">
         <is>
@@ -11417,13 +11417,13 @@
         <v>0</v>
       </c>
       <c r="H207" s="2" t="n">
-        <v>45.45237066477775</v>
+        <v>38.01328002965563</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>23.61800215999284</v>
+        <v>22.87129576352825</v>
       </c>
       <c r="J207" s="2" t="n">
-        <v>0.3847564771851635</v>
+        <v>1.465955008307782</v>
       </c>
       <c r="K207" s="2" t="n">
         <v>0</v>
@@ -11435,31 +11435,31 @@
         <v>-1</v>
       </c>
       <c r="N207" s="2" t="n">
-        <v>-0.3070565583893425</v>
+        <v>0.1587910253246383</v>
       </c>
       <c r="O207" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="n">
-        <v>3710</v>
+        <v>3354</v>
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>連展投控</t>
+          <t>律勝</t>
         </is>
       </c>
       <c r="C208" s="2" t="n">
         <v/>
       </c>
       <c r="D208" s="2" t="n">
-        <v>221.4518496302138</v>
+        <v>226.2932770591245</v>
       </c>
       <c r="E208" s="2" t="n">
-        <v>6.2</v>
+        <v>29.4</v>
       </c>
       <c r="F208" s="2" t="inlineStr">
         <is>
@@ -11470,13 +11470,13 @@
         <v>0</v>
       </c>
       <c r="H208" s="2" t="n">
-        <v>46.0239114450733</v>
+        <v>48.41770238226951</v>
       </c>
       <c r="I208" s="2" t="n">
-        <v>12.20949971475762</v>
+        <v>21.13928662519362</v>
       </c>
       <c r="J208" s="2" t="n">
-        <v>1.061577001854865</v>
+        <v>0.762236609663261</v>
       </c>
       <c r="K208" s="2" t="n">
         <v>1</v>
@@ -11488,31 +11488,31 @@
         <v>-1</v>
       </c>
       <c r="N208" s="2" t="n">
-        <v>0.0190538550081155</v>
+        <v>-0.2200916167583875</v>
       </c>
       <c r="O208" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>ema60_gt_ema120, market_above_ma60, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="n">
-        <v>3686</v>
+        <v>3434</v>
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>達能</t>
+          <t>哲固</t>
         </is>
       </c>
       <c r="C209" s="2" t="n">
         <v/>
       </c>
       <c r="D209" s="2" t="n">
-        <v>220.1961503091636</v>
+        <v>221.5681720430988</v>
       </c>
       <c r="E209" s="2" t="n">
-        <v>17.15</v>
+        <v>29.75</v>
       </c>
       <c r="F209" s="2" t="inlineStr">
         <is>
@@ -11523,16 +11523,16 @@
         <v>0</v>
       </c>
       <c r="H209" s="2" t="n">
-        <v>48.35103447687114</v>
+        <v>45.45237066477775</v>
       </c>
       <c r="I209" s="2" t="n">
-        <v>15.64438082225382</v>
+        <v>23.61800215999284</v>
       </c>
       <c r="J209" s="2" t="n">
-        <v>0.8543946555277133</v>
+        <v>0.3847564771851635</v>
       </c>
       <c r="K209" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L209" s="2" t="n">
         <v>0</v>
@@ -11541,31 +11541,31 @@
         <v>-1</v>
       </c>
       <c r="N209" s="2" t="n">
-        <v>0.0333369857118369</v>
+        <v>-0.3070565583893425</v>
       </c>
       <c r="O209" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, adx_trending, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="n">
-        <v>3557</v>
+        <v>3710</v>
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>嘉威</t>
+          <t>連展投控</t>
         </is>
       </c>
       <c r="C210" s="2" t="n">
         <v/>
       </c>
       <c r="D210" s="2" t="n">
-        <v>218.1196709814013</v>
+        <v>221.4518496302138</v>
       </c>
       <c r="E210" s="2" t="n">
-        <v>26.2</v>
+        <v>6.2</v>
       </c>
       <c r="F210" s="2" t="inlineStr">
         <is>
@@ -11576,16 +11576,16 @@
         <v>0</v>
       </c>
       <c r="H210" s="2" t="n">
-        <v>49.57032328735038</v>
+        <v>46.0239114450733</v>
       </c>
       <c r="I210" s="2" t="n">
-        <v>17.27580168956115</v>
+        <v>12.20949971475762</v>
       </c>
       <c r="J210" s="2" t="n">
-        <v>0.5835099731882487</v>
+        <v>1.061577001854865</v>
       </c>
       <c r="K210" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L210" s="2" t="n">
         <v>0</v>
@@ -11594,7 +11594,7 @@
         <v>-1</v>
       </c>
       <c r="N210" s="2" t="n">
-        <v>0.3874195768246781</v>
+        <v>0.0190538550081155</v>
       </c>
       <c r="O210" s="2" t="inlineStr">
         <is>
@@ -11604,21 +11604,21 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="n">
-        <v>3494</v>
+        <v>3686</v>
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>誠研</t>
+          <t>達能</t>
         </is>
       </c>
       <c r="C211" s="2" t="n">
         <v/>
       </c>
       <c r="D211" s="2" t="n">
-        <v>215.1094953692832</v>
+        <v>220.1961503091636</v>
       </c>
       <c r="E211" s="2" t="n">
-        <v>8.02</v>
+        <v>17.15</v>
       </c>
       <c r="F211" s="2" t="inlineStr">
         <is>
@@ -11629,16 +11629,16 @@
         <v>0</v>
       </c>
       <c r="H211" s="2" t="n">
-        <v>49.55517972338813</v>
+        <v>48.35103447687114</v>
       </c>
       <c r="I211" s="2" t="n">
-        <v>9.854844603834543</v>
+        <v>15.64438082225382</v>
       </c>
       <c r="J211" s="2" t="n">
-        <v>0.8404334572233996</v>
+        <v>0.8543946555277133</v>
       </c>
       <c r="K211" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L211" s="2" t="n">
         <v>0</v>
@@ -11647,7 +11647,7 @@
         <v>-1</v>
       </c>
       <c r="N211" s="2" t="n">
-        <v>-0.0047222896953103</v>
+        <v>0.0333369857118369</v>
       </c>
       <c r="O211" s="2" t="inlineStr">
         <is>
@@ -11657,21 +11657,21 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="n">
-        <v>3178</v>
+        <v>3557</v>
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>公準</t>
+          <t>嘉威</t>
         </is>
       </c>
       <c r="C212" s="2" t="n">
         <v/>
       </c>
       <c r="D212" s="2" t="n">
-        <v>211.3484270245831</v>
+        <v>218.1196709814013</v>
       </c>
       <c r="E212" s="2" t="n">
-        <v>68.8</v>
+        <v>26.2</v>
       </c>
       <c r="F212" s="2" t="inlineStr">
         <is>
@@ -11682,16 +11682,16 @@
         <v>0</v>
       </c>
       <c r="H212" s="2" t="n">
-        <v>54.91762955557353</v>
+        <v>49.57032328735038</v>
       </c>
       <c r="I212" s="2" t="n">
-        <v>18.65103342436845</v>
+        <v>17.27580168956115</v>
       </c>
       <c r="J212" s="2" t="n">
-        <v>0.7526202581200381</v>
+        <v>0.5835099731882487</v>
       </c>
       <c r="K212" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L212" s="2" t="n">
         <v>0</v>
@@ -11700,31 +11700,31 @@
         <v>-1</v>
       </c>
       <c r="N212" s="2" t="n">
-        <v>-0.0289028802336622</v>
+        <v>0.3874195768246781</v>
       </c>
       <c r="O212" s="2" t="inlineStr">
         <is>
-          <t>above_ema60, ema60_gt_ema120, market_above_ma60</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="213">
       <c r="A213" s="2" t="n">
-        <v>3548</v>
+        <v>3494</v>
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>兆利</t>
+          <t>誠研</t>
         </is>
       </c>
       <c r="C213" s="2" t="n">
         <v/>
       </c>
       <c r="D213" s="2" t="n">
-        <v>190.1524290894424</v>
+        <v>215.1094953692832</v>
       </c>
       <c r="E213" s="2" t="n">
-        <v>89</v>
+        <v>8.02</v>
       </c>
       <c r="F213" s="2" t="inlineStr">
         <is>
@@ -11735,13 +11735,13 @@
         <v>0</v>
       </c>
       <c r="H213" s="2" t="n">
-        <v>39.81842865547117</v>
+        <v>49.55517972338813</v>
       </c>
       <c r="I213" s="2" t="n">
-        <v>13.31037272553994</v>
+        <v>9.854844603834543</v>
       </c>
       <c r="J213" s="2" t="n">
-        <v>0.5015017607038008</v>
+        <v>0.8404334572233996</v>
       </c>
       <c r="K213" s="2" t="n">
         <v>2</v>
@@ -11753,31 +11753,31 @@
         <v>-1</v>
       </c>
       <c r="N213" s="2" t="n">
-        <v>-0.7237973138712055</v>
+        <v>-0.0047222896953103</v>
       </c>
       <c r="O213" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="214">
       <c r="A214" s="2" t="n">
-        <v>3541</v>
+        <v>3178</v>
       </c>
       <c r="B214" s="2" t="inlineStr">
         <is>
-          <t>西柏</t>
+          <t>公準</t>
         </is>
       </c>
       <c r="C214" s="2" t="n">
         <v/>
       </c>
       <c r="D214" s="2" t="n">
-        <v>186.1047049734353</v>
+        <v>211.3484270245831</v>
       </c>
       <c r="E214" s="2" t="n">
-        <v>21.85</v>
+        <v>68.8</v>
       </c>
       <c r="F214" s="2" t="inlineStr">
         <is>
@@ -11788,16 +11788,16 @@
         <v>0</v>
       </c>
       <c r="H214" s="2" t="n">
-        <v>40.03991461386758</v>
+        <v>54.91762955557353</v>
       </c>
       <c r="I214" s="2" t="n">
-        <v>37.57413370592099</v>
+        <v>18.65103342436845</v>
       </c>
       <c r="J214" s="2" t="n">
-        <v>0.5477309651921888</v>
+        <v>0.7526202581200381</v>
       </c>
       <c r="K214" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L214" s="2" t="n">
         <v>0</v>
@@ -11806,31 +11806,31 @@
         <v>-1</v>
       </c>
       <c r="N214" s="2" t="n">
-        <v>0.0133755815783762</v>
+        <v>-0.0289028802336622</v>
       </c>
       <c r="O214" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, adx_trending</t>
+          <t>above_ema60, ema60_gt_ema120, market_above_ma60</t>
         </is>
       </c>
     </row>
     <row r="215">
       <c r="A215" s="2" t="n">
-        <v>4133</v>
+        <v>3548</v>
       </c>
       <c r="B215" s="2" t="inlineStr">
         <is>
-          <t>亞諾法</t>
+          <t>兆利</t>
         </is>
       </c>
       <c r="C215" s="2" t="n">
         <v/>
       </c>
       <c r="D215" s="2" t="n">
-        <v>183.6413398410541</v>
+        <v>190.1524290894424</v>
       </c>
       <c r="E215" s="2" t="n">
-        <v>20.7</v>
+        <v>89</v>
       </c>
       <c r="F215" s="2" t="inlineStr">
         <is>
@@ -11841,16 +11841,16 @@
         <v>0</v>
       </c>
       <c r="H215" s="2" t="n">
-        <v>43.41895566145328</v>
+        <v>39.81842865547117</v>
       </c>
       <c r="I215" s="2" t="n">
-        <v>11.06534576310716</v>
+        <v>13.31037272553994</v>
       </c>
       <c r="J215" s="2" t="n">
-        <v>0.6998411025076552</v>
+        <v>0.5015017607038008</v>
       </c>
       <c r="K215" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="L215" s="2" t="n">
         <v>0</v>
@@ -11859,31 +11859,31 @@
         <v>-1</v>
       </c>
       <c r="N215" s="2" t="n">
-        <v>0.0203618512063975</v>
+        <v>-0.7237973138712055</v>
       </c>
       <c r="O215" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, mfi_strong</t>
+          <t>market_above_ma60, avoid_chase, liquidity_ok</t>
         </is>
       </c>
     </row>
     <row r="216">
       <c r="A216" s="2" t="n">
-        <v>3272</v>
+        <v>3541</v>
       </c>
       <c r="B216" s="2" t="inlineStr">
         <is>
-          <t>東碩</t>
+          <t>西柏</t>
         </is>
       </c>
       <c r="C216" s="2" t="n">
         <v/>
       </c>
       <c r="D216" s="2" t="n">
-        <v>178.9532420262444</v>
+        <v>186.1047049734353</v>
       </c>
       <c r="E216" s="2" t="n">
-        <v>16.65</v>
+        <v>21.85</v>
       </c>
       <c r="F216" s="2" t="inlineStr">
         <is>
@@ -11894,13 +11894,13 @@
         <v>0</v>
       </c>
       <c r="H216" s="2" t="n">
-        <v>43.4872906400584</v>
+        <v>40.03991461386758</v>
       </c>
       <c r="I216" s="2" t="n">
-        <v>19.34221248188285</v>
+        <v>37.57413370592099</v>
       </c>
       <c r="J216" s="2" t="n">
-        <v>0.8851821297587628</v>
+        <v>0.5477309651921888</v>
       </c>
       <c r="K216" s="2" t="n">
         <v>0</v>
@@ -11912,31 +11912,31 @@
         <v>-1</v>
       </c>
       <c r="N216" s="2" t="n">
-        <v>-0.0236700741999913</v>
+        <v>0.0133755815783762</v>
       </c>
       <c r="O216" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
+          <t>market_above_ma60, avoid_chase, adx_trending</t>
         </is>
       </c>
     </row>
     <row r="217">
       <c r="A217" s="2" t="n">
-        <v>3664</v>
+        <v>4133</v>
       </c>
       <c r="B217" s="2" t="inlineStr">
         <is>
-          <t>安瑞-KY</t>
+          <t>亞諾法</t>
         </is>
       </c>
       <c r="C217" s="2" t="n">
         <v/>
       </c>
       <c r="D217" s="2" t="n">
-        <v>170.3465518484875</v>
+        <v>183.6413398410541</v>
       </c>
       <c r="E217" s="2" t="n">
-        <v>7.42</v>
+        <v>20.7</v>
       </c>
       <c r="F217" s="2" t="inlineStr">
         <is>
@@ -11947,13 +11947,13 @@
         <v>0</v>
       </c>
       <c r="H217" s="2" t="n">
-        <v>49.51664917676781</v>
+        <v>43.41895566145328</v>
       </c>
       <c r="I217" s="2" t="n">
-        <v>9.465859934104634</v>
+        <v>11.06534576310716</v>
       </c>
       <c r="J217" s="2" t="n">
-        <v>0.5973035497221675</v>
+        <v>0.6998411025076552</v>
       </c>
       <c r="K217" s="2" t="n">
         <v>0</v>
@@ -11965,31 +11965,31 @@
         <v>-1</v>
       </c>
       <c r="N217" s="2" t="n">
-        <v>-0.0302508124501769</v>
+        <v>0.0203618512063975</v>
       </c>
       <c r="O217" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, stronger_than_market</t>
+          <t>market_above_ma60, avoid_chase, mfi_strong</t>
         </is>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="n">
-        <v>3666</v>
+        <v>3272</v>
       </c>
       <c r="B218" s="2" t="inlineStr">
         <is>
-          <t>光耀</t>
+          <t>東碩</t>
         </is>
       </c>
       <c r="C218" s="2" t="n">
         <v/>
       </c>
       <c r="D218" s="2" t="n">
-        <v>170.2236245981331</v>
+        <v>178.9532420262444</v>
       </c>
       <c r="E218" s="2" t="n">
-        <v>25.45</v>
+        <v>16.65</v>
       </c>
       <c r="F218" s="2" t="inlineStr">
         <is>
@@ -12000,13 +12000,13 @@
         <v>0</v>
       </c>
       <c r="H218" s="2" t="n">
-        <v>37.23601443741156</v>
+        <v>43.4872906400584</v>
       </c>
       <c r="I218" s="2" t="n">
-        <v>13.09567514076778</v>
+        <v>19.34221248188285</v>
       </c>
       <c r="J218" s="2" t="n">
-        <v>0.963435925657961</v>
+        <v>0.8851821297587628</v>
       </c>
       <c r="K218" s="2" t="n">
         <v>0</v>
@@ -12018,31 +12018,31 @@
         <v>-1</v>
       </c>
       <c r="N218" s="2" t="n">
-        <v>-0.155780969139619</v>
+        <v>-0.0236700741999913</v>
       </c>
       <c r="O218" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, avoid_chase, obv_uptrend</t>
         </is>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="n">
-        <v>3632</v>
+        <v>3664</v>
       </c>
       <c r="B219" s="2" t="inlineStr">
         <is>
-          <t>研勤</t>
+          <t>安瑞-KY</t>
         </is>
       </c>
       <c r="C219" s="2" t="n">
         <v/>
       </c>
       <c r="D219" s="2" t="n">
-        <v>160.5060210735686</v>
+        <v>170.3465518484875</v>
       </c>
       <c r="E219" s="2" t="n">
-        <v>7.93</v>
+        <v>7.42</v>
       </c>
       <c r="F219" s="2" t="inlineStr">
         <is>
@@ -12053,13 +12053,13 @@
         <v>0</v>
       </c>
       <c r="H219" s="2" t="n">
-        <v>42.82700808785491</v>
+        <v>49.51664917676781</v>
       </c>
       <c r="I219" s="2" t="n">
-        <v>12.76843318452953</v>
+        <v>9.465859934104634</v>
       </c>
       <c r="J219" s="2" t="n">
-        <v>1.215480389859597</v>
+        <v>0.5973035497221675</v>
       </c>
       <c r="K219" s="2" t="n">
         <v>0</v>
@@ -12071,31 +12071,31 @@
         <v>-1</v>
       </c>
       <c r="N219" s="2" t="n">
-        <v>-0.0012388248779778</v>
+        <v>-0.0302508124501769</v>
       </c>
       <c r="O219" s="2" t="inlineStr">
         <is>
-          <t>market_above_ma60, avoid_chase</t>
+          <t>market_above_ma60, stronger_than_market</t>
         </is>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="n">
-        <v>3609</v>
+        <v>3666</v>
       </c>
       <c r="B220" s="2" t="inlineStr">
         <is>
-          <t>三一東林</t>
+          <t>光耀</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
         <v/>
       </c>
       <c r="D220" s="2" t="n">
-        <v>137.9882032273577</v>
+        <v>170.2236245981331</v>
       </c>
       <c r="E220" s="2" t="n">
-        <v>27.6</v>
+        <v>25.45</v>
       </c>
       <c r="F220" s="2" t="inlineStr">
         <is>
@@ -12106,13 +12106,13 @@
         <v>0</v>
       </c>
       <c r="H220" s="2" t="n">
-        <v>50.95583472794407</v>
+        <v>37.23601443741156</v>
       </c>
       <c r="I220" s="2" t="n">
-        <v>12.95906418661302</v>
+        <v>13.09567514076778</v>
       </c>
       <c r="J220" s="2" t="n">
-        <v>1.25871712213214</v>
+        <v>0.963435925657961</v>
       </c>
       <c r="K220" s="2" t="n">
         <v>0</v>
@@ -12124,7 +12124,7 @@
         <v>-1</v>
       </c>
       <c r="N220" s="2" t="n">
-        <v>-0.1603554138147829</v>
+        <v>-0.155780969139619</v>
       </c>
       <c r="O220" s="2" t="inlineStr">
         <is>
@@ -12134,21 +12134,21 @@
     </row>
     <row r="221">
       <c r="A221" s="2" t="n">
-        <v>3508</v>
+        <v>3632</v>
       </c>
       <c r="B221" s="2" t="inlineStr">
         <is>
-          <t>位速</t>
+          <t>研勤</t>
         </is>
       </c>
       <c r="C221" s="2" t="n">
         <v/>
       </c>
       <c r="D221" s="2" t="n">
-        <v>130.4871698606401</v>
+        <v>160.5060210735686</v>
       </c>
       <c r="E221" s="2" t="n">
-        <v>18.65</v>
+        <v>7.93</v>
       </c>
       <c r="F221" s="2" t="inlineStr">
         <is>
@@ -12159,16 +12159,16 @@
         <v>0</v>
       </c>
       <c r="H221" s="2" t="n">
-        <v>40.23008044732842</v>
+        <v>42.82700808785491</v>
       </c>
       <c r="I221" s="2" t="n">
-        <v>12.83150354005056</v>
+        <v>12.76843318452953</v>
       </c>
       <c r="J221" s="2" t="n">
-        <v>1.079532248478326</v>
+        <v>1.215480389859597</v>
       </c>
       <c r="K221" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L221" s="2" t="n">
         <v>0</v>
@@ -12177,7 +12177,7 @@
         <v>-1</v>
       </c>
       <c r="N221" s="2" t="n">
-        <v>0.1931760316990893</v>
+        <v>-0.0012388248779778</v>
       </c>
       <c r="O221" s="2" t="inlineStr">
         <is>
@@ -12187,52 +12187,158 @@
     </row>
     <row r="222">
       <c r="A222" s="2" t="n">
+        <v>3609</v>
+      </c>
+      <c r="B222" s="2" t="inlineStr">
+        <is>
+          <t>三一東林</t>
+        </is>
+      </c>
+      <c r="C222" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D222" s="2" t="n">
+        <v>137.9882032273577</v>
+      </c>
+      <c r="E222" s="2" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="F222" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G222" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H222" s="2" t="n">
+        <v>50.95583472794407</v>
+      </c>
+      <c r="I222" s="2" t="n">
+        <v>12.95906418661302</v>
+      </c>
+      <c r="J222" s="2" t="n">
+        <v>1.25871712213214</v>
+      </c>
+      <c r="K222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L222" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M222" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N222" s="2" t="n">
+        <v>-0.1603554138147829</v>
+      </c>
+      <c r="O222" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="2" t="n">
+        <v>3508</v>
+      </c>
+      <c r="B223" s="2" t="inlineStr">
+        <is>
+          <t>位速</t>
+        </is>
+      </c>
+      <c r="C223" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D223" s="2" t="n">
+        <v>130.4871698606401</v>
+      </c>
+      <c r="E223" s="2" t="n">
+        <v>18.65</v>
+      </c>
+      <c r="F223" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G223" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H223" s="2" t="n">
+        <v>40.23008044732842</v>
+      </c>
+      <c r="I223" s="2" t="n">
+        <v>12.83150354005056</v>
+      </c>
+      <c r="J223" s="2" t="n">
+        <v>1.079532248478326</v>
+      </c>
+      <c r="K223" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L223" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M223" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N223" s="2" t="n">
+        <v>0.1931760316990893</v>
+      </c>
+      <c r="O223" s="2" t="inlineStr">
+        <is>
+          <t>market_above_ma60, avoid_chase</t>
+        </is>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="2" t="n">
         <v>3540</v>
       </c>
-      <c r="B222" s="2" t="inlineStr">
+      <c r="B224" s="2" t="inlineStr">
         <is>
           <t>曜越</t>
         </is>
       </c>
-      <c r="C222" s="2" t="n">
-        <v/>
-      </c>
-      <c r="D222" s="2" t="n">
+      <c r="C224" s="2" t="n">
+        <v/>
+      </c>
+      <c r="D224" s="2" t="n">
         <v>105.8837889144976</v>
       </c>
-      <c r="E222" s="2" t="n">
+      <c r="E224" s="2" t="n">
         <v>25.35</v>
       </c>
-      <c r="F222" s="2" t="inlineStr">
-        <is>
-          <t>2026-06-22</t>
-        </is>
-      </c>
-      <c r="G222" s="2" t="b">
-        <v>0</v>
-      </c>
-      <c r="H222" s="2" t="n">
+      <c r="F224" s="2" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="G224" s="2" t="b">
+        <v>0</v>
+      </c>
+      <c r="H224" s="2" t="n">
         <v>42.43376677839633</v>
       </c>
-      <c r="I222" s="2" t="n">
+      <c r="I224" s="2" t="n">
         <v>14.11577826139581</v>
       </c>
-      <c r="J222" s="2" t="n">
+      <c r="J224" s="2" t="n">
         <v>0.7288259036940818</v>
       </c>
-      <c r="K222" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="L222" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M222" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N222" s="2" t="n">
+      <c r="K224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L224" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M224" s="2" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N224" s="2" t="n">
         <v>-0.1003105361410058</v>
       </c>
-      <c r="O222" s="2" t="inlineStr">
+      <c r="O224" s="2" t="inlineStr">
         <is>
           <t>market_above_ma60, avoid_chase</t>
         </is>
